--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R162"/>
+  <dimension ref="A1:R173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4123,12 +4123,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_repay.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_debt.tres</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_repay</t>
+          <t>demon_blood_debt</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>血偿</t>
+          <t>血债清算</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -4146,17 +4146,17 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -4171,20 +4171,14 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>血债清算</t>
         </is>
       </c>
       <c r="L53" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="4" t="n"/>
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="3" t="inlineStr"/>
@@ -4193,12 +4187,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_rite_slash.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_forge_armor.tres</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_rite_slash</t>
+          <t>demon_blood_forge_armor</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4208,7 +4202,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>血祭斩</t>
+          <t>血铸魔甲</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -4216,17 +4210,17 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -4245,15 +4239,15 @@
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O54" s="3" t="inlineStr"/>
       <c r="P54" s="4" t="n"/>
@@ -4263,12 +4257,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_sea_surge.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_repay.tres</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_surge</t>
+          <t>demon_blood_repay</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4278,67 +4272,73 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>血海滔天</t>
+          <t>血偿</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O55" s="3" t="inlineStr"/>
-      <c r="P55" s="4" t="n"/>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="Q55" s="3" t="inlineStr"/>
       <c r="R55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_ward.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_reversal.tres</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_ward</t>
+          <t>demon_blood_reversal</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>血盾</t>
+          <t>命血逆流</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -4385,30 +4385,36 @@
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="O56" s="3" t="inlineStr"/>
-      <c r="P56" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q56" s="3" t="inlineStr"/>
       <c r="R56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_rite_slash.tres</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>demon_defend</t>
+          <t>demon_blood_rite_slash</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4418,7 +4424,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>血祭斩</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -4426,12 +4432,12 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4446,19 +4452,25 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L57" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="4" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="3" t="inlineStr"/>
@@ -4467,12 +4479,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_sea_surge.tres</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>demon_desperate_burst</t>
+          <t>demon_blood_sea_surge</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4482,7 +4494,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>绝命爆发</t>
+          <t>血海滔天</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -4495,7 +4507,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4505,24 +4517,30 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="4" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="3" t="inlineStr"/>
@@ -4531,12 +4549,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_ward.tres</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>demon_flame</t>
+          <t>demon_blood_ward</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4546,52 +4564,52 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>魔焰燎原</t>
+          <t>血盾</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N59" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="4" t="n"/>
@@ -4601,12 +4619,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_black</t>
+          <t>demon_defend</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4616,7 +4634,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>魔焰黑·噬血</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4624,17 +4642,17 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4649,25 +4667,15 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="3" t="inlineStr"/>
       <c r="R60" s="4" t="n"/>
@@ -4675,12 +4683,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_blue</t>
+          <t>demon_desperate_burst</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4690,25 +4698,25 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>魔焰蓝·灵涌</t>
+          <t>绝命爆发</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -4718,22 +4726,18 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="4" t="n"/>
@@ -4743,12 +4747,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_green</t>
+          <t>demon_flame</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4758,20 +4762,20 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>魔焰绿·镇煞</t>
+          <t>魔焰燎原</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4786,17 +4790,25 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="3" t="inlineStr"/>
@@ -4805,12 +4817,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_heart</t>
+          <t>demon_flame_black</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4820,11 +4832,11 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>魔焰焚心</t>
+          <t>魔焰黑·噬血</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -4848,26 +4860,30 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="L63" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
       <c r="N63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O63" s="3" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="3" t="inlineStr"/>
       <c r="R63" s="4" t="n"/>
@@ -4875,12 +4891,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_purple</t>
+          <t>demon_flame_blue</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4890,7 +4906,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>魔焰紫·蚀魂</t>
+          <t>魔焰蓝·灵涌</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -4898,22 +4914,22 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4923,25 +4939,19 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="3" t="inlineStr"/>
       <c r="R64" s="4" t="n"/>
@@ -4949,12 +4959,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_red</t>
+          <t>demon_flame_green</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4964,25 +4974,25 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>魔焰红·焚界</t>
+          <t>魔焰绿·镇煞</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -4997,17 +5007,11 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="4" t="n"/>
@@ -5017,12 +5021,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_white</t>
+          <t>demon_flame_heart</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5032,11 +5036,11 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>魔焰白·护魂</t>
+          <t>魔焰焚心</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
@@ -5050,7 +5054,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -5060,7 +5064,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -5069,21 +5073,17 @@
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N66" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="3" t="inlineStr"/>
       <c r="R66" s="4" t="n"/>
@@ -5091,12 +5091,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_yellow</t>
+          <t>demon_flame_purple</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>魔焰黄·狂烬</t>
+          <t>魔焰紫·蚀魂</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -5139,13 +5139,25 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="4" t="n"/>
-      <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="3" t="inlineStr"/>
       <c r="R67" s="4" t="n"/>
@@ -5153,12 +5165,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>demon_flesh_rebirth</t>
+          <t>demon_flame_red</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5168,25 +5180,25 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>血肉重生</t>
+          <t>魔焰红·焚界</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -5196,18 +5208,22 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="4" t="n"/>
@@ -5217,12 +5233,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_devour</t>
+          <t>demon_flame_white</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5232,11 +5248,11 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>万魂噬天</t>
+          <t>魔焰白·护魂</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -5245,22 +5261,22 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -5269,17 +5285,21 @@
         </is>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O69" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="3" t="inlineStr"/>
       <c r="R69" s="4" t="n"/>
@@ -5287,12 +5307,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>demon_shatter_soul_seal</t>
+          <t>demon_flame_yellow</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5302,7 +5322,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>碎魂印</t>
+          <t>魔焰黄·狂烬</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -5315,7 +5335,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5330,25 +5350,17 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="3" t="inlineStr"/>
@@ -5357,12 +5369,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_devour_claw</t>
+          <t>demon_flesh_rebirth</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5372,7 +5384,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>噬魂爪</t>
+          <t>血肉重生</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -5380,17 +5392,17 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -5405,20 +5417,14 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L71" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="4" t="n"/>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="3" t="inlineStr"/>
@@ -5427,12 +5433,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>demon_strike</t>
+          <t>demon_forbidden_archive</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5442,44 +5448,44 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>窥心魔典</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>configured_discover_effect</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="4" t="n"/>
@@ -5491,12 +5497,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_membrane</t>
+          <t>demon_myriad_marks_return</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5506,25 +5512,25 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>血膜</t>
+          <t>万印归墟</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -5539,20 +5545,12 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>6</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -5561,12 +5559,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_qi_guard</t>
+          <t>demon_myriad_soul_devour</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5576,30 +5574,30 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>血气护体</t>
+          <t>万魂噬天</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -5609,12 +5607,20 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="3" t="inlineStr"/>
@@ -5623,12 +5629,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_recompense</t>
+          <t>demon_seven_flame_cycle</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5638,15 +5644,15 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>血偿万道</t>
+          <t>七焰回环</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5656,7 +5662,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -5671,7 +5677,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_flame_effect</t>
         </is>
       </c>
       <c r="L75" s="4" t="n"/>
@@ -5685,12 +5691,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_boundless</t>
+          <t>demon_sha_blade</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -5700,11 +5706,11 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>血海无量</t>
+          <t>煞刃</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
@@ -5713,12 +5719,12 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -5733,15 +5739,11 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>configured_x_cost_self_damage_effect</t>
+          <t>耗煞伤害</t>
         </is>
       </c>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>configured_x_cost_damage_effect</t>
-        </is>
-      </c>
+      <c r="M76" s="3" t="inlineStr"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="4" t="n"/>
@@ -5751,12 +5753,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>demon_bloodthirst</t>
+          <t>demon_shatter_soul_seal</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5766,7 +5768,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>嗜血成性</t>
+          <t>碎魂印</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5774,12 +5776,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -5794,17 +5796,25 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -5813,12 +5823,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_breath</t>
+          <t>demon_soul_devour_claw</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5828,7 +5838,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>焰息</t>
+          <t>噬魂爪</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -5836,17 +5846,17 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5856,20 +5866,20 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N78" s="4" t="n">
@@ -5883,12 +5893,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_continuity</t>
+          <t>demon_soul_lamp_renewal</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5898,20 +5908,20 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>焰心承续</t>
+          <t>魂灯续燃</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -5921,22 +5931,28 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_soul_mark_consume_effect</t>
         </is>
       </c>
       <c r="L79" s="4" t="n"/>
-      <c r="M79" s="3" t="inlineStr"/>
-      <c r="N79" s="4" t="n"/>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="3" t="inlineStr"/>
@@ -5945,12 +5961,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_refining</t>
+          <t>demon_strike</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5960,7 +5976,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>炼焰术</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -5968,17 +5984,17 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -5988,15 +6004,17 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="3" t="inlineStr"/>
@@ -6007,12 +6025,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_burn_sky</t>
+          <t>demon_blood_membrane</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6022,25 +6040,25 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>万魂焚天</t>
+          <t>血膜</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -6055,26 +6073,40 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="4" t="n"/>
-      <c r="O81" s="3" t="inlineStr"/>
-      <c r="P81" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q81" s="3" t="inlineStr"/>
       <c r="R81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_nurture</t>
+          <t>demon_blood_qi_guard</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6084,7 +6116,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>养煞</t>
+          <t>血气护体</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6112,7 +6144,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -6131,12 +6163,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_return</t>
+          <t>demon_blood_recompense</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6146,15 +6178,15 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>归煞</t>
+          <t>血偿万道</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6164,22 +6196,22 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>configured_consume_status_to_block_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L83" s="4" t="n"/>
@@ -6193,12 +6225,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_banner</t>
+          <t>demon_blood_sea_boundless</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6208,25 +6240,25 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>引魂幡</t>
+          <t>血海无量</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -6236,25 +6268,21 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_x_cost_self_damage_effect</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="n"/>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_x_cost_damage_effect</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="n"/>
       <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="3" t="inlineStr"/>
@@ -6263,12 +6291,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_echo</t>
+          <t>demon_bloodthirst</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6278,11 +6306,11 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>噬魂回响</t>
+          <t>嗜血成性</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
@@ -6296,7 +6324,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -6306,7 +6334,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
@@ -6325,12 +6353,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_flame_cycle</t>
+          <t>demon_flame_breath</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6340,7 +6368,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>魂火相济</t>
+          <t>焰息</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -6348,7 +6376,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6358,7 +6386,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -6368,17 +6396,25 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="3" t="inlineStr"/>
-      <c r="N86" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="3" t="inlineStr"/>
@@ -6387,12 +6423,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_mark_sense</t>
+          <t>demon_flame_continuity</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6402,7 +6438,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>魂印感应</t>
+          <t>焰心承续</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -6420,7 +6456,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -6449,12 +6485,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_rite</t>
+          <t>demon_flame_refining</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6464,7 +6500,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>夺魂仪</t>
+          <t>炼焰术</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -6482,7 +6518,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -6492,7 +6528,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -6511,12 +6547,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>forbidden_mantra</t>
+          <t>demon_myriad_soul_burn_sky</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6526,30 +6562,30 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>禁咒入魔</t>
+          <t>万魂焚天</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -6559,20 +6595,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="4" t="n"/>
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="3" t="inlineStr"/>
@@ -6581,12 +6609,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>hun_kai</t>
+          <t>demon_sha_nurture</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6596,7 +6624,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>魂铠</t>
+          <t>养煞</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -6604,12 +6632,12 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -6629,18 +6657,12 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L90" s="4" t="n"/>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v>8</v>
-      </c>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="4" t="n"/>
       <c r="O90" s="3" t="inlineStr"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="3" t="inlineStr"/>
@@ -6649,12 +6671,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>hun_zang</t>
+          <t>demon_sha_return</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6664,30 +6686,30 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>魂葬</t>
+          <t>归煞</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -6697,7 +6719,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_consume_status_to_block_effect</t>
         </is>
       </c>
       <c r="L91" s="4" t="n"/>
@@ -6711,12 +6733,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>ju_sha</t>
+          <t>demon_soul_banner</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6726,11 +6748,11 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>聚煞</t>
+          <t>引魂幡</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
@@ -6739,7 +6761,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -6759,19 +6781,19 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N92" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O92" s="3" t="inlineStr"/>
       <c r="P92" s="4" t="n"/>
@@ -6781,12 +6803,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>lie_hun</t>
+          <t>demon_soul_echo</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6796,25 +6818,25 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>裂魂</t>
+          <t>噬魂回响</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -6829,7 +6851,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L93" s="4" t="n"/>
@@ -6843,12 +6865,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>demon_black_contract</t>
+          <t>demon_soul_flame_cycle</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6858,7 +6880,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>黑契</t>
+          <t>魂火相济</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -6876,7 +6898,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -6891,20 +6913,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
-        </is>
-      </c>
-      <c r="N94" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="4" t="n"/>
       <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="3" t="inlineStr"/>
@@ -6913,12 +6927,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_oath</t>
+          <t>demon_soul_mark_sense</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6928,20 +6942,20 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>血誓</t>
+          <t>魂印感应</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -6956,25 +6970,17 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="4" t="n"/>
       <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="3" t="inlineStr"/>
@@ -6983,12 +6989,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea</t>
+          <t>demon_soul_rite</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -6998,20 +7004,20 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>血海翻涌</t>
+          <t>夺魂仪</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7026,25 +7032,17 @@
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N96" s="4" t="n">
-        <v>4</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="3" t="inlineStr"/>
+      <c r="N96" s="4" t="n"/>
       <c r="O96" s="3" t="inlineStr"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="3" t="inlineStr"/>
@@ -7053,12 +7051,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
+          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_self_heaven</t>
+          <t>forbidden_mantra</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7068,73 +7066,67 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>焚身问天</t>
+          <t>禁咒入魔</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>功法</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>暗金</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="O97" s="3" t="inlineStr"/>
+      <c r="P97" s="4" t="n"/>
       <c r="Q97" s="3" t="inlineStr"/>
       <c r="R97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>demon_cut_soul</t>
+          <t>hun_kai</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7144,7 +7136,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>割魂刃</t>
+          <t>魂铠</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7152,7 +7144,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -7172,24 +7164,22 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="n">
-        <v>6</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="n"/>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N98" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O98" s="3" t="inlineStr"/>
       <c r="P98" s="4" t="n"/>
@@ -7199,12 +7189,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_power</t>
+          <t>hun_zang</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7214,25 +7204,25 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>禁咒开脉</t>
+          <t>魂葬</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -7242,45 +7232,31 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P99" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="4" t="n"/>
       <c r="Q99" s="3" t="inlineStr"/>
       <c r="R99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
+          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>demon_ghost_hook</t>
+          <t>ju_sha</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7290,20 +7266,20 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>幽钩</t>
+          <t>聚煞</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7318,45 +7294,39 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(sha_qi)</t>
         </is>
       </c>
       <c r="N100" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O100" s="3" t="inlineStr"/>
+      <c r="P100" s="4" t="n"/>
       <c r="Q100" s="3" t="inlineStr"/>
       <c r="R100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>demon_hell_soul_seal</t>
+          <t>lie_hun</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7366,11 +7336,11 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>幽冥万魂印</t>
+          <t>裂魂</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
@@ -7379,12 +7349,12 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -7394,25 +7364,17 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N101" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="4" t="n"/>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="3" t="inlineStr"/>
@@ -7421,12 +7383,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>demon_hundred_ghosts</t>
+          <t>demon_black_contract</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7436,25 +7398,25 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>百鬼留痕</t>
+          <t>黑契</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -7469,15 +7431,15 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N102" s="4" t="n">
@@ -7491,12 +7453,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>demon_lantern_shadow</t>
+          <t>demon_blood_oath</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7506,15 +7468,15 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>灯影噬魂</t>
+          <t>血誓</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7543,11 +7505,11 @@
         </is>
       </c>
       <c r="L103" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N103" s="4" t="n">
@@ -7561,12 +7523,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>demon_life_for_mana</t>
+          <t>demon_blood_sea</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7576,25 +7538,25 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>命换灵机</t>
+          <t>血海翻涌</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -7604,16 +7566,16 @@
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7621,7 +7583,7 @@
         </is>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="4" t="n"/>
@@ -7631,12 +7593,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>demon_mark_bloom</t>
+          <t>demon_burn_self_heaven</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7646,67 +7608,73 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>印开彼岸</t>
+          <t>焚身问天</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>暗金</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="L105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N105" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O105" s="3" t="inlineStr"/>
-      <c r="P105" s="4" t="n"/>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q105" s="3" t="inlineStr"/>
       <c r="R105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>demon_sacrificial_flame</t>
+          <t>demon_cut_soul</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7716,7 +7684,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>祭焰</t>
+          <t>割魂刃</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -7729,7 +7697,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -7749,11 +7717,11 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7771,12 +7739,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_armor</t>
+          <t>demon_forbidden_power</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7786,7 +7754,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>魂衣</t>
+          <t>禁咒开脉</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
@@ -7804,7 +7772,7 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -7814,39 +7782,45 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N107" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" s="3" t="inlineStr"/>
-      <c r="P107" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q107" s="3" t="inlineStr"/>
       <c r="R107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_price</t>
+          <t>demon_ghost_hook</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7856,25 +7830,25 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>以魂为价</t>
+          <t>幽钩</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -7884,28 +7858,28 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="P108" s="4" t="n">
@@ -7917,12 +7891,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_prison</t>
+          <t>demon_hell_soul_seal</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7932,15 +7906,15 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>万魂牢</t>
+          <t>幽冥万魂印</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -7950,7 +7924,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -7960,19 +7934,25 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="L109" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M109" s="3" t="inlineStr"/>
-      <c r="N109" s="4" t="n"/>
+      <c r="N109" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O109" s="3" t="inlineStr"/>
       <c r="P109" s="4" t="n"/>
       <c r="Q109" s="3" t="inlineStr"/>
@@ -7981,12 +7961,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_siphon</t>
+          <t>demon_hundred_ghosts</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7996,11 +7976,11 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>摄魂归元</t>
+          <t>百鬼留痕</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
@@ -8009,7 +7989,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8024,7 +8004,7 @@
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -8033,36 +8013,30 @@
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N110" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O110" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O110" s="3" t="inlineStr"/>
+      <c r="P110" s="4" t="n"/>
       <c r="Q110" s="3" t="inlineStr"/>
       <c r="R110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_stamp</t>
+          <t>demon_lantern_shadow</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -8072,7 +8046,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>魂印</t>
+          <t>灯影噬魂</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -8080,7 +8054,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -8109,7 +8083,7 @@
         </is>
       </c>
       <c r="L111" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -8117,7 +8091,7 @@
         </is>
       </c>
       <c r="N111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="4" t="n"/>
@@ -8127,12 +8101,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>demon_spirit_net</t>
+          <t>demon_life_for_mana</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8142,11 +8116,11 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>缚魂网</t>
+          <t>命换灵机</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
@@ -8155,7 +8129,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8170,12 +8144,12 @@
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
@@ -8183,11 +8157,11 @@
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" s="3" t="inlineStr"/>
       <c r="P112" s="4" t="n"/>
@@ -8197,12 +8171,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>demon_ten_thousand_sacrifice</t>
+          <t>demon_mark_bloom</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8212,7 +8186,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>万祭归一</t>
+          <t>印开彼岸</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
@@ -8220,7 +8194,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -8230,34 +8204,34 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L113" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N113" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="4" t="n"/>
@@ -8267,12 +8241,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>san_hun_tong_fen</t>
+          <t>demon_sacrificial_flame</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8282,45 +8256,53 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>三魂同焚</t>
+          <t>祭焰</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="n"/>
-      <c r="M114" s="3" t="inlineStr"/>
-      <c r="N114" s="4" t="n"/>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="4" t="n"/>
       <c r="Q114" s="3" t="inlineStr"/>
@@ -8329,12 +8311,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>shadow_step</t>
+          <t>demon_soul_armor</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8344,11 +8326,11 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>影遁</t>
+          <t>魂衣</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -8362,29 +8344,35 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M115" s="3" t="inlineStr"/>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="4" t="n"/>
       <c r="Q115" s="3" t="inlineStr"/>
@@ -8393,12 +8381,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>she_hun_xu_yuan</t>
+          <t>demon_soul_price</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8408,20 +8396,20 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>摄魂续元</t>
+          <t>以魂为价</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -8436,26 +8424,28 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L116" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N116" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="P116" s="4" t="n">
@@ -8467,12 +8457,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>soul_drain</t>
+          <t>demon_soul_prison</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8482,25 +8472,25 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>摄魂</t>
+          <t>万魂牢</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -8510,45 +8500,33 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L117" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N117" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O117" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P117" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr"/>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="3" t="inlineStr"/>
+      <c r="P117" s="4" t="n"/>
       <c r="Q117" s="3" t="inlineStr"/>
       <c r="R117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>yin_sha_jue</t>
+          <t>demon_soul_siphon</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -8558,7 +8536,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>引煞诀</t>
+          <t>摄魂归元</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -8586,7 +8564,7 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
@@ -8595,40 +8573,46 @@
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N118" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O118" s="3" t="inlineStr"/>
-      <c r="P118" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P118" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q118" s="3" t="inlineStr"/>
       <c r="R118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>demon_soul_stamp</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>魂印</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -8656,7 +8640,7 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
@@ -8665,10 +8649,16 @@
         </is>
       </c>
       <c r="L119" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" s="3" t="inlineStr"/>
-      <c r="N119" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O119" s="3" t="inlineStr"/>
       <c r="P119" s="4" t="n"/>
       <c r="Q119" s="3" t="inlineStr"/>
@@ -8677,22 +8667,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>guard_sword</t>
+          <t>demon_spirit_net</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>御剑守心</t>
+          <t>缚魂网</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -8705,7 +8695,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -8720,20 +8710,20 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N120" s="4" t="n">
@@ -8747,67 +8737,67 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>sword_blade_embryo</t>
+          <t>demon_ten_thousand_sacrifice</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>剑胎初鸣</t>
+          <t>万祭归一</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N121" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="4" t="n"/>
@@ -8817,40 +8807,40 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
+          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>sword_breath_return</t>
+          <t>san_hun_tong_fen</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>回风纳息</t>
+          <t>三魂同焚</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -8860,25 +8850,17 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="L122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N122" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="3" t="inlineStr"/>
+      <c r="N122" s="4" t="n"/>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="3" t="inlineStr"/>
@@ -8887,68 +8869,62 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
+          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_cut</t>
+          <t>shadow_step</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>云隙递剑</t>
+          <t>影遁</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L123" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M123" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N123" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr"/>
+      <c r="N123" s="4" t="n"/>
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="4" t="n"/>
       <c r="Q123" s="3" t="inlineStr"/>
@@ -8957,22 +8933,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
+          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_scroll</t>
+          <t>she_hun_xu_yuan</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>云海剑书</t>
+          <t>摄魂续元</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -8985,7 +8961,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9000,43 +8976,53 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M124" s="3" t="inlineStr"/>
-      <c r="N124" s="4" t="n"/>
-      <c r="O124" s="3" t="inlineStr"/>
-      <c r="P124" s="4" t="n"/>
+      <c r="P124" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q124" s="3" t="inlineStr"/>
       <c r="R124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
+          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>sword_flow_shift</t>
+          <t>soul_drain</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>流光换形</t>
+          <t>摄魂</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -9044,17 +9030,17 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -9064,49 +9050,55 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
           <t>护体</t>
         </is>
       </c>
-      <c r="L125" s="4" t="n">
+      <c r="N125" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N125" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O125" s="3" t="inlineStr"/>
-      <c r="P125" s="4" t="n"/>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P125" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q125" s="3" t="inlineStr"/>
       <c r="R125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
+          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>sword_forge_spark</t>
+          <t>yin_sha_jue</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>炉火铸锋</t>
+          <t>引煞诀</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9114,17 +9106,17 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -9134,24 +9126,24 @@
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>状态(sha_qi)</t>
         </is>
       </c>
       <c r="N126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O126" s="3" t="inlineStr"/>
       <c r="P126" s="4" t="n"/>
@@ -9161,12 +9153,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
+          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>sword_furnace_open</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -9176,53 +9168,47 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>剑炉大开</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="4" t="n"/>
       <c r="O127" s="3" t="inlineStr"/>
       <c r="P127" s="4" t="n"/>
       <c r="Q127" s="3" t="inlineStr"/>
@@ -9231,12 +9217,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
+          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>sword_hidden_edge</t>
+          <t>guard_sword</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9246,7 +9232,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>藏锋式</t>
+          <t>御剑守心</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9279,14 +9265,20 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M128" s="3" t="inlineStr"/>
-      <c r="N128" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O128" s="3" t="inlineStr"/>
       <c r="P128" s="4" t="n"/>
       <c r="Q128" s="3" t="inlineStr"/>
@@ -9295,12 +9287,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>sword_hundred_forge</t>
+          <t>sword_blade_embryo</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9310,7 +9302,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>百炼锋芒</t>
+          <t>剑胎初鸣</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9318,7 +9310,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -9328,7 +9320,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -9338,19 +9330,25 @@
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M129" s="3" t="inlineStr"/>
-      <c r="N129" s="4" t="n"/>
+      <c r="N129" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="4" t="n"/>
       <c r="Q129" s="3" t="inlineStr"/>
@@ -9359,12 +9357,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>sword_iron_cleave</t>
+          <t>sword_breath_return</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9374,25 +9372,25 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>斩铁成锋</t>
+          <t>回风纳息</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
@@ -9402,23 +9400,25 @@
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N130" s="4" t="n"/>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O130" s="3" t="inlineStr"/>
       <c r="P130" s="4" t="n"/>
       <c r="Q130" s="3" t="inlineStr"/>
@@ -9427,12 +9427,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>sword_light_step</t>
+          <t>sword_cloud_cut</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9442,20 +9442,20 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>剑步轻灵</t>
+          <t>云隙递剑</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -9470,16 +9470,16 @@
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9497,12 +9497,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>sword_marrow_forge</t>
+          <t>sword_cloud_scroll</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>洗髓铸刃</t>
+          <t>云海剑书</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9545,20 +9545,14 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M132" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N132" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr"/>
+      <c r="N132" s="4" t="n"/>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="4" t="n"/>
       <c r="Q132" s="3" t="inlineStr"/>
@@ -9567,12 +9561,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>sword_probe_meridian</t>
+          <t>sword_flow_shift</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9582,7 +9576,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>剑影探脉</t>
+          <t>流光换形</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9590,17 +9584,17 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
@@ -9610,12 +9604,12 @@
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L133" s="4" t="n">
@@ -9627,28 +9621,22 @@
         </is>
       </c>
       <c r="N133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="P133" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O133" s="3" t="inlineStr"/>
+      <c r="P133" s="4" t="n"/>
       <c r="Q133" s="3" t="inlineStr"/>
       <c r="R133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>sword_ring_sheath</t>
+          <t>sword_forge_spark</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9658,7 +9646,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>剑鸣归鞘</t>
+          <t>炉火铸锋</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9676,7 +9664,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -9686,16 +9674,16 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9713,12 +9701,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>sword_sky_river</t>
+          <t>sword_furnace_open</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9728,7 +9716,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>天河倒卷</t>
+          <t>剑炉大开</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -9736,12 +9724,12 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -9756,24 +9744,24 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="4" t="n"/>
@@ -9783,12 +9771,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>sword_split_heaven</t>
+          <t>sword_hidden_edge</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9798,25 +9786,25 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>一剑开天</t>
+          <t>藏锋式</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -9831,17 +9819,13 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L136" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr"/>
       <c r="N136" s="4" t="n"/>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="4" t="n"/>
@@ -9851,12 +9835,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>sword_temper_edge</t>
+          <t>sword_hundred_forge</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9866,7 +9850,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>淬锋</t>
+          <t>百炼锋芒</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -9874,17 +9858,17 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -9899,17 +9883,13 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M137" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr"/>
       <c r="N137" s="4" t="n"/>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="4" t="n"/>
@@ -9919,12 +9899,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>sword_trial_edge</t>
+          <t>sword_iron_cleave</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9934,11 +9914,11 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>试锋</t>
+          <t>斩铁成锋</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
@@ -9952,7 +9932,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -9971,16 +9951,14 @@
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N138" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="n"/>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="4" t="n"/>
       <c r="Q138" s="3" t="inlineStr"/>
@@ -9989,12 +9967,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>sword_void_roam</t>
+          <t>sword_light_step</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -10004,25 +9982,25 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>太虚游剑</t>
+          <t>剑步轻灵</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -10032,16 +10010,16 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -10049,28 +10027,22 @@
         </is>
       </c>
       <c r="N139" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O139" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P139" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O139" s="3" t="inlineStr"/>
+      <c r="P139" s="4" t="n"/>
       <c r="Q139" s="3" t="inlineStr"/>
       <c r="R139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>sword_wash_blade</t>
+          <t>sword_marrow_forge</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -10080,7 +10052,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>洗剑诀</t>
+          <t>洗髓铸刃</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -10098,7 +10070,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -10113,14 +10085,20 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M140" s="3" t="inlineStr"/>
-      <c r="N140" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>状态(forge_sword)</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O140" s="3" t="inlineStr"/>
       <c r="P140" s="4" t="n"/>
       <c r="Q140" s="3" t="inlineStr"/>
@@ -10129,12 +10107,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>piercing_light</t>
+          <t>sword_probe_meridian</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -10144,11 +10122,11 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>一线天</t>
+          <t>剑影探脉</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
@@ -10162,7 +10140,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -10181,30 +10159,36 @@
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
           <t>状态(exposed)</t>
         </is>
       </c>
-      <c r="N141" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O141" s="3" t="inlineStr"/>
-      <c r="P141" s="4" t="n"/>
+      <c r="P141" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q141" s="3" t="inlineStr"/>
       <c r="R141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>sword_blood_curse</t>
+          <t>sword_ring_sheath</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10214,20 +10198,20 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>血祭剑咒</t>
+          <t>剑鸣归鞘</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -10247,40 +10231,34 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L142" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N142" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O142" s="3" t="inlineStr">
-        <is>
-          <t>状态(bleed)</t>
-        </is>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O142" s="3" t="inlineStr"/>
+      <c r="P142" s="4" t="n"/>
       <c r="Q142" s="3" t="inlineStr"/>
       <c r="R142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>sword_energy_charge</t>
+          <t>sword_sky_river</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10290,25 +10268,25 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>凝气术</t>
+          <t>天河倒卷</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -10318,24 +10296,24 @@
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>状态(energy_charge)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N143" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O143" s="3" t="inlineStr"/>
       <c r="P143" s="4" t="n"/>
@@ -10345,12 +10323,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>sword_guard_formation</t>
+          <t>sword_split_heaven</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10360,25 +10338,25 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>万剑护体</t>
+          <t>一剑开天</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -10393,13 +10371,17 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_guard)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M144" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
       <c r="N144" s="4" t="n"/>
       <c r="O144" s="3" t="inlineStr"/>
       <c r="P144" s="4" t="n"/>
@@ -10409,12 +10391,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>sword_heart</t>
+          <t>sword_temper_edge</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10424,7 +10406,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>剑心通明</t>
+          <t>淬锋</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
@@ -10432,17 +10414,17 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -10452,25 +10434,23 @@
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L145" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N145" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="n"/>
       <c r="O145" s="3" t="inlineStr"/>
       <c r="P145" s="4" t="n"/>
       <c r="Q145" s="3" t="inlineStr"/>
@@ -10479,12 +10459,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>sword_nurture</t>
+          <t>sword_trial_edge</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10494,7 +10474,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>养剑诀</t>
+          <t>试锋</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -10502,12 +10482,12 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -10527,14 +10507,20 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_intent)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L146" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M146" s="3" t="inlineStr"/>
-      <c r="N146" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>状态(forge_sword)</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O146" s="3" t="inlineStr"/>
       <c r="P146" s="4" t="n"/>
       <c r="Q146" s="3" t="inlineStr"/>
@@ -10543,12 +10529,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>sword_qi_draw</t>
+          <t>sword_void_roam</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10558,25 +10544,25 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>剑气引</t>
+          <t>太虚游剑</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -10591,34 +10577,40 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L147" s="4" t="n">
+      <c r="N147" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M147" s="3" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O147" s="3" t="inlineStr"/>
-      <c r="P147" s="4" t="n"/>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P147" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q147" s="3" t="inlineStr"/>
       <c r="R147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>sword_rain</t>
+          <t>sword_wash_blade</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10628,44 +10620,44 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>剑雨</t>
+          <t>洗剑诀</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L148" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="M148" s="3" t="inlineStr"/>
       <c r="N148" s="4" t="n"/>
@@ -10677,12 +10669,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
+          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>sword_shadow_strike</t>
+          <t>piercing_light</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10692,11 +10684,11 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>瞬影剑</t>
+          <t>一线天</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
@@ -10715,7 +10707,7 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -10729,15 +10721,15 @@
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N149" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="4" t="n"/>
@@ -10747,12 +10739,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
+          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>sword_star_shatter</t>
+          <t>sword_blood_curse</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10762,61 +10754,73 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>碎星斩</t>
+          <t>血祭剑咒</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>状态(bleed)</t>
+        </is>
+      </c>
+      <c r="P150" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>target_status_bonus_damage_effect</t>
-        </is>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M150" s="3" t="inlineStr"/>
-      <c r="N150" s="4" t="n"/>
-      <c r="O150" s="3" t="inlineStr"/>
-      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
+          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>sword_wanjian</t>
+          <t>sword_energy_charge</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10826,47 +10830,53 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>万剑归宗</t>
+          <t>凝气术</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>player_status_damage_effect</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L151" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M151" s="3" t="inlineStr"/>
-      <c r="N151" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>状态(energy_charge)</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O151" s="3" t="inlineStr"/>
       <c r="P151" s="4" t="n"/>
       <c r="Q151" s="3" t="inlineStr"/>
@@ -10875,12 +10885,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
+          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>sword_water_break</t>
+          <t>sword_guard_formation</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10890,7 +10900,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>断水剑</t>
+          <t>万剑护体</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
@@ -10898,12 +10908,12 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -10918,25 +10928,19 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(sword_guard)</t>
         </is>
       </c>
       <c r="L152" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M152" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr"/>
+      <c r="N152" s="4" t="n"/>
       <c r="O152" s="3" t="inlineStr"/>
       <c r="P152" s="4" t="n"/>
       <c r="Q152" s="3" t="inlineStr"/>
@@ -10945,12 +10949,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
+          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>sword_wind_return</t>
+          <t>sword_heart</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10960,7 +10964,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>回风剑</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
@@ -10968,17 +10972,17 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -10988,24 +10992,24 @@
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L153" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N153" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="4" t="n"/>
@@ -11015,22 +11019,22 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>sword_nurture</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>养剑诀</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -11058,16 +11062,16 @@
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(sword_intent)</t>
         </is>
       </c>
       <c r="L154" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M154" s="3" t="inlineStr"/>
       <c r="N154" s="4" t="n"/>
@@ -11079,40 +11083,40 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>sword_qi_draw</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>剑气引</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11122,20 +11126,20 @@
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L155" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="N155" s="4" t="n">
@@ -11149,26 +11153,26 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>sword_rain</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>剑雨</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
@@ -11177,7 +11181,7 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -11192,7 +11196,7 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -11201,16 +11205,10 @@
         </is>
       </c>
       <c r="L156" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M156" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N156" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr"/>
+      <c r="N156" s="4" t="n"/>
       <c r="O156" s="3" t="inlineStr"/>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="3" t="inlineStr"/>
@@ -11219,26 +11217,26 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>sword_shadow_strike</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>瞬影剑</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
@@ -11252,17 +11250,17 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -11271,10 +11269,16 @@
         </is>
       </c>
       <c r="L157" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M157" s="3" t="inlineStr"/>
-      <c r="N157" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O157" s="3" t="inlineStr"/>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="3" t="inlineStr"/>
@@ -11283,54 +11287,60 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>sword_star_shatter</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>碎星斩</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr"/>
-      <c r="L158" s="4" t="n"/>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>target_status_bonus_damage_effect</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="M158" s="3" t="inlineStr"/>
       <c r="N158" s="4" t="n"/>
       <c r="O158" s="3" t="inlineStr"/>
@@ -11341,26 +11351,26 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>sword_wanjian</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>万剑归宗</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
@@ -11374,7 +11384,7 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
@@ -11384,25 +11394,19 @@
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>player_status_damage_effect</t>
         </is>
       </c>
       <c r="L159" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M159" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N159" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="M159" s="3" t="inlineStr"/>
+      <c r="N159" s="4" t="n"/>
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="4" t="n"/>
       <c r="Q159" s="3" t="inlineStr"/>
@@ -11411,26 +11415,26 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>sword_water_break</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>断水剑</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
@@ -11454,7 +11458,7 @@
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -11463,15 +11467,15 @@
         </is>
       </c>
       <c r="L160" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N160" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="4" t="n"/>
@@ -11481,26 +11485,26 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>sword_wind_return</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>回风剑</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
@@ -11509,12 +11513,12 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -11524,7 +11528,7 @@
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -11533,15 +11537,15 @@
         </is>
       </c>
       <c r="L161" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N161" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="4" t="n"/>
@@ -11551,22 +11555,22 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -11574,17 +11578,17 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -11594,51 +11598,761 @@
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M162" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N162" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O162" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P162" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M162" s="3" t="inlineStr"/>
+      <c r="N162" s="4" t="n"/>
+      <c r="O162" s="3" t="inlineStr"/>
+      <c r="P162" s="4" t="n"/>
       <c r="Q162" s="3" t="inlineStr"/>
       <c r="R162" s="4" t="n"/>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/ink_flow_slash.tres</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>ink_flow_slash</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>墨流斩</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" s="3" t="inlineStr"/>
+      <c r="P163" s="4" t="n"/>
+      <c r="Q163" s="3" t="inlineStr"/>
+      <c r="R163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/muscle_resonance_strike.tres</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>muscle_resonance_strike</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>劲气共鸣</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" s="3" t="inlineStr"/>
+      <c r="P164" s="4" t="n"/>
+      <c r="Q164" s="3" t="inlineStr"/>
+      <c r="R164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/status/eclipse_scar.tres</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>eclipse_scar</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>蚀痕</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr"/>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="3" t="inlineStr"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="3" t="inlineStr"/>
+      <c r="P165" s="4" t="n"/>
+      <c r="Q165" s="3" t="inlineStr"/>
+      <c r="R165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/status/heart_demon.tres</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>heart_demon</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>心魔</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr"/>
+      <c r="L166" s="4" t="n"/>
+      <c r="M166" s="3" t="inlineStr"/>
+      <c r="N166" s="4" t="n"/>
+      <c r="O166" s="3" t="inlineStr"/>
+      <c r="P166" s="4" t="n"/>
+      <c r="Q166" s="3" t="inlineStr"/>
+      <c r="R166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/status/underworld_writ.tres</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>underworld_writ</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>判牒</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
+      <c r="L167" s="4" t="n"/>
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="3" t="inlineStr"/>
+      <c r="P167" s="4" t="n"/>
+      <c r="Q167" s="3" t="inlineStr"/>
+      <c r="R167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/strike.tres</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>strike</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>打击</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr"/>
+      <c r="N168" s="4" t="n"/>
+      <c r="O168" s="3" t="inlineStr"/>
+      <c r="P168" s="4" t="n"/>
+      <c r="Q168" s="3" t="inlineStr"/>
+      <c r="R168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/toxin.tres</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>toxin</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>浊气</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr"/>
+      <c r="L169" s="4" t="n"/>
+      <c r="M169" s="3" t="inlineStr"/>
+      <c r="N169" s="4" t="n"/>
+      <c r="O169" s="3" t="inlineStr"/>
+      <c r="P169" s="4" t="n"/>
+      <c r="Q169" s="3" t="inlineStr"/>
+      <c r="R169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/attack_guard_unity.tres</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>attack_guard_unity</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>攻守合一</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O170" s="3" t="inlineStr"/>
+      <c r="P170" s="4" t="n"/>
+      <c r="Q170" s="3" t="inlineStr"/>
+      <c r="R170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/blood_beast_rend.tres</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>blood_beast_rend</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>血兽撕咬</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" s="3" t="inlineStr"/>
+      <c r="P171" s="4" t="n"/>
+      <c r="Q171" s="3" t="inlineStr"/>
+      <c r="R171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>demon_rain_swordfire</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>魔雨剑火</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" s="3" t="inlineStr"/>
+      <c r="P172" s="4" t="n"/>
+      <c r="Q172" s="3" t="inlineStr"/>
+      <c r="R172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L173" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q173" s="3" t="inlineStr"/>
+      <c r="R173" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11749,7 +12463,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>最大生命 +10，并回复 10 点生命。</t>
+          <t>最大生命 +10。</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -11829,7 +12543,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>获得 90 灵石。</t>
+          <t>获得 100 灵石。</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -11844,7 +12558,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="n"/>
@@ -11864,27 +12578,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>气海拓宽</t>
+          <t>丹炉馈赠</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>最大法力 +1。</t>
+          <t>获得 2 个随机符箓丹药。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>potion</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>gain_potion</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="n"/>
@@ -11904,67 +12618,73 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>灵光启智</t>
+          <t>行脚盘缠</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>每回合抽牌数 +1。</t>
+          <t>获得 60 灵石与 1 个随机符箓丹药。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>potion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>gain_potion</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>灵脉余泽</t>
+          <t>补天盟密阵</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>劫尘之下残存的灵脉余泽，稳住入墟者根基。</t>
+          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>旧术点化</t>
+          <t>炼魂阵·焚</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>随机突破一张可突破卡牌。</t>
+          <t>移除两张打击或防御。</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>remove_card</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>remove_strike_defend</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="n"/>
@@ -11974,355 +12694,343 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>残仙遗蜕</t>
+          <t>补天盟密阵</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
+          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>残魂灌体</t>
+          <t>淬炼阵·升</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>最大法力 +1；但最大生命 -10。</t>
+          <t>随机突破两张卡牌。</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>lose_max_health</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>残仙遗蜕</t>
+          <t>补天盟密阵</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
+          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>枯荣逆转</t>
+          <t>衍法阵·启</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>最大生命 +18 并回满；但失去 80 灵石。</t>
+          <t>获得两张随机职业术法。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>duplicate_card</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>add_random_cards</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>full_heal</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>lose_gold</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>80</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>残仙遗蜕</t>
+          <t>补天盟密阵</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
+          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>嗜血淬炼</t>
+          <t>夺天阵·稀</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>随机突破 2 张牌；但最大生命 -8。</t>
+          <t>获得一张随机金卡术法。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>rare_card</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>add_random_rare_card</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>lose_max_health</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>残仙遗蜕</t>
+          <t>补天盟密阵</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
+          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>鬻命求财</t>
+          <t>蜕形阵·换</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>获得 160 灵石；但最大生命 -14。</t>
+          <t>两张打击或防御蜕变为随机职业术法。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>duplicate_card</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>transform_card</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>lose_max_health</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>14</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>补天盟密阵</t>
+          <t>残仙遗蜕</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
+          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>炼魂阵·焚</t>
+          <t>残魂灌体</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>移除牌组中随机 1 张牌。</t>
+          <t>最大法力 +1；但最大生命 -12。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>remove_card</t>
+          <t>max_mana</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>remove_card</t>
+          <t>max_mana</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>补天盟密阵</t>
+          <t>残仙遗蜕</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
+          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>复刻阵·衍</t>
+          <t>嗜血淬炼</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>复制牌组中随机 1 张牌。</t>
+          <t>随机突破三张卡牌；但最大生命 -30。</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>duplicate_card</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>duplicate_card</t>
+          <t>upgrade</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>补天盟密阵</t>
+          <t>残仙遗蜕</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
+          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>淬炼大阵</t>
+          <t>鬻命求财</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>随机突破 2 张牌。</t>
+          <t>获得 170 灵石；但最大生命 -12。</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="n"/>
+        <v>170</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>补天盟密阵</t>
+          <t>残仙遗蜕</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>补天盟遗下的炼魂大阵，重塑你的命牌。</t>
+          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>拆解重组</t>
+          <t>蜕骨夺珍</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>移除随机 1 张牌，并获得 70 灵石。</t>
+          <t>获得两张随机金卡术法；但最大生命 -14。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>remove_card</t>
+          <t>rare_card</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>remove_card</t>
+          <t>add_random_rare_card</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>lose_max_health</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="n"/>
@@ -12330,40 +13038,46 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>照命石审判</t>
+          <t>残仙遗蜕</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>照命石映出你的命格，或赐法宝，或索取代价。</t>
+          <t>飞升失败者的残魂附蜕，予你力量，也予你劫。</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>命石垂赐</t>
+          <t>燃脉借力</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>获得 1 件随机法宝。</t>
+          <t>每回合抽牌数 +1；但最大生命 -20。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>relic</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>grant_relic</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="n"/>
     </row>
@@ -12375,41 +13089,35 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>照命石映出你的命格，或赐法宝，或索取代价。</t>
+          <t>照命石映出你的命格，或赐机缘，或索代价。</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>富贵险中</t>
+          <t>命石垂赐</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>获得 180 灵石；但最大生命 -10。</t>
+          <t>获得一件随机法宝。</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>grant_relic</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>lose_max_health</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="n"/>
     </row>
@@ -12421,41 +13129,35 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>照命石映出你的命格，或赐法宝，或索取代价。</t>
+          <t>照命石映出你的命格，或赐机缘，或索代价。</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>舍身得宝</t>
+          <t>破劫之印</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>获得 1 件随机法宝；但最大生命 -12。</t>
+          <t>接下来 3 场战斗，敌人以七成气血入场。</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>relic</t>
+          <t>seal</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>grant_relic</t>
+          <t>weaken_next_battles</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>lose_max_health</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>12</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="n"/>
     </row>
@@ -12467,28 +13169,28 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>照命石映出你的命格，或赐法宝，或索取代价。</t>
+          <t>照命石映出你的命格，或赐机缘，或索代价。</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>照命满血</t>
+          <t>孤注一掷</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>回复至满生命，并获得 50 灵石。</t>
+          <t>散尽全部灵石，换一件法宝与一张金卡术法。</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>full_heal</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>full_heal</t>
+          <t>lose_all_gold</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -12496,53 +13198,55 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>grant_relic</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>add_random_rare_card</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>命格共鸣</t>
+          <t>照命石审判</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>你的命格与劫域共鸣，唤出专属之力。</t>
+          <t>照命石映出你的命格，或赐机缘，或索代价。</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>魂祭·以命</t>
+          <t>舍身得宝</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>最大法力 +1；但最大生命 -8。</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>demonic</t>
-        </is>
-      </c>
+          <t>获得两件随机法宝；但最大生命 -16。</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>max_mana</t>
+          <t>grant_relic</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -12550,7 +13254,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="n"/>
@@ -12558,44 +13262,46 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>命格共鸣</t>
+          <t>照命石审判</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>你的命格与劫域共鸣，唤出专属之力。</t>
+          <t>照命石映出你的命格，或赐机缘，或索代价。</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>煞海之躯</t>
+          <t>富贵险中</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>最大生命 +24 并回复同等生命。</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>demonic</t>
-        </is>
-      </c>
+          <t>获得 250 灵石；但最大生命 -20。</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="n"/>
+        <v>250</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="n"/>
     </row>
@@ -12612,34 +13318,40 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>剑骨通玄</t>
+          <t>魂祭·以命</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>每回合抽牌数 +1。</t>
+          <t>最大法力 +1；但最大生命 -18。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>demonic</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>max_mana</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>max_mana</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="n"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>lose_max_health</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="n"/>
     </row>
@@ -12656,34 +13368,40 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>千锤百炼</t>
+          <t>血劫同源</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>随机突破 2 张牌。</t>
+          <t>最大生命 +15，并获得 1 个随机符箓丹药。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>demonic</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>max_health</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>upgrade</t>
+          <t>max_health</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>gain_potion</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="n"/>
     </row>
@@ -12700,31 +13418,31 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>金身不坏</t>
+          <t>剑骨通玄</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>最大生命 +30 并回复同等生命。</t>
+          <t>每回合抽牌数 +1。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="n"/>
@@ -12744,31 +13462,31 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>万兽来财</t>
+          <t>金身不坏</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>获得 120 灵石。</t>
+          <t>最大生命 +30。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>beastmaster</t>
+          <t>body</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>max_health</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>max_health</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="n"/>
@@ -12788,27 +13506,31 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>命途加身</t>
+          <t>万兽来财</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>最大生命 +12 并回复同等生命。</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>获得 120 灵石。</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>beastmaster</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>max_health</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="n"/>
@@ -12824,13 +13546,13 @@
       <formula1>"max_health,full_heal,gold,max_mana,draw,upgrade,remove_card,duplicate_card,relic"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,max_mana,draw,upgrade,remove_card,duplicate_card,grant_relic"</formula1>
+      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,lose_all_gold,max_mana,draw,upgrade,remove_card,remove_strike_defend,duplicate_card,add_random_cards,add_random_rare_card,transform_card,grant_relic,gain_potion,weaken_next_battles"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,max_mana,draw,upgrade,remove_card,duplicate_card,grant_relic"</formula1>
+      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,lose_all_gold,max_mana,draw,upgrade,remove_card,remove_strike_defend,duplicate_card,add_random_cards,add_random_rare_card,transform_card,grant_relic,gain_potion,weaken_next_battles"</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,max_mana,draw,upgrade,remove_card,duplicate_card,grant_relic"</formula1>
+      <formula1>",max_health,lose_max_health,full_heal,gold,lose_gold,lose_all_gold,max_mana,draw,upgrade,remove_card,remove_strike_defend,duplicate_card,add_random_cards,add_random_rare_card,transform_card,grant_relic,gain_potion,weaken_next_battles"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12908,7 +13630,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -12938,7 +13660,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
     </row>
@@ -12964,7 +13686,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -12994,7 +13716,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
     </row>
@@ -13020,7 +13742,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -13050,7 +13772,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
     </row>
@@ -13076,7 +13798,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
     </row>
@@ -13102,7 +13824,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -13132,7 +13854,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
     </row>
@@ -13158,7 +13880,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
     </row>
@@ -13184,7 +13906,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
     </row>
@@ -13256,7 +13978,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   效果类型: max_health / lose_max_health / full_heal / gold / lose_gold / max_mana / draw / upgrade / remove_card / duplicate_card / grant_relic</t>
+          <t xml:space="preserve">   效果类型: max_health / lose_max_health / full_heal / gold / lose_gold / lose_all_gold / max_mana / draw / upgrade / remove_card / remove_strike_defend / duplicate_card / add_random_cards / add_random_rare_card / transform_card / grant_relic / gain_potion / weaken_next_battles</t>
         </is>
       </c>
     </row>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
@@ -5953,8 +5953,14 @@
       <c r="N79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O79" s="3" t="inlineStr"/>
-      <c r="P79" s="4" t="n"/>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q79" s="3" t="inlineStr"/>
       <c r="R79" s="4" t="n"/>
     </row>
@@ -8888,7 +8894,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
@@ -8917,7 +8923,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>牌堆检索</t>
         </is>
       </c>
       <c r="L123" s="4" t="n">

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -5402,12 +5402,12 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -5423,8 +5423,14 @@
       <c r="L71" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="4" t="n"/>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="3" t="inlineStr"/>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -6056,11 +6056,11 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -6101,12 +6101,10 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="3" t="inlineStr"/>
       <c r="R81" s="4" t="n"/>
     </row>
@@ -6735,8 +6733,14 @@
         </is>
       </c>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="3" t="inlineStr"/>
-      <c r="N91" s="4" t="n"/>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="3" t="inlineStr"/>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R173"/>
+  <dimension ref="A1:R175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11775,12 +11775,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -11821,8 +11821,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="4" t="n"/>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="4" t="n"/>
       <c r="O165" s="3" t="inlineStr"/>
@@ -11833,12 +11839,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11848,7 +11854,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -11891,12 +11897,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11906,7 +11912,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -11949,12 +11955,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>karmic_fire_curse</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11964,7 +11970,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -11972,12 +11978,12 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -11987,7 +11993,7 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -11997,11 +12003,11 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L168" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M168" s="3" t="inlineStr"/>
       <c r="N168" s="4" t="n"/>
@@ -12013,12 +12019,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/status/underworld_writ.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>underworld_writ</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12028,11 +12034,11 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>判牒</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
@@ -12051,7 +12057,7 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -12071,22 +12077,22 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/strike.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>strike</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12104,7 +12110,7 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -12125,14 +12131,8 @@
       <c r="L170" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M170" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N170" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="M170" s="3" t="inlineStr"/>
+      <c r="N170" s="4" t="n"/>
       <c r="O170" s="3" t="inlineStr"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="3" t="inlineStr"/>
@@ -12141,22 +12141,22 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>common_cards/toxin.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12164,45 +12164,33 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M171" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr"/>
+      <c r="L171" s="4" t="n"/>
+      <c r="M171" s="3" t="inlineStr"/>
+      <c r="N171" s="4" t="n"/>
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -12211,12 +12199,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>fusion_cards/attack_guard_unity.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>attack_guard_unity</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12226,11 +12214,11 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>攻守合一</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
@@ -12239,12 +12227,12 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -12254,7 +12242,7 @@
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
@@ -12263,15 +12251,15 @@
         </is>
       </c>
       <c r="L172" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N172" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O172" s="3" t="inlineStr"/>
       <c r="P172" s="4" t="n"/>
@@ -12281,12 +12269,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>fusion_cards/blood_beast_rend.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>blood_beast_rend</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -12296,7 +12284,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>血兽撕咬</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12324,7 +12312,7 @@
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
@@ -12333,42 +12321,182 @@
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N173" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O173" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P173" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O173" s="3" t="inlineStr"/>
+      <c r="P173" s="4" t="n"/>
       <c r="Q173" s="3" t="inlineStr"/>
       <c r="R173" s="4" t="n"/>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>demon_rain_swordfire</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>魔雨剑火</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" s="3" t="inlineStr"/>
+      <c r="P174" s="4" t="n"/>
+      <c r="Q174" s="3" t="inlineStr"/>
+      <c r="R174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q175" s="3" t="inlineStr"/>
+      <c r="R175" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -8025,12 +8025,10 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L110" s="4" t="n">
-        <v>4</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="n"/>
       <c r="M110" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
@@ -8801,11 +8799,11 @@
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R175"/>
+  <dimension ref="A1:R183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11569,12 +11569,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>common_cards/ash_heart_guard.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>ash_heart_guard</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>灰烬护心</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -11617,11 +11617,11 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M162" s="3" t="inlineStr"/>
       <c r="N162" s="4" t="n"/>
@@ -11633,12 +11633,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>common_cards/circulating_breath.tres</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>circulating_breath</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>周天吐纳</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L163" s="4" t="n">
@@ -11703,12 +11703,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -11751,20 +11751,14 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L164" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M164" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr"/>
+      <c r="N164" s="4" t="n"/>
       <c r="O164" s="3" t="inlineStr"/>
       <c r="P164" s="4" t="n"/>
       <c r="Q164" s="3" t="inlineStr"/>
@@ -11773,12 +11767,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/blood_debt_curse.tres</t>
+          <t>common_cards/discard_aegis.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>blood_debt_curse</t>
+          <t>discard_aegis</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11788,11 +11782,11 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>血债</t>
+          <t>弃念成罡</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
@@ -11806,7 +11800,7 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -11821,11 +11815,11 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L165" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="4" t="n"/>
@@ -11837,12 +11831,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/embers_return.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>embers_return</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11852,11 +11846,11 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>烬归灵台</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
@@ -11870,12 +11864,12 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -11883,10 +11877,22 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K166" s="3" t="inlineStr"/>
-      <c r="L166" s="4" t="n"/>
-      <c r="M166" s="3" t="inlineStr"/>
-      <c r="N166" s="4" t="n"/>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O166" s="3" t="inlineStr"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="3" t="inlineStr"/>
@@ -11895,12 +11901,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/flowing_cloud_guard.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>flowing_cloud_guard</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11910,11 +11916,11 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>流云护身</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
@@ -11928,7 +11934,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -11941,7 +11947,11 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K167" s="3" t="inlineStr"/>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>计数增幅</t>
+        </is>
+      </c>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="3" t="inlineStr"/>
       <c r="N167" s="4" t="n"/>
@@ -11953,12 +11963,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/karmic_fire_curse.tres</t>
+          <t>common_cards/ink_flow_slash.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>karmic_fire_curse</t>
+          <t>ink_flow_slash</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11968,7 +11978,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>墨流斩</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -11976,12 +11986,12 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -11991,7 +12001,7 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -12001,14 +12011,20 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L168" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M168" s="3" t="inlineStr"/>
-      <c r="N168" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O168" s="3" t="inlineStr"/>
       <c r="P168" s="4" t="n"/>
       <c r="Q168" s="3" t="inlineStr"/>
@@ -12017,12 +12033,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/momentum_pursuit.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>momentum_pursuit</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12032,25 +12048,25 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>乘势追击</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -12063,8 +12079,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K169" s="3" t="inlineStr"/>
-      <c r="L169" s="4" t="n"/>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M169" s="3" t="inlineStr"/>
       <c r="N169" s="4" t="n"/>
       <c r="O169" s="3" t="inlineStr"/>
@@ -12075,12 +12097,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/muscle_resonance_strike.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>muscle_resonance_strike</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12090,7 +12112,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>劲气共鸣</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12127,10 +12149,16 @@
         </is>
       </c>
       <c r="L170" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M170" s="3" t="inlineStr"/>
-      <c r="N170" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="O170" s="3" t="inlineStr"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="3" t="inlineStr"/>
@@ -12139,12 +12167,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/returning_light.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>returning_light</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -12154,7 +12182,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>回光返照</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12172,7 +12200,7 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
@@ -12185,8 +12213,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="4" t="n"/>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="4" t="n"/>
       <c r="O171" s="3" t="inlineStr"/>
@@ -12197,26 +12231,26 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/spirit_stone_needle.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>spirit_stone_needle</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>灵石飞针</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
@@ -12230,12 +12264,12 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -12249,16 +12283,10 @@
         </is>
       </c>
       <c r="L172" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M172" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="n">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr"/>
+      <c r="N172" s="4" t="n"/>
       <c r="O172" s="3" t="inlineStr"/>
       <c r="P172" s="4" t="n"/>
       <c r="Q172" s="3" t="inlineStr"/>
@@ -12267,40 +12295,40 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -12310,25 +12338,19 @@
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M173" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N173" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="M173" s="3" t="inlineStr"/>
+      <c r="N173" s="4" t="n"/>
       <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -12337,40 +12359,40 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
@@ -12380,25 +12402,13 @@
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L174" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M174" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N174" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="3" t="inlineStr"/>
+      <c r="N174" s="4" t="n"/>
       <c r="O174" s="3" t="inlineStr"/>
       <c r="P174" s="4" t="n"/>
       <c r="Q174" s="3" t="inlineStr"/>
@@ -12407,40 +12417,40 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -12450,51 +12460,563 @@
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M175" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N175" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O175" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P175" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr"/>
+      <c r="L175" s="4" t="n"/>
+      <c r="M175" s="3" t="inlineStr"/>
+      <c r="N175" s="4" t="n"/>
+      <c r="O175" s="3" t="inlineStr"/>
+      <c r="P175" s="4" t="n"/>
       <c r="Q175" s="3" t="inlineStr"/>
       <c r="R175" s="4" t="n"/>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>karmic_fire_curse</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>业火</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr"/>
+      <c r="N176" s="4" t="n"/>
+      <c r="O176" s="3" t="inlineStr"/>
+      <c r="P176" s="4" t="n"/>
+      <c r="Q176" s="3" t="inlineStr"/>
+      <c r="R176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/status/underworld_writ.tres</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>underworld_writ</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>判牒</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr"/>
+      <c r="L177" s="4" t="n"/>
+      <c r="M177" s="3" t="inlineStr"/>
+      <c r="N177" s="4" t="n"/>
+      <c r="O177" s="3" t="inlineStr"/>
+      <c r="P177" s="4" t="n"/>
+      <c r="Q177" s="3" t="inlineStr"/>
+      <c r="R177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/strike.tres</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>strike</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>打击</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr"/>
+      <c r="N178" s="4" t="n"/>
+      <c r="O178" s="3" t="inlineStr"/>
+      <c r="P178" s="4" t="n"/>
+      <c r="Q178" s="3" t="inlineStr"/>
+      <c r="R178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>common_cards/toxin.tres</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>toxin</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>浊气</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="3" t="inlineStr"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="3" t="inlineStr"/>
+      <c r="P179" s="4" t="n"/>
+      <c r="Q179" s="3" t="inlineStr"/>
+      <c r="R179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/attack_guard_unity.tres</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>attack_guard_unity</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>攻守合一</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O180" s="3" t="inlineStr"/>
+      <c r="P180" s="4" t="n"/>
+      <c r="Q180" s="3" t="inlineStr"/>
+      <c r="R180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/blood_beast_rend.tres</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>blood_beast_rend</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>血兽撕咬</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O181" s="3" t="inlineStr"/>
+      <c r="P181" s="4" t="n"/>
+      <c r="Q181" s="3" t="inlineStr"/>
+      <c r="R181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>demon_rain_swordfire</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>魔雨剑火</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" s="3" t="inlineStr"/>
+      <c r="P182" s="4" t="n"/>
+      <c r="Q182" s="3" t="inlineStr"/>
+      <c r="R182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q183" s="3" t="inlineStr"/>
+      <c r="R183" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R183"/>
+  <dimension ref="A1:R184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5759,12 +5759,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>demon_shatter_soul_seal</t>
+          <t>demon_shadow_reenactment</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>碎魂印</t>
+          <t>魔影复刻</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5787,40 +5787,32 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>复刻</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="4" t="n"/>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -5829,12 +5821,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_devour_claw</t>
+          <t>demon_shatter_soul_seal</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5844,7 +5836,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>噬魂爪</t>
+          <t>碎魂印</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -5852,7 +5844,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5862,7 +5854,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5872,7 +5864,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -5881,7 +5873,7 @@
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5889,7 +5881,7 @@
         </is>
       </c>
       <c r="N78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="4" t="n"/>
@@ -5899,12 +5891,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_lamp_renewal</t>
+          <t>demon_soul_devour_claw</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>魂灯续燃</t>
+          <t>噬魂爪</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -5922,7 +5914,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5932,12 +5924,12 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5947,38 +5939,34 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="3" t="inlineStr"/>
       <c r="R79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>demon_strike</t>
+          <t>demon_soul_lamp_renewal</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5988,7 +5976,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>魂灯续燃</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -5996,7 +5984,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6006,43 +5994,53 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M80" s="3" t="inlineStr"/>
-      <c r="N80" s="4" t="n"/>
-      <c r="O80" s="3" t="inlineStr"/>
-      <c r="P80" s="4" t="n"/>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q80" s="3" t="inlineStr"/>
       <c r="R80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_membrane</t>
+          <t>demon_strike</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6052,7 +6050,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>血膜</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6060,17 +6058,17 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -6080,30 +6078,20 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N81" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="3" t="inlineStr"/>
       <c r="R81" s="4" t="n"/>
@@ -6111,12 +6099,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_qi_guard</t>
+          <t>demon_blood_membrane</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6126,7 +6114,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>血气护体</t>
+          <t>血膜</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6144,7 +6132,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -6159,13 +6147,25 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
           <t>configured_demonic_engine_effect</t>
         </is>
       </c>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="4" t="n"/>
-      <c r="O82" s="3" t="inlineStr"/>
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="3" t="inlineStr"/>
       <c r="R82" s="4" t="n"/>
@@ -6173,12 +6173,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_recompense</t>
+          <t>demon_blood_qi_guard</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6188,11 +6188,11 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>血偿万道</t>
+          <t>血气护体</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -6235,12 +6235,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_boundless</t>
+          <t>demon_blood_recompense</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6250,20 +6250,20 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>血海无量</t>
+          <t>血偿万道</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6283,15 +6283,11 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>configured_x_cost_self_damage_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L84" s="4" t="n"/>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>configured_x_cost_damage_effect</t>
-        </is>
-      </c>
+      <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="4" t="n"/>
@@ -6301,12 +6297,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>demon_bloodthirst</t>
+          <t>demon_blood_sea_boundless</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6316,25 +6312,25 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>嗜血成性</t>
+          <t>血海无量</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -6349,11 +6345,15 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_x_cost_self_damage_effect</t>
         </is>
       </c>
       <c r="L85" s="4" t="n"/>
-      <c r="M85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>configured_x_cost_damage_effect</t>
+        </is>
+      </c>
       <c r="N85" s="4" t="n"/>
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="4" t="n"/>
@@ -6363,12 +6363,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_breath</t>
+          <t>demon_bloodthirst</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>焰息</t>
+          <t>嗜血成性</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6406,25 +6406,17 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="4" t="n"/>
       <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="3" t="inlineStr"/>
@@ -6433,12 +6425,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_continuity</t>
+          <t>demon_flame_breath</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6448,7 +6440,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>焰心承续</t>
+          <t>焰息</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -6456,7 +6448,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -6481,12 +6473,20 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L87" s="4" t="n"/>
-      <c r="M87" s="3" t="inlineStr"/>
-      <c r="N87" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="3" t="inlineStr"/>
@@ -6495,12 +6495,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_refining</t>
+          <t>demon_flame_continuity</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>炼焰术</t>
+          <t>焰心承续</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -6557,12 +6557,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_burn_sky</t>
+          <t>demon_flame_refining</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6572,30 +6572,30 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>万魂焚天</t>
+          <t>炼焰术</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L89" s="4" t="n"/>
@@ -6619,12 +6619,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_nurture</t>
+          <t>demon_myriad_soul_burn_sky</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6634,40 +6634,40 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>养煞</t>
+          <t>万魂焚天</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L90" s="4" t="n"/>
@@ -6681,12 +6681,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_return</t>
+          <t>demon_sha_nurture</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6696,15 +6696,15 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>归煞</t>
+          <t>养煞</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -6729,18 +6729,12 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>configured_consume_status_to_block_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L91" s="4" t="n"/>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="4" t="n"/>
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="3" t="inlineStr"/>
@@ -6749,12 +6743,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_banner</t>
+          <t>demon_sha_return</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6764,11 +6758,11 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>引魂幡</t>
+          <t>归煞</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
@@ -6777,17 +6771,17 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -6797,15 +6791,13 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_consume_status_to_block_effect</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="n"/>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N92" s="4" t="n">
@@ -6819,12 +6811,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_echo</t>
+          <t>demon_soul_banner</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6834,45 +6826,53 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>噬魂回响</t>
+          <t>引魂幡</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>暗金</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="n"/>
-      <c r="M93" s="3" t="inlineStr"/>
-      <c r="N93" s="4" t="n"/>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="3" t="inlineStr"/>
@@ -6881,12 +6881,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_flame_cycle</t>
+          <t>demon_soul_echo</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6896,11 +6896,11 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>魂火相济</t>
+          <t>噬魂回响</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -6943,12 +6943,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_mark_sense</t>
+          <t>demon_soul_flame_cycle</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>魂印感应</t>
+          <t>魂火相济</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
@@ -7005,12 +7005,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_rite</t>
+          <t>demon_soul_mark_sense</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>夺魂仪</t>
+          <t>魂印感应</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -7067,12 +7067,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>forbidden_mantra</t>
+          <t>demon_soul_rite</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>禁咒入魔</t>
+          <t>夺魂仪</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -7110,25 +7110,17 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="3" t="inlineStr"/>
+      <c r="N97" s="4" t="n"/>
       <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="3" t="inlineStr"/>
@@ -7137,12 +7129,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
+          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>hun_kai</t>
+          <t>forbidden_mantra</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7152,7 +7144,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>魂铠</t>
+          <t>禁咒入魔</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7160,17 +7152,17 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -7180,22 +7172,24 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N98" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O98" s="3" t="inlineStr"/>
       <c r="P98" s="4" t="n"/>
@@ -7205,12 +7199,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>hun_zang</t>
+          <t>hun_kai</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7220,15 +7214,15 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>魂葬</t>
+          <t>魂铠</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -7238,7 +7232,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -7253,12 +7247,18 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_soul_mark_consume_effect</t>
         </is>
       </c>
       <c r="L99" s="4" t="n"/>
-      <c r="M99" s="3" t="inlineStr"/>
-      <c r="N99" s="4" t="n"/>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="4" t="n"/>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -7267,12 +7267,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>ju_sha</t>
+          <t>hun_zang</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7282,25 +7282,25 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>聚煞</t>
+          <t>魂葬</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -7315,20 +7315,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>状态(sha_qi)</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="3" t="inlineStr"/>
+      <c r="N100" s="4" t="n"/>
       <c r="O100" s="3" t="inlineStr"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="3" t="inlineStr"/>
@@ -7337,12 +7329,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
+          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>lie_hun</t>
+          <t>ju_sha</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7352,20 +7344,20 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>裂魂</t>
+          <t>聚煞</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7385,12 +7377,20 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="3" t="inlineStr"/>
-      <c r="N101" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="3" t="inlineStr"/>
@@ -7399,12 +7399,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
+          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>demon_black_contract</t>
+          <t>lie_hun</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>黑契</t>
+          <t>裂魂</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -7442,25 +7442,17 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L102" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
-        </is>
-      </c>
-      <c r="N102" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="3" t="inlineStr"/>
+      <c r="N102" s="4" t="n"/>
       <c r="O102" s="3" t="inlineStr"/>
       <c r="P102" s="4" t="n"/>
       <c r="Q102" s="3" t="inlineStr"/>
@@ -7469,12 +7461,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_oath</t>
+          <t>demon_black_contract</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7484,20 +7476,20 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>血誓</t>
+          <t>黑契</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -7517,19 +7509,19 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L103" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N103" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="4" t="n"/>
@@ -7539,12 +7531,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea</t>
+          <t>demon_blood_oath</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7554,52 +7546,52 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>血海翻涌</t>
+          <t>血誓</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="4" t="n"/>
@@ -7609,12 +7601,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_self_heaven</t>
+          <t>demon_blood_sea</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7624,11 +7616,11 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>焚身问天</t>
+          <t>血海翻涌</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
@@ -7642,17 +7634,17 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
@@ -7661,36 +7653,30 @@
         </is>
       </c>
       <c r="L105" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N105" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O105" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="P105" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O105" s="3" t="inlineStr"/>
+      <c r="P105" s="4" t="n"/>
       <c r="Q105" s="3" t="inlineStr"/>
       <c r="R105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>demon_cut_soul</t>
+          <t>demon_burn_self_heaven</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7700,11 +7686,11 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>割魂刃</t>
+          <t>焚身问天</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
@@ -7713,17 +7699,17 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -7733,34 +7719,40 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N106" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O106" s="3" t="inlineStr"/>
-      <c r="P106" s="4" t="n"/>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q106" s="3" t="inlineStr"/>
       <c r="R106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_power</t>
+          <t>demon_cut_soul</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7770,7 +7762,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>禁咒开脉</t>
+          <t>割魂刃</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
@@ -7778,17 +7770,17 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -7803,40 +7795,34 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N107" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P107" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="4" t="n"/>
       <c r="Q107" s="3" t="inlineStr"/>
       <c r="R107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>demon_ghost_hook</t>
+          <t>demon_forbidden_power</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7846,7 +7832,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>幽钩</t>
+          <t>禁咒开脉</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -7854,17 +7840,17 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -7874,20 +7860,20 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N108" s="4" t="n">
@@ -7895,7 +7881,7 @@
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="P108" s="4" t="n">
@@ -7907,12 +7893,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>demon_hell_soul_seal</t>
+          <t>demon_ghost_hook</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7922,11 +7908,11 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>幽冥万魂印</t>
+          <t>幽钩</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
@@ -7935,12 +7921,12 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -7950,7 +7936,7 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -7959,30 +7945,36 @@
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N109" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O109" s="3" t="inlineStr"/>
-      <c r="P109" s="4" t="n"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q109" s="3" t="inlineStr"/>
       <c r="R109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>demon_hundred_ghosts</t>
+          <t>demon_hell_soul_seal</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7992,11 +7984,11 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>百鬼留痕</t>
+          <t>幽冥万魂印</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
@@ -8010,7 +8002,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -8025,17 +8017,19 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L110" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N110" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O110" s="3" t="inlineStr"/>
       <c r="P110" s="4" t="n"/>
@@ -8045,12 +8039,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>demon_lantern_shadow</t>
+          <t>demon_hundred_ghosts</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -8060,25 +8054,25 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>灯影噬魂</t>
+          <t>百鬼留痕</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -8093,19 +8087,17 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L111" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="n"/>
       <c r="M111" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N111" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="4" t="n"/>
@@ -8115,12 +8107,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>demon_life_for_mana</t>
+          <t>demon_lantern_shadow</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8130,11 +8122,11 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>命换灵机</t>
+          <t>灯影噬魂</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
@@ -8143,7 +8135,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8163,15 +8155,15 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N112" s="4" t="n">
@@ -8185,12 +8177,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>demon_mark_bloom</t>
+          <t>demon_life_for_mana</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8200,52 +8192,52 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>印开彼岸</t>
+          <t>命换灵机</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M113" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N113" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="4" t="n"/>
@@ -8255,12 +8247,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>demon_sacrificial_flame</t>
+          <t>demon_mark_bloom</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8270,25 +8262,25 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>祭焰</t>
+          <t>印开彼岸</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -8298,24 +8290,24 @@
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="4" t="n"/>
@@ -8325,12 +8317,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_armor</t>
+          <t>demon_sacrificial_flame</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8340,7 +8332,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>魂衣</t>
+          <t>祭焰</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
@@ -8348,12 +8340,12 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -8368,24 +8360,24 @@
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="4" t="n"/>
@@ -8395,12 +8387,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_price</t>
+          <t>demon_soul_armor</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8410,15 +8402,15 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>以魂为价</t>
+          <t>魂衣</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -8428,7 +8420,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -8438,45 +8430,39 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O116" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P116" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O116" s="3" t="inlineStr"/>
+      <c r="P116" s="4" t="n"/>
       <c r="Q116" s="3" t="inlineStr"/>
       <c r="R116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_prison</t>
+          <t>demon_soul_price</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8486,7 +8472,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>万魂牢</t>
+          <t>以魂为价</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -8494,17 +8480,17 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -8514,33 +8500,45 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L117" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M117" s="3" t="inlineStr"/>
-      <c r="N117" s="4" t="n"/>
-      <c r="O117" s="3" t="inlineStr"/>
-      <c r="P117" s="4" t="n"/>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q117" s="3" t="inlineStr"/>
       <c r="R117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_siphon</t>
+          <t>demon_soul_prison</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -8550,25 +8548,25 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>摄魂归元</t>
+          <t>万魂牢</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -8578,45 +8576,33 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O118" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P118" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr"/>
+      <c r="N118" s="4" t="n"/>
+      <c r="O118" s="3" t="inlineStr"/>
+      <c r="P118" s="4" t="n"/>
       <c r="Q118" s="3" t="inlineStr"/>
       <c r="R118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_stamp</t>
+          <t>demon_soul_siphon</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -8626,7 +8612,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>魂印</t>
+          <t>摄魂归元</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -8644,7 +8630,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -8654,7 +8640,7 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
@@ -8667,26 +8653,32 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O119" s="3" t="inlineStr"/>
-      <c r="P119" s="4" t="n"/>
+      <c r="P119" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q119" s="3" t="inlineStr"/>
       <c r="R119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>demon_spirit_net</t>
+          <t>demon_soul_stamp</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -8696,7 +8688,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>缚魂网</t>
+          <t>魂印</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -8704,7 +8696,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -8724,16 +8716,16 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8751,12 +8743,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>demon_ten_thousand_sacrifice</t>
+          <t>demon_spirit_net</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -8766,15 +8758,15 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>万祭归一</t>
+          <t>缚魂网</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -8784,34 +8776,34 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N121" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="4" t="n"/>
@@ -8821,12 +8813,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>san_hun_tong_fen</t>
+          <t>demon_ten_thousand_sacrifice</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8836,7 +8828,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>三魂同焚</t>
+          <t>万祭归一</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -8854,27 +8846,35 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L122" s="4" t="n"/>
-      <c r="M122" s="3" t="inlineStr"/>
-      <c r="N122" s="4" t="n"/>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="3" t="inlineStr"/>
@@ -8883,12 +8883,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
+          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>shadow_step</t>
+          <t>san_hun_tong_fen</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8898,20 +8898,20 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>影遁</t>
+          <t>三魂同焚</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -8921,22 +8921,20 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="n"/>
       <c r="M123" s="3" t="inlineStr"/>
       <c r="N123" s="4" t="n"/>
       <c r="O123" s="3" t="inlineStr"/>
@@ -8947,12 +8945,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
+          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>she_hun_xu_yuan</t>
+          <t>shadow_step</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8962,7 +8960,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>摄魂续元</t>
+          <t>影遁</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -8975,7 +8973,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -8985,48 +8983,38 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="n"/>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="N124" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O124" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P124" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="3" t="inlineStr"/>
+      <c r="P124" s="4" t="n"/>
       <c r="Q124" s="3" t="inlineStr"/>
       <c r="R124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
+          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>soul_drain</t>
+          <t>she_hun_xu_yuan</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -9036,7 +9024,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>摄魂</t>
+          <t>摄魂续元</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -9044,7 +9032,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -9054,7 +9042,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -9064,28 +9052,26 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L125" s="4" t="n">
-        <v>5</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n"/>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="N125" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="P125" s="4" t="n">
@@ -9097,12 +9083,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
+          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>yin_sha_jue</t>
+          <t>soul_drain</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -9112,7 +9098,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>引煞诀</t>
+          <t>摄魂</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9130,7 +9116,7 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -9140,7 +9126,7 @@
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
@@ -9149,40 +9135,46 @@
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N126" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O126" s="3" t="inlineStr"/>
-      <c r="P126" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P126" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q126" s="3" t="inlineStr"/>
       <c r="R126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>yin_sha_jue</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>引煞诀</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
@@ -9200,7 +9192,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
@@ -9210,7 +9202,7 @@
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
@@ -9221,8 +9213,14 @@
       <c r="L127" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M127" s="3" t="inlineStr"/>
-      <c r="N127" s="4" t="n"/>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O127" s="3" t="inlineStr"/>
       <c r="P127" s="4" t="n"/>
       <c r="Q127" s="3" t="inlineStr"/>
@@ -9231,12 +9229,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
+          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>guard_sword</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9246,7 +9244,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>御剑守心</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9254,12 +9252,12 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -9279,20 +9277,14 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M128" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N128" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr"/>
+      <c r="N128" s="4" t="n"/>
       <c r="O128" s="3" t="inlineStr"/>
       <c r="P128" s="4" t="n"/>
       <c r="Q128" s="3" t="inlineStr"/>
@@ -9301,12 +9293,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
+          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>sword_blade_embryo</t>
+          <t>guard_sword</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9316,7 +9308,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>剑胎初鸣</t>
+          <t>御剑守心</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9324,7 +9316,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -9349,15 +9341,15 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N129" s="4" t="n">
@@ -9371,12 +9363,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>sword_breath_return</t>
+          <t>sword_blade_embryo</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9386,7 +9378,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>回风纳息</t>
+          <t>剑胎初鸣</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9394,7 +9386,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -9414,12 +9406,12 @@
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="L130" s="4" t="n">
@@ -9427,7 +9419,7 @@
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N130" s="4" t="n">
@@ -9441,12 +9433,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_cut</t>
+          <t>sword_breath_return</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9456,7 +9448,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>云隙递剑</t>
+          <t>回风纳息</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9464,12 +9456,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -9484,20 +9476,20 @@
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N131" s="4" t="n">
@@ -9511,12 +9503,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_scroll</t>
+          <t>sword_cloud_cut</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9526,7 +9518,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>云海剑书</t>
+          <t>云隙递剑</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9534,17 +9526,17 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
@@ -9554,19 +9546,25 @@
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L132" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M132" s="3" t="inlineStr"/>
-      <c r="N132" s="4" t="n"/>
+      <c r="N132" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="4" t="n"/>
       <c r="Q132" s="3" t="inlineStr"/>
@@ -9575,12 +9573,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>sword_flow_shift</t>
+          <t>sword_cloud_scroll</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9590,7 +9588,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>流光换形</t>
+          <t>云海剑书</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9623,20 +9621,14 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M133" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N133" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="M133" s="3" t="inlineStr"/>
+      <c r="N133" s="4" t="n"/>
       <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="4" t="n"/>
       <c r="Q133" s="3" t="inlineStr"/>
@@ -9645,12 +9637,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>sword_forge_spark</t>
+          <t>sword_flow_shift</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9660,7 +9652,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>炉火铸锋</t>
+          <t>流光换形</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9678,7 +9670,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -9688,7 +9680,7 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -9697,15 +9689,15 @@
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N134" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" s="3" t="inlineStr"/>
       <c r="P134" s="4" t="n"/>
@@ -9715,12 +9707,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>sword_furnace_open</t>
+          <t>sword_forge_spark</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9730,15 +9722,15 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>剑炉大开</t>
+          <t>炉火铸锋</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -9748,7 +9740,7 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -9763,11 +9755,11 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9775,7 +9767,7 @@
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="4" t="n"/>
@@ -9785,12 +9777,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>sword_hidden_edge</t>
+          <t>sword_furnace_open</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9800,15 +9792,15 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>藏锋式</t>
+          <t>剑炉大开</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -9818,7 +9810,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -9828,19 +9820,25 @@
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L136" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M136" s="3" t="inlineStr"/>
-      <c r="N136" s="4" t="n"/>
+      <c r="N136" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="4" t="n"/>
       <c r="Q136" s="3" t="inlineStr"/>
@@ -9849,12 +9847,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>sword_hundred_forge</t>
+          <t>sword_hidden_edge</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9864,7 +9862,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>百炼锋芒</t>
+          <t>藏锋式</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -9882,7 +9880,7 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -9892,7 +9890,7 @@
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -9901,7 +9899,7 @@
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M137" s="3" t="inlineStr"/>
       <c r="N137" s="4" t="n"/>
@@ -9913,12 +9911,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>sword_iron_cleave</t>
+          <t>sword_hundred_forge</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9928,20 +9926,20 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>斩铁成锋</t>
+          <t>百炼锋芒</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -9956,22 +9954,18 @@
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M138" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr"/>
       <c r="N138" s="4" t="n"/>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="4" t="n"/>
@@ -9981,12 +9975,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>sword_light_step</t>
+          <t>sword_iron_cleave</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -9996,25 +9990,25 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>剑步轻灵</t>
+          <t>斩铁成锋</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -10024,25 +10018,23 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N139" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="n"/>
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="4" t="n"/>
       <c r="Q139" s="3" t="inlineStr"/>
@@ -10051,12 +10043,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>sword_marrow_forge</t>
+          <t>sword_light_step</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -10066,11 +10058,11 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>洗髓铸刃</t>
+          <t>剑步轻灵</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
@@ -10084,7 +10076,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -10103,11 +10095,11 @@
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N140" s="4" t="n">
@@ -10121,12 +10113,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>sword_probe_meridian</t>
+          <t>sword_marrow_forge</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -10136,7 +10128,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>剑影探脉</t>
+          <t>洗髓铸刃</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
@@ -10144,17 +10136,17 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -10164,45 +10156,39 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N141" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O141" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="P141" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O141" s="3" t="inlineStr"/>
+      <c r="P141" s="4" t="n"/>
       <c r="Q141" s="3" t="inlineStr"/>
       <c r="R141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>sword_ring_sheath</t>
+          <t>sword_probe_meridian</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10212,7 +10198,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>剑鸣归鞘</t>
+          <t>剑影探脉</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
@@ -10220,17 +10206,17 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -10245,34 +10231,40 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
       <c r="N142" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O142" s="3" t="inlineStr"/>
-      <c r="P142" s="4" t="n"/>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="P142" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q142" s="3" t="inlineStr"/>
       <c r="R142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>sword_sky_river</t>
+          <t>sword_ring_sheath</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10282,52 +10274,52 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>天河倒卷</t>
+          <t>剑鸣归鞘</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N143" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O143" s="3" t="inlineStr"/>
       <c r="P143" s="4" t="n"/>
@@ -10337,12 +10329,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>sword_split_heaven</t>
+          <t>sword_sky_river</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10352,11 +10344,11 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>一剑开天</t>
+          <t>天河倒卷</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
@@ -10365,12 +10357,12 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -10380,7 +10372,7 @@
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -10389,14 +10381,16 @@
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N144" s="4" t="n"/>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O144" s="3" t="inlineStr"/>
       <c r="P144" s="4" t="n"/>
       <c r="Q144" s="3" t="inlineStr"/>
@@ -10405,12 +10399,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>sword_temper_edge</t>
+          <t>sword_split_heaven</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10420,11 +10414,11 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>淬锋</t>
+          <t>一剑开天</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
@@ -10438,7 +10432,7 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -10448,7 +10442,7 @@
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -10457,7 +10451,7 @@
         </is>
       </c>
       <c r="L145" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10473,12 +10467,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>sword_trial_edge</t>
+          <t>sword_temper_edge</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10488,7 +10482,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>试锋</t>
+          <t>淬锋</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -10516,7 +10510,7 @@
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -10525,16 +10519,14 @@
         </is>
       </c>
       <c r="L146" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N146" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="n"/>
       <c r="O146" s="3" t="inlineStr"/>
       <c r="P146" s="4" t="n"/>
       <c r="Q146" s="3" t="inlineStr"/>
@@ -10543,12 +10535,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>sword_void_roam</t>
+          <t>sword_trial_edge</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10558,11 +10550,11 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>太虚游剑</t>
+          <t>试锋</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
@@ -10576,7 +10568,7 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -10595,36 +10587,30 @@
         </is>
       </c>
       <c r="L147" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N147" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O147" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P147" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O147" s="3" t="inlineStr"/>
+      <c r="P147" s="4" t="n"/>
       <c r="Q147" s="3" t="inlineStr"/>
       <c r="R147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>sword_wash_blade</t>
+          <t>sword_void_roam</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10634,25 +10620,25 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>洗剑诀</t>
+          <t>太虚游剑</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -10662,33 +10648,45 @@
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L148" s="4" t="n">
+      <c r="N148" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M148" s="3" t="inlineStr"/>
-      <c r="N148" s="4" t="n"/>
-      <c r="O148" s="3" t="inlineStr"/>
-      <c r="P148" s="4" t="n"/>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q148" s="3" t="inlineStr"/>
       <c r="R148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>piercing_light</t>
+          <t>sword_wash_blade</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10698,53 +10696,47 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>一线天</t>
+          <t>洗剑诀</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M149" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M149" s="3" t="inlineStr"/>
+      <c r="N149" s="4" t="n"/>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="4" t="n"/>
       <c r="Q149" s="3" t="inlineStr"/>
@@ -10753,12 +10745,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
+          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>sword_blood_curse</t>
+          <t>piercing_light</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10768,11 +10760,11 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>血祭剑咒</t>
+          <t>一线天</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
@@ -10801,40 +10793,34 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L150" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N150" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O150" s="3" t="inlineStr">
-        <is>
-          <t>状态(bleed)</t>
-        </is>
-      </c>
-      <c r="P150" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="O150" s="3" t="inlineStr"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
+          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>sword_energy_charge</t>
+          <t>sword_blood_curse</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10844,25 +10830,25 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>凝气术</t>
+          <t>血祭剑咒</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -10877,34 +10863,40 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L151" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>状态(energy_charge)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="N151" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O151" s="3" t="inlineStr"/>
-      <c r="P151" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>状态(bleed)</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q151" s="3" t="inlineStr"/>
       <c r="R151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
+          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>sword_guard_formation</t>
+          <t>sword_energy_charge</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10914,15 +10906,15 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>万剑护体</t>
+          <t>凝气术</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -10932,7 +10924,7 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -10947,14 +10939,20 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_guard)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L152" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M152" s="3" t="inlineStr"/>
-      <c r="N152" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>状态(energy_charge)</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O152" s="3" t="inlineStr"/>
       <c r="P152" s="4" t="n"/>
       <c r="Q152" s="3" t="inlineStr"/>
@@ -10963,12 +10961,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
+          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>sword_heart</t>
+          <t>sword_guard_formation</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10978,11 +10976,11 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>剑心通明</t>
+          <t>万剑护体</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
@@ -10996,35 +10994,29 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>状态(sword_guard)</t>
         </is>
       </c>
       <c r="L153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M153" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N153" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr"/>
+      <c r="N153" s="4" t="n"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="4" t="n"/>
       <c r="Q153" s="3" t="inlineStr"/>
@@ -11033,12 +11025,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
+          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>sword_nurture</t>
+          <t>sword_heart</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -11048,7 +11040,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>养剑诀</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -11056,7 +11048,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -11066,7 +11058,7 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -11081,14 +11073,20 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_intent)</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L154" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M154" s="3" t="inlineStr"/>
-      <c r="N154" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N154" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O154" s="3" t="inlineStr"/>
       <c r="P154" s="4" t="n"/>
       <c r="Q154" s="3" t="inlineStr"/>
@@ -11097,12 +11095,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
+          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>sword_qi_draw</t>
+          <t>sword_nurture</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -11112,11 +11110,11 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>剑气引</t>
+          <t>养剑诀</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
@@ -11130,7 +11128,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11145,20 +11143,14 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(sword_intent)</t>
         </is>
       </c>
       <c r="L155" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M155" s="3" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="N155" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M155" s="3" t="inlineStr"/>
+      <c r="N155" s="4" t="n"/>
       <c r="O155" s="3" t="inlineStr"/>
       <c r="P155" s="4" t="n"/>
       <c r="Q155" s="3" t="inlineStr"/>
@@ -11167,12 +11159,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
+          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>sword_rain</t>
+          <t>sword_qi_draw</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -11182,47 +11174,53 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>剑雨</t>
+          <t>剑气引</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L156" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M156" s="3" t="inlineStr"/>
-      <c r="N156" s="4" t="n"/>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O156" s="3" t="inlineStr"/>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="3" t="inlineStr"/>
@@ -11231,12 +11229,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>sword_shadow_strike</t>
+          <t>sword_rain</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -11246,11 +11244,11 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>瞬影剑</t>
+          <t>剑雨</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
@@ -11259,22 +11257,22 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -11283,16 +11281,10 @@
         </is>
       </c>
       <c r="L157" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M157" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N157" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr"/>
+      <c r="N157" s="4" t="n"/>
       <c r="O157" s="3" t="inlineStr"/>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="3" t="inlineStr"/>
@@ -11301,12 +11293,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
+          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>sword_star_shatter</t>
+          <t>sword_shadow_strike</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11316,11 +11308,11 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>碎星斩</t>
+          <t>瞬影剑</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
@@ -11334,29 +11326,35 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>target_status_bonus_damage_effect</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L158" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M158" s="3" t="inlineStr"/>
-      <c r="N158" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O158" s="3" t="inlineStr"/>
       <c r="P158" s="4" t="n"/>
       <c r="Q158" s="3" t="inlineStr"/>
@@ -11365,12 +11363,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
+          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>sword_wanjian</t>
+          <t>sword_star_shatter</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -11380,11 +11378,11 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>万剑归宗</t>
+          <t>碎星斩</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
@@ -11413,11 +11411,11 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>player_status_damage_effect</t>
+          <t>target_status_bonus_damage_effect</t>
         </is>
       </c>
       <c r="L159" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M159" s="3" t="inlineStr"/>
       <c r="N159" s="4" t="n"/>
@@ -11429,12 +11427,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>sword_water_break</t>
+          <t>sword_wanjian</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -11444,11 +11442,11 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>断水剑</t>
+          <t>万剑归宗</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
@@ -11462,7 +11460,7 @@
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
@@ -11472,25 +11470,19 @@
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>player_status_damage_effect</t>
         </is>
       </c>
       <c r="L160" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M160" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr"/>
+      <c r="N160" s="4" t="n"/>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="3" t="inlineStr"/>
@@ -11499,12 +11491,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
+          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>sword_wind_return</t>
+          <t>sword_water_break</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -11514,11 +11506,11 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>回风剑</t>
+          <t>断水剑</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
@@ -11532,7 +11524,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -11542,7 +11534,7 @@
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -11551,15 +11543,15 @@
         </is>
       </c>
       <c r="L161" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N161" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="4" t="n"/>
@@ -11569,22 +11561,22 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ash_heart_guard.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ash_heart_guard</t>
+          <t>sword_wind_return</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>灰烬护心</t>
+          <t>回风剑</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -11592,17 +11584,17 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -11612,19 +11604,25 @@
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M162" s="3" t="inlineStr"/>
-      <c r="N162" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O162" s="3" t="inlineStr"/>
       <c r="P162" s="4" t="n"/>
       <c r="Q162" s="3" t="inlineStr"/>
@@ -11633,12 +11631,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>common_cards/circulating_breath.tres</t>
+          <t>common_cards/ash_heart_guard.tres</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>circulating_breath</t>
+          <t>ash_heart_guard</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -11648,7 +11646,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>周天吐纳</t>
+          <t>灰烬护心</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
@@ -11666,7 +11664,7 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -11681,20 +11679,14 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L163" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M163" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N163" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr"/>
+      <c r="N163" s="4" t="n"/>
       <c r="O163" s="3" t="inlineStr"/>
       <c r="P163" s="4" t="n"/>
       <c r="Q163" s="3" t="inlineStr"/>
@@ -11703,12 +11695,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>common_cards/circulating_breath.tres</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>circulating_breath</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11718,7 +11710,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>周天吐纳</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -11757,8 +11749,14 @@
       <c r="L164" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M164" s="3" t="inlineStr"/>
-      <c r="N164" s="4" t="n"/>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O164" s="3" t="inlineStr"/>
       <c r="P164" s="4" t="n"/>
       <c r="Q164" s="3" t="inlineStr"/>
@@ -11767,12 +11765,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>common_cards/discard_aegis.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>discard_aegis</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11782,7 +11780,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>弃念成罡</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -11800,7 +11798,7 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -11815,11 +11813,11 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L165" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="4" t="n"/>
@@ -11831,12 +11829,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/embers_return.tres</t>
+          <t>common_cards/discard_aegis.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>embers_return</t>
+          <t>discard_aegis</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11846,7 +11844,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>烬归灵台</t>
+          <t>弃念成罡</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -11864,12 +11862,12 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -11879,20 +11877,14 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L166" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M166" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N166" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr"/>
+      <c r="N166" s="4" t="n"/>
       <c r="O166" s="3" t="inlineStr"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="3" t="inlineStr"/>
@@ -11901,12 +11893,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/flowing_cloud_guard.tres</t>
+          <t>common_cards/embers_return.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>flowing_cloud_guard</t>
+          <t>embers_return</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11916,7 +11908,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>流云护身</t>
+          <t>烬归灵台</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -11939,7 +11931,7 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -11949,12 +11941,20 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="n"/>
-      <c r="M167" s="3" t="inlineStr"/>
-      <c r="N167" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -11963,12 +11963,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>common_cards/flowing_cloud_guard.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>flowing_cloud_guard</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>流云护身</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -11986,17 +11986,17 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -12011,20 +12011,12 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L168" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M168" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N168" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="n"/>
+      <c r="M168" s="3" t="inlineStr"/>
+      <c r="N168" s="4" t="n"/>
       <c r="O168" s="3" t="inlineStr"/>
       <c r="P168" s="4" t="n"/>
       <c r="Q168" s="3" t="inlineStr"/>
@@ -12033,12 +12025,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/momentum_pursuit.tres</t>
+          <t>common_cards/ink_flow_slash.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>momentum_pursuit</t>
+          <t>ink_flow_slash</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12048,7 +12040,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>乘势追击</t>
+          <t>墨流斩</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12066,7 +12058,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -12081,14 +12073,20 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L169" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" s="3" t="inlineStr"/>
-      <c r="N169" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N169" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O169" s="3" t="inlineStr"/>
       <c r="P169" s="4" t="n"/>
       <c r="Q169" s="3" t="inlineStr"/>
@@ -12097,12 +12095,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>common_cards/momentum_pursuit.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>momentum_pursuit</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12112,7 +12110,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>乘势追击</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12130,7 +12128,7 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -12145,20 +12143,14 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L170" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M170" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N170" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr"/>
+      <c r="N170" s="4" t="n"/>
       <c r="O170" s="3" t="inlineStr"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="3" t="inlineStr"/>
@@ -12167,12 +12159,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>common_cards/returning_light.tres</t>
+          <t>common_cards/muscle_resonance_strike.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>returning_light</t>
+          <t>muscle_resonance_strike</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -12182,7 +12174,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>回光返照</t>
+          <t>劲气共鸣</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12190,22 +12182,22 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -12215,14 +12207,20 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L171" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M171" s="3" t="inlineStr"/>
-      <c r="N171" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -12231,12 +12229,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>common_cards/spirit_stone_needle.tres</t>
+          <t>common_cards/returning_light.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>spirit_stone_needle</t>
+          <t>returning_light</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12246,25 +12244,25 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>灵石飞针</t>
+          <t>回光返照</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -12279,11 +12277,11 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L172" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M172" s="3" t="inlineStr"/>
       <c r="N172" s="4" t="n"/>
@@ -12295,12 +12293,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/blood_debt_curse.tres</t>
+          <t>common_cards/spirit_stone_needle.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>blood_debt_curse</t>
+          <t>spirit_stone_needle</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -12310,7 +12308,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>血债</t>
+          <t>灵石飞针</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12318,12 +12316,12 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -12333,7 +12331,7 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -12343,11 +12341,11 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="4" t="n"/>
@@ -12359,12 +12357,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -12374,7 +12372,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -12405,8 +12403,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K174" s="3" t="inlineStr"/>
-      <c r="L174" s="4" t="n"/>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="4" t="n"/>
       <c r="O174" s="3" t="inlineStr"/>
@@ -12417,12 +12421,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -12432,7 +12436,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
@@ -12475,12 +12479,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/karmic_fire_curse.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>karmic_fire_curse</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -12490,11 +12494,11 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
@@ -12513,7 +12517,7 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -12521,14 +12525,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="K176" s="3" t="inlineStr"/>
+      <c r="L176" s="4" t="n"/>
       <c r="M176" s="3" t="inlineStr"/>
       <c r="N176" s="4" t="n"/>
       <c r="O176" s="3" t="inlineStr"/>
@@ -12539,12 +12537,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>karmic_fire_curse</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -12554,11 +12552,11 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
@@ -12577,7 +12575,7 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -12585,8 +12583,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="4" t="n"/>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M177" s="3" t="inlineStr"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="3" t="inlineStr"/>
@@ -12597,12 +12601,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/status/underworld_writ.tres</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>underworld_writ</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -12612,20 +12616,20 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>判牒</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -12643,14 +12647,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="K178" s="3" t="inlineStr"/>
+      <c r="L178" s="4" t="n"/>
       <c r="M178" s="3" t="inlineStr"/>
       <c r="N178" s="4" t="n"/>
       <c r="O178" s="3" t="inlineStr"/>
@@ -12661,12 +12659,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/strike.tres</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>strike</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -12676,7 +12674,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
@@ -12684,12 +12682,12 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -12699,7 +12697,7 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
@@ -12707,8 +12705,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K179" s="3" t="inlineStr"/>
-      <c r="L179" s="4" t="n"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="3" t="inlineStr"/>
@@ -12719,22 +12723,22 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/toxin.tres</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
@@ -12742,22 +12746,22 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -12765,22 +12769,10 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L180" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M180" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N180" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="K180" s="3" t="inlineStr"/>
+      <c r="L180" s="4" t="n"/>
+      <c r="M180" s="3" t="inlineStr"/>
+      <c r="N180" s="4" t="n"/>
       <c r="O180" s="3" t="inlineStr"/>
       <c r="P180" s="4" t="n"/>
       <c r="Q180" s="3" t="inlineStr"/>
@@ -12789,12 +12781,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>fusion_cards/attack_guard_unity.tres</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>attack_guard_unity</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -12804,7 +12796,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>攻守合一</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
@@ -12832,7 +12824,7 @@
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -12841,15 +12833,15 @@
         </is>
       </c>
       <c r="L181" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N181" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O181" s="3" t="inlineStr"/>
       <c r="P181" s="4" t="n"/>
@@ -12859,12 +12851,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>fusion_cards/blood_beast_rend.tres</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>blood_beast_rend</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -12874,52 +12866,52 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>血兽撕咬</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M182" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="O182" s="3" t="inlineStr"/>
       <c r="P182" s="4" t="n"/>
@@ -12929,12 +12921,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>demon_rain_swordfire</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -12944,11 +12936,11 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>魔雨剑火</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
@@ -12957,12 +12949,12 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -12972,7 +12964,7 @@
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -12981,42 +12973,112 @@
         </is>
       </c>
       <c r="L183" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N183" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O183" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P183" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O183" s="3" t="inlineStr"/>
+      <c r="P183" s="4" t="n"/>
       <c r="Q183" s="3" t="inlineStr"/>
       <c r="R183" s="4" t="n"/>
     </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q184" s="3" t="inlineStr"/>
+      <c r="R184" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R184"/>
+  <dimension ref="A1:R186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4619,12 +4619,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_calamity_embryo.tres</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>demon_defend</t>
+          <t>demon_calamity_embryo</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>劫火魔胎</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4652,43 +4652,59 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3" t="inlineStr"/>
-      <c r="N60" s="4" t="n"/>
-      <c r="O60" s="3" t="inlineStr"/>
-      <c r="P60" s="4" t="n"/>
-      <c r="Q60" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="R60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>demon_desperate_burst</t>
+          <t>demon_defend</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4698,44 +4714,44 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>绝命爆发</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="4" t="n"/>
@@ -4747,12 +4763,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>demon_flame</t>
+          <t>demon_desperate_burst</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4762,7 +4778,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>魔焰燎原</t>
+          <t>绝命爆发</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -4775,17 +4791,17 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -4795,20 +4811,14 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="3" t="inlineStr"/>
@@ -4817,12 +4827,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_black</t>
+          <t>demon_flame</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4832,11 +4842,11 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>魔焰黑·噬血</t>
+          <t>魔焰燎原</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -4845,7 +4855,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4860,30 +4870,26 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
           <t>自损</t>
         </is>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+      <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="3" t="inlineStr"/>
       <c r="R63" s="4" t="n"/>
@@ -4891,12 +4897,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_blue</t>
+          <t>demon_flame_black</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4906,7 +4912,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>魔焰蓝·灵涌</t>
+          <t>魔焰黑·噬血</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -4914,12 +4920,12 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4929,7 +4935,7 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4939,19 +4945,25 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n"/>
-      <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="3" t="inlineStr"/>
       <c r="R64" s="4" t="n"/>
@@ -4959,12 +4971,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_green</t>
+          <t>demon_flame_blue</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4974,7 +4986,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>魔焰绿·镇煞</t>
+          <t>魔焰蓝·灵涌</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -4997,7 +5009,7 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -5007,11 +5019,17 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="4" t="n"/>
@@ -5021,12 +5039,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_heart</t>
+          <t>demon_flame_green</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5036,20 +5054,20 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>魔焰焚心</t>
+          <t>魔焰绿·镇煞</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5064,25 +5082,17 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="4" t="n"/>
       <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="3" t="inlineStr"/>
@@ -5091,12 +5101,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_purple</t>
+          <t>demon_flame_heart</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5106,11 +5116,11 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>魔焰紫·蚀魂</t>
+          <t>魔焰焚心</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
@@ -5124,7 +5134,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -5134,30 +5144,26 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
           <t>状态(exposed)</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
       <c r="N67" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="3" t="inlineStr"/>
       <c r="R67" s="4" t="n"/>
@@ -5165,12 +5171,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_red</t>
+          <t>demon_flame_purple</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5180,11 +5186,11 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>魔焰红·焚界</t>
+          <t>魔焰紫·蚀魂</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
@@ -5193,12 +5199,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -5213,19 +5219,25 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="L68" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="N68" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
         <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n"/>
-      <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="3" t="inlineStr"/>
       <c r="R68" s="4" t="n"/>
@@ -5233,12 +5245,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_white</t>
+          <t>demon_flame_red</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5248,11 +5260,11 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>魔焰白·护魂</t>
+          <t>魔焰红·焚界</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -5261,12 +5273,12 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -5285,21 +5297,15 @@
         </is>
       </c>
       <c r="L69" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="3" t="inlineStr"/>
       <c r="R69" s="4" t="n"/>
@@ -5307,12 +5313,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_yellow</t>
+          <t>demon_flame_white</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5322,7 +5328,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>魔焰黄·狂烬</t>
+          <t>魔焰白·护魂</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -5330,17 +5336,17 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -5355,13 +5361,25 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L70" s="4" t="n"/>
-      <c r="M70" s="3" t="inlineStr"/>
-      <c r="N70" s="4" t="n"/>
-      <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="4" t="n"/>
@@ -5369,12 +5387,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>demon_flesh_rebirth</t>
+          <t>demon_flame_yellow</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5384,7 +5402,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>血肉重生</t>
+          <t>魔焰黄·狂烬</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -5402,35 +5420,27 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="4" t="n"/>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="3" t="inlineStr"/>
@@ -5439,12 +5449,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_archive</t>
+          <t>demon_flesh_rebirth</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5454,11 +5464,11 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>窥心魔典</t>
+          <t>血肉重生</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
@@ -5487,14 +5497,20 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>configured_discover_effect</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="3" t="inlineStr"/>
@@ -5503,12 +5519,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_marks_return</t>
+          <t>demon_forbidden_archive</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5518,7 +5534,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>万印归墟</t>
+          <t>窥心魔典</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
@@ -5526,12 +5542,12 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5551,10 +5567,12 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n"/>
+          <t>configured_discover_effect</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="3" t="inlineStr"/>
@@ -5565,12 +5583,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_lurking_soul_curse.tres</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_devour</t>
+          <t>demon_lurking_soul_curse</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5580,30 +5598,30 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>万魂噬天</t>
+          <t>伏魂咒</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -5617,7 +5635,7 @@
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5625,9 +5643,13 @@
         </is>
       </c>
       <c r="N74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O74" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="3" t="inlineStr"/>
       <c r="R74" s="4" t="n"/>
@@ -5635,12 +5657,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>demon_seven_flame_cycle</t>
+          <t>demon_myriad_marks_return</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5650,30 +5672,30 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>七焰回环</t>
+          <t>万印归墟</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5683,7 +5705,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>configured_flame_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L75" s="4" t="n"/>
@@ -5697,12 +5719,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_blade</t>
+          <t>demon_myriad_soul_devour</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -5712,11 +5734,11 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>煞刃</t>
+          <t>万魂噬天</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
@@ -5725,17 +5747,17 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5745,12 +5767,20 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>耗煞伤害</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="3" t="inlineStr"/>
@@ -5759,12 +5789,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>demon_shadow_reenactment</t>
+          <t>demon_seven_flame_cycle</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5774,7 +5804,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>魔影复刻</t>
+          <t>七焰回环</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5792,12 +5822,12 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -5807,7 +5837,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>复刻</t>
+          <t>configured_flame_effect</t>
         </is>
       </c>
       <c r="L77" s="4" t="n"/>
@@ -5821,12 +5851,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>demon_shatter_soul_seal</t>
+          <t>demon_sha_blade</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5836,15 +5866,15 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>碎魂印</t>
+          <t>煞刃</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5854,7 +5884,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5864,25 +5894,17 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>耗煞伤害</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="4" t="n"/>
       <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="3" t="inlineStr"/>
@@ -5891,12 +5913,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_devour_claw</t>
+          <t>demon_shadow_reenactment</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5906,7 +5928,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>噬魂爪</t>
+          <t>魔影复刻</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -5914,22 +5936,22 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5939,20 +5961,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>复刻</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="4" t="n"/>
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="3" t="inlineStr"/>
@@ -5961,12 +5975,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_lamp_renewal</t>
+          <t>demon_shatter_soul_seal</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5976,7 +5990,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>魂灯续燃</t>
+          <t>碎魂印</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -5999,48 +6013,44 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="4" t="n"/>
       <c r="Q80" s="3" t="inlineStr"/>
       <c r="R80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>demon_strike</t>
+          <t>demon_soul_devour_claw</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6050,7 +6060,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>噬魂爪</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6078,7 +6088,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -6089,8 +6099,14 @@
       <c r="L81" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="3" t="inlineStr"/>
@@ -6099,12 +6115,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_membrane</t>
+          <t>demon_soul_lamp_renewal</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6114,7 +6130,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>血膜</t>
+          <t>魂灯续燃</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6122,12 +6138,12 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6137,7 +6153,7 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -6147,38 +6163,38 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n"/>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N82" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="n"/>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q82" s="3" t="inlineStr"/>
       <c r="R82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_qi_guard</t>
+          <t>demon_strike</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6188,7 +6204,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>血气护体</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -6196,12 +6212,12 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6216,15 +6232,17 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M83" s="3" t="inlineStr"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="3" t="inlineStr"/>
@@ -6235,12 +6253,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_recompense</t>
+          <t>demon_blood_membrane</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6250,46 +6268,58 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>血偿万道</t>
+          <t>血膜</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>功法</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
         <is>
           <t>configured_demonic_engine_effect</t>
         </is>
       </c>
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="3" t="inlineStr"/>
-      <c r="N84" s="4" t="n"/>
-      <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="3" t="inlineStr"/>
       <c r="R84" s="4" t="n"/>
@@ -6297,12 +6327,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_boundless</t>
+          <t>demon_blood_qi_guard</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6312,25 +6342,25 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>血海无量</t>
+          <t>血气护体</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -6345,15 +6375,11 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>configured_x_cost_self_damage_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L85" s="4" t="n"/>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>configured_x_cost_damage_effect</t>
-        </is>
-      </c>
+      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="4" t="n"/>
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="4" t="n"/>
@@ -6363,12 +6389,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demon_bloodthirst</t>
+          <t>demon_blood_recompense</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6378,11 +6404,11 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>嗜血成性</t>
+          <t>血偿万道</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
@@ -6396,7 +6422,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -6425,12 +6451,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_breath</t>
+          <t>demon_blood_sea_boundless</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6440,25 +6466,25 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>焰息</t>
+          <t>血海无量</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -6468,25 +6494,21 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v>8</v>
-      </c>
+          <t>configured_x_cost_self_damage_effect</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="n"/>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_x_cost_damage_effect</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="n"/>
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="3" t="inlineStr"/>
@@ -6495,12 +6517,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_continuity</t>
+          <t>demon_bloodthirst</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6510,7 +6532,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>焰心承续</t>
+          <t>嗜血成性</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -6538,7 +6560,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -6557,12 +6579,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_refining</t>
+          <t>demon_flame_breath</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6572,7 +6594,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>炼焰术</t>
+          <t>焰息</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
@@ -6580,7 +6602,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6590,7 +6612,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -6600,17 +6622,25 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="3" t="inlineStr"/>
-      <c r="N89" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="3" t="inlineStr"/>
@@ -6619,12 +6649,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_burn_sky</t>
+          <t>demon_flame_continuity</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6634,40 +6664,40 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>万魂焚天</t>
+          <t>焰心承续</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L90" s="4" t="n"/>
@@ -6681,12 +6711,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_nurture</t>
+          <t>demon_flame_refining</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6696,7 +6726,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>养煞</t>
+          <t>炼焰术</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -6714,7 +6744,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -6724,7 +6754,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -6743,12 +6773,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_return</t>
+          <t>demon_myriad_soul_burn_sky</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6758,25 +6788,25 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>归煞</t>
+          <t>万魂焚天</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -6786,23 +6816,17 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>configured_consume_status_to_block_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L92" s="4" t="n"/>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="4" t="n"/>
       <c r="O92" s="3" t="inlineStr"/>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="3" t="inlineStr"/>
@@ -6811,12 +6835,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_banner</t>
+          <t>demon_sha_nurture</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6826,7 +6850,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>引魂幡</t>
+          <t>养煞</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
@@ -6834,12 +6858,12 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -6859,20 +6883,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M93" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="4" t="n"/>
       <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="3" t="inlineStr"/>
@@ -6881,12 +6897,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_echo</t>
+          <t>demon_sha_return</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6896,15 +6912,15 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>噬魂回响</t>
+          <t>归煞</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -6914,12 +6930,12 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -6929,12 +6945,18 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_consume_status_to_block_effect</t>
         </is>
       </c>
       <c r="L94" s="4" t="n"/>
-      <c r="M94" s="3" t="inlineStr"/>
-      <c r="N94" s="4" t="n"/>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="3" t="inlineStr"/>
@@ -6943,12 +6965,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_flame_cycle</t>
+          <t>demon_soul_banner</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6958,7 +6980,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>魂火相济</t>
+          <t>引魂幡</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -6966,17 +6988,17 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -6986,17 +7008,25 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="3" t="inlineStr"/>
-      <c r="N95" s="4" t="n"/>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="3" t="inlineStr"/>
@@ -7005,12 +7035,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_mark_sense</t>
+          <t>demon_soul_echo</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7020,11 +7050,11 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>魂印感应</t>
+          <t>噬魂回响</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
@@ -7038,7 +7068,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -7067,12 +7097,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_rite</t>
+          <t>demon_soul_flame_cycle</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7082,7 +7112,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>夺魂仪</t>
+          <t>魂火相济</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -7100,7 +7130,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -7110,7 +7140,7 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -7129,12 +7159,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>forbidden_mantra</t>
+          <t>demon_soul_mark_sense</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7144,7 +7174,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>禁咒入魔</t>
+          <t>魂印感应</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7162,7 +7192,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -7172,25 +7202,17 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N98" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="3" t="inlineStr"/>
+      <c r="N98" s="4" t="n"/>
       <c r="O98" s="3" t="inlineStr"/>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="3" t="inlineStr"/>
@@ -7199,12 +7221,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>hun_kai</t>
+          <t>demon_soul_rite</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7214,7 +7236,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>魂铠</t>
+          <t>夺魂仪</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -7222,17 +7244,17 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -7247,18 +7269,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L99" s="4" t="n"/>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v>8</v>
-      </c>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="4" t="n"/>
       <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="4" t="n"/>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -7267,12 +7283,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
+          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>hun_zang</t>
+          <t>forbidden_mantra</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7282,45 +7298,53 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>魂葬</t>
+          <t>禁咒入魔</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>功法</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L100" s="4" t="n"/>
-      <c r="M100" s="3" t="inlineStr"/>
-      <c r="N100" s="4" t="n"/>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O100" s="3" t="inlineStr"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="3" t="inlineStr"/>
@@ -7329,12 +7353,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>ju_sha</t>
+          <t>hun_kai</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7344,11 +7368,11 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>聚煞</t>
+          <t>魂铠</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
@@ -7357,7 +7381,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7377,19 +7401,17 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n"/>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N101" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="4" t="n"/>
@@ -7399,12 +7421,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>lie_hun</t>
+          <t>hun_zang</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7414,11 +7436,11 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>裂魂</t>
+          <t>魂葬</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
@@ -7432,7 +7454,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -7461,12 +7483,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
+          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>demon_black_contract</t>
+          <t>ju_sha</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7476,15 +7498,15 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>黑契</t>
+          <t>聚煞</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7504,7 +7526,7 @@
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
@@ -7517,11 +7539,11 @@
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>状态(sha_qi)</t>
         </is>
       </c>
       <c r="N103" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="4" t="n"/>
@@ -7531,12 +7553,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
+          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_oath</t>
+          <t>lie_hun</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7546,11 +7568,11 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>血誓</t>
+          <t>裂魂</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
@@ -7574,25 +7596,17 @@
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="3" t="inlineStr"/>
+      <c r="N104" s="4" t="n"/>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="3" t="inlineStr"/>
@@ -7601,12 +7615,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea</t>
+          <t>demon_black_contract</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7616,25 +7630,25 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>血海翻涌</t>
+          <t>黑契</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -7644,24 +7658,24 @@
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L105" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N105" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="4" t="n"/>
@@ -7671,12 +7685,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_self_heaven</t>
+          <t>demon_blood_oath</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7686,11 +7700,11 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>焚身问天</t>
+          <t>血誓</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
@@ -7699,17 +7713,17 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -7723,36 +7737,30 @@
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N106" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O106" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="P106" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="O106" s="3" t="inlineStr"/>
+      <c r="P106" s="4" t="n"/>
       <c r="Q106" s="3" t="inlineStr"/>
       <c r="R106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>demon_cut_soul</t>
+          <t>demon_blood_sea</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7762,11 +7770,11 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>割魂刃</t>
+          <t>血海翻涌</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
@@ -7775,12 +7783,12 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -7790,16 +7798,16 @@
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7807,7 +7815,7 @@
         </is>
       </c>
       <c r="N107" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="4" t="n"/>
@@ -7817,12 +7825,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_power</t>
+          <t>demon_burn_self_heaven</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7832,30 +7840,30 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>禁咒开脉</t>
+          <t>焚身问天</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -7865,27 +7873,27 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L108" s="4" t="n">
+      <c r="N108" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M108" s="3" t="inlineStr">
+      <c r="O108" s="3" t="inlineStr">
         <is>
           <t>自损</t>
         </is>
       </c>
-      <c r="N108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O108" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
       <c r="P108" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q108" s="3" t="inlineStr"/>
       <c r="R108" s="4" t="n"/>
@@ -7893,12 +7901,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>demon_ghost_hook</t>
+          <t>demon_cut_soul</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7908,7 +7916,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>幽钩</t>
+          <t>割魂刃</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
@@ -7936,45 +7944,39 @@
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N109" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O109" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="4" t="n"/>
       <c r="Q109" s="3" t="inlineStr"/>
       <c r="R109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>demon_hell_soul_seal</t>
+          <t>demon_forbidden_power</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7984,25 +7986,25 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>幽冥万魂印</t>
+          <t>禁咒开脉</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -8017,34 +8019,40 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N110" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O110" s="3" t="inlineStr"/>
-      <c r="P110" s="4" t="n"/>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q110" s="3" t="inlineStr"/>
       <c r="R110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>demon_hundred_ghosts</t>
+          <t>demon_ghost_hook</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -8054,11 +8062,11 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>百鬼留痕</t>
+          <t>幽钩</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
@@ -8067,12 +8075,12 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -8082,37 +8090,45 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L111" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="N111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O111" s="3" t="inlineStr"/>
-      <c r="P111" s="4" t="n"/>
+      <c r="P111" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q111" s="3" t="inlineStr"/>
       <c r="R111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>demon_lantern_shadow</t>
+          <t>demon_hell_soul_seal</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8122,25 +8138,25 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>灯影噬魂</t>
+          <t>幽冥万魂印</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -8159,15 +8175,15 @@
         </is>
       </c>
       <c r="L112" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="M112" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N112" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="O112" s="3" t="inlineStr"/>
       <c r="P112" s="4" t="n"/>
@@ -8177,12 +8193,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>demon_life_for_mana</t>
+          <t>demon_hundred_ghosts</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8192,25 +8208,25 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>命换灵机</t>
+          <t>百鬼留痕</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -8225,19 +8241,17 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n"/>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N113" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="4" t="n"/>
@@ -8247,12 +8261,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>demon_mark_bloom</t>
+          <t>demon_lantern_shadow</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8262,52 +8276,52 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>印开彼岸</t>
+          <t>灯影噬魂</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N114" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="4" t="n"/>
@@ -8317,12 +8331,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>demon_sacrificial_flame</t>
+          <t>demon_life_for_mana</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8332,20 +8346,20 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>祭焰</t>
+          <t>命换灵机</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -8365,11 +8379,11 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8387,12 +8401,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_armor</t>
+          <t>demon_mark_bloom</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8402,11 +8416,11 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>魂衣</t>
+          <t>印开彼岸</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
@@ -8415,12 +8429,12 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -8430,24 +8444,24 @@
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N116" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" s="3" t="inlineStr"/>
       <c r="P116" s="4" t="n"/>
@@ -8457,12 +8471,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_price</t>
+          <t>demon_sacrificial_flame</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8472,25 +8486,25 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>以魂为价</t>
+          <t>祭焰</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -8505,40 +8519,34 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
           <t>自损</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N117" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O117" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P117" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O117" s="3" t="inlineStr"/>
+      <c r="P117" s="4" t="n"/>
       <c r="Q117" s="3" t="inlineStr"/>
       <c r="R117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_prison</t>
+          <t>demon_soul_armor</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -8548,11 +8556,11 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>万魂牢</t>
+          <t>魂衣</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
@@ -8561,12 +8569,12 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -8576,19 +8584,25 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M118" s="3" t="inlineStr"/>
-      <c r="N118" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O118" s="3" t="inlineStr"/>
       <c r="P118" s="4" t="n"/>
       <c r="Q118" s="3" t="inlineStr"/>
@@ -8597,12 +8611,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_siphon</t>
+          <t>demon_soul_price</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -8612,20 +8626,20 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>摄魂归元</t>
+          <t>以魂为价</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -8640,12 +8654,12 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L119" s="4" t="n">
@@ -8653,15 +8667,15 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="P119" s="4" t="n">
@@ -8673,12 +8687,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_stamp</t>
+          <t>demon_soul_prison</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -8688,25 +8702,25 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>魂印</t>
+          <t>万魂牢</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -8716,25 +8730,19 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M120" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N120" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr"/>
+      <c r="N120" s="4" t="n"/>
       <c r="O120" s="3" t="inlineStr"/>
       <c r="P120" s="4" t="n"/>
       <c r="Q120" s="3" t="inlineStr"/>
@@ -8743,12 +8751,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>demon_spirit_net</t>
+          <t>demon_soul_siphon</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -8758,7 +8766,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>缚魂网</t>
+          <t>摄魂归元</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
@@ -8766,7 +8774,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -8776,7 +8784,7 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -8786,39 +8794,45 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O121" s="3" t="inlineStr"/>
-      <c r="P121" s="4" t="n"/>
+      <c r="P121" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q121" s="3" t="inlineStr"/>
       <c r="R121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>demon_ten_thousand_sacrifice</t>
+          <t>demon_soul_stamp</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8828,11 +8842,11 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>万祭归一</t>
+          <t>魂印</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
@@ -8846,12 +8860,12 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -8861,19 +8875,19 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N122" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="4" t="n"/>
@@ -8883,12 +8897,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>san_hun_tong_fen</t>
+          <t>demon_spirit_net</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8898,15 +8912,15 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>三魂同焚</t>
+          <t>缚魂网</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -8916,7 +8930,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -8926,17 +8940,25 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="n"/>
-      <c r="M123" s="3" t="inlineStr"/>
-      <c r="N123" s="4" t="n"/>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="4" t="n"/>
       <c r="Q123" s="3" t="inlineStr"/>
@@ -8945,12 +8967,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>shadow_step</t>
+          <t>demon_ten_thousand_sacrifice</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8960,25 +8982,25 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>影遁</t>
+          <t>万祭归一</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
@@ -8993,14 +9015,20 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>牌堆检索</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M124" s="3" t="inlineStr"/>
-      <c r="N124" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="O124" s="3" t="inlineStr"/>
       <c r="P124" s="4" t="n"/>
       <c r="Q124" s="3" t="inlineStr"/>
@@ -9009,12 +9037,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
+          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>she_hun_xu_yuan</t>
+          <t>san_hun_tong_fen</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -9024,15 +9052,15 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>摄魂续元</t>
+          <t>三魂同焚</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -9057,38 +9085,26 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L125" s="4" t="n"/>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="N125" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O125" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P125" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M125" s="3" t="inlineStr"/>
+      <c r="N125" s="4" t="n"/>
+      <c r="O125" s="3" t="inlineStr"/>
+      <c r="P125" s="4" t="n"/>
       <c r="Q125" s="3" t="inlineStr"/>
       <c r="R125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
+          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>soul_drain</t>
+          <t>shadow_step</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -9098,7 +9114,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>摄魂</t>
+          <t>影遁</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9106,22 +9122,22 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -9131,40 +9147,28 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>牌堆检索</t>
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M126" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N126" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O126" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P126" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr"/>
+      <c r="N126" s="4" t="n"/>
+      <c r="O126" s="3" t="inlineStr"/>
+      <c r="P126" s="4" t="n"/>
       <c r="Q126" s="3" t="inlineStr"/>
       <c r="R126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
+          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>yin_sha_jue</t>
+          <t>she_hun_xu_yuan</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -9174,7 +9178,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>引煞诀</t>
+          <t>摄魂续元</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
@@ -9182,7 +9186,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -9207,44 +9211,48 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="n">
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>状态(sha_qi)</t>
-        </is>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O127" s="3" t="inlineStr"/>
-      <c r="P127" s="4" t="n"/>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q127" s="3" t="inlineStr"/>
       <c r="R127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>soul_drain</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>摄魂</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9272,7 +9280,7 @@
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
@@ -9281,34 +9289,46 @@
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M128" s="3" t="inlineStr"/>
-      <c r="N128" s="4" t="n"/>
-      <c r="O128" s="3" t="inlineStr"/>
-      <c r="P128" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P128" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q128" s="3" t="inlineStr"/>
       <c r="R128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>guard_sword</t>
+          <t>yin_sha_jue</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>御剑守心</t>
+          <t>引煞诀</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9316,17 +9336,17 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -9336,24 +9356,24 @@
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(sha_qi)</t>
         </is>
       </c>
       <c r="N129" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="4" t="n"/>
@@ -9363,12 +9383,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
+          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>sword_blade_embryo</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9378,7 +9398,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>剑胎初鸣</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9386,12 +9406,12 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -9411,20 +9431,14 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M130" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N130" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr"/>
+      <c r="N130" s="4" t="n"/>
       <c r="O130" s="3" t="inlineStr"/>
       <c r="P130" s="4" t="n"/>
       <c r="Q130" s="3" t="inlineStr"/>
@@ -9433,12 +9447,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
+          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>sword_breath_return</t>
+          <t>guard_sword</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9448,7 +9462,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>回风纳息</t>
+          <t>御剑守心</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9476,20 +9490,20 @@
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
-        </is>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N131" s="4" t="n">
@@ -9503,12 +9517,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_cut</t>
+          <t>sword_blade_embryo</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9518,7 +9532,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>云隙递剑</t>
+          <t>剑胎初鸣</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9526,12 +9540,12 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -9551,15 +9565,15 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N132" s="4" t="n">
@@ -9573,12 +9587,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_scroll</t>
+          <t>sword_breath_return</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9588,7 +9602,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>云海剑书</t>
+          <t>回风纳息</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9606,7 +9620,7 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
@@ -9625,10 +9639,16 @@
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M133" s="3" t="inlineStr"/>
-      <c r="N133" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N133" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="4" t="n"/>
       <c r="Q133" s="3" t="inlineStr"/>
@@ -9637,12 +9657,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>sword_flow_shift</t>
+          <t>sword_cloud_cut</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9652,7 +9672,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>流光换形</t>
+          <t>云隙递剑</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9660,17 +9680,17 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -9680,16 +9700,16 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9697,7 +9717,7 @@
         </is>
       </c>
       <c r="N134" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134" s="3" t="inlineStr"/>
       <c r="P134" s="4" t="n"/>
@@ -9707,12 +9727,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>sword_forge_spark</t>
+          <t>sword_cloud_scroll</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9722,7 +9742,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>炉火铸锋</t>
+          <t>云海剑书</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -9740,7 +9760,7 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -9750,25 +9770,19 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M135" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N135" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr"/>
+      <c r="N135" s="4" t="n"/>
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="4" t="n"/>
       <c r="Q135" s="3" t="inlineStr"/>
@@ -9777,12 +9791,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>sword_furnace_open</t>
+          <t>sword_flow_shift</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9792,52 +9806,52 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>剑炉大开</t>
+          <t>流光换形</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N136" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
-        </is>
-      </c>
-      <c r="L136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N136" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="4" t="n"/>
@@ -9847,12 +9861,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>sword_hidden_edge</t>
+          <t>sword_forge_spark</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9862,7 +9876,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>藏锋式</t>
+          <t>炉火铸锋</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -9890,19 +9904,25 @@
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L137" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M137" s="3" t="inlineStr"/>
-      <c r="N137" s="4" t="n"/>
+      <c r="N137" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="4" t="n"/>
       <c r="Q137" s="3" t="inlineStr"/>
@@ -9911,12 +9931,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>sword_hundred_forge</t>
+          <t>sword_furnace_open</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9926,15 +9946,15 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>百炼锋芒</t>
+          <t>剑炉大开</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -9944,7 +9964,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -9959,14 +9979,20 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L138" s="4" t="n">
+      <c r="N138" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M138" s="3" t="inlineStr"/>
-      <c r="N138" s="4" t="n"/>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="4" t="n"/>
       <c r="Q138" s="3" t="inlineStr"/>
@@ -9975,12 +10001,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>sword_iron_cleave</t>
+          <t>sword_hidden_edge</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -9990,50 +10016,46 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>斩铁成锋</t>
+          <t>藏锋式</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>状态(forge_sword)</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M139" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+      <c r="M139" s="3" t="inlineStr"/>
       <c r="N139" s="4" t="n"/>
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="4" t="n"/>
@@ -10043,12 +10065,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>sword_light_step</t>
+          <t>sword_hundred_forge</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -10058,11 +10080,11 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>剑步轻灵</t>
+          <t>百炼锋芒</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
@@ -10076,7 +10098,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -10086,25 +10108,19 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L140" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M140" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M140" s="3" t="inlineStr"/>
+      <c r="N140" s="4" t="n"/>
       <c r="O140" s="3" t="inlineStr"/>
       <c r="P140" s="4" t="n"/>
       <c r="Q140" s="3" t="inlineStr"/>
@@ -10113,12 +10129,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>sword_marrow_forge</t>
+          <t>sword_iron_cleave</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -10128,20 +10144,20 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>洗髓铸刃</t>
+          <t>斩铁成锋</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -10156,25 +10172,23 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N141" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N141" s="4" t="n"/>
       <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="4" t="n"/>
       <c r="Q141" s="3" t="inlineStr"/>
@@ -10183,12 +10197,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>sword_probe_meridian</t>
+          <t>sword_light_step</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10198,20 +10212,20 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>剑影探脉</t>
+          <t>剑步轻灵</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -10226,12 +10240,12 @@
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L142" s="4" t="n">
@@ -10245,26 +10259,20 @@
       <c r="N142" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O142" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O142" s="3" t="inlineStr"/>
+      <c r="P142" s="4" t="n"/>
       <c r="Q142" s="3" t="inlineStr"/>
       <c r="R142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>sword_ring_sheath</t>
+          <t>sword_marrow_forge</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10274,7 +10282,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>剑鸣归鞘</t>
+          <t>洗髓铸刃</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
@@ -10302,16 +10310,16 @@
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10329,12 +10337,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>sword_sky_river</t>
+          <t>sword_probe_meridian</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10344,11 +10352,11 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>天河倒卷</t>
+          <t>剑影探脉</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
@@ -10357,31 +10365,31 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -10389,22 +10397,28 @@
         </is>
       </c>
       <c r="N144" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O144" s="3" t="inlineStr"/>
-      <c r="P144" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="P144" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q144" s="3" t="inlineStr"/>
       <c r="R144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>sword_split_heaven</t>
+          <t>sword_ring_sheath</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10414,25 +10428,25 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>一剑开天</t>
+          <t>剑鸣归鞘</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -10447,18 +10461,20 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L145" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N145" s="4" t="n"/>
+          <t>状态(forge_sword)</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O145" s="3" t="inlineStr"/>
       <c r="P145" s="4" t="n"/>
       <c r="Q145" s="3" t="inlineStr"/>
@@ -10467,12 +10483,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>sword_temper_edge</t>
+          <t>sword_sky_river</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10482,11 +10498,11 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>淬锋</t>
+          <t>天河倒卷</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
@@ -10495,12 +10511,12 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
@@ -10510,7 +10526,7 @@
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -10519,14 +10535,16 @@
         </is>
       </c>
       <c r="L146" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N146" s="4" t="n"/>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O146" s="3" t="inlineStr"/>
       <c r="P146" s="4" t="n"/>
       <c r="Q146" s="3" t="inlineStr"/>
@@ -10535,12 +10553,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>sword_trial_edge</t>
+          <t>sword_split_heaven</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10550,11 +10568,11 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>试锋</t>
+          <t>一剑开天</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
@@ -10568,7 +10586,7 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -10587,16 +10605,14 @@
         </is>
       </c>
       <c r="L147" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="n"/>
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="4" t="n"/>
       <c r="Q147" s="3" t="inlineStr"/>
@@ -10605,12 +10621,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>sword_void_roam</t>
+          <t>sword_temper_edge</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10620,11 +10636,11 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>太虚游剑</t>
+          <t>淬锋</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
@@ -10638,7 +10654,7 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -10648,7 +10664,7 @@
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -10657,36 +10673,28 @@
         </is>
       </c>
       <c r="L148" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N148" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O148" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P148" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="n"/>
+      <c r="O148" s="3" t="inlineStr"/>
+      <c r="P148" s="4" t="n"/>
       <c r="Q148" s="3" t="inlineStr"/>
       <c r="R148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>sword_wash_blade</t>
+          <t>sword_trial_edge</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10696,7 +10704,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>洗剑诀</t>
+          <t>试锋</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -10704,12 +10712,12 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -10724,19 +10732,25 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M149" s="3" t="inlineStr"/>
-      <c r="N149" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>状态(forge_sword)</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="4" t="n"/>
       <c r="Q149" s="3" t="inlineStr"/>
@@ -10745,12 +10759,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>piercing_light</t>
+          <t>sword_void_roam</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10760,7 +10774,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>一线天</t>
+          <t>太虚游剑</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -10778,7 +10792,7 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
@@ -10797,30 +10811,36 @@
         </is>
       </c>
       <c r="L150" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N150" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O150" s="3" t="inlineStr"/>
-      <c r="P150" s="4" t="n"/>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P150" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>sword_blood_curse</t>
+          <t>sword_wash_blade</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10830,25 +10850,25 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>血祭剑咒</t>
+          <t>洗剑诀</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -10858,45 +10878,33 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L151" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M151" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N151" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O151" s="3" t="inlineStr">
-        <is>
-          <t>状态(bleed)</t>
-        </is>
-      </c>
-      <c r="P151" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="M151" s="3" t="inlineStr"/>
+      <c r="N151" s="4" t="n"/>
+      <c r="O151" s="3" t="inlineStr"/>
+      <c r="P151" s="4" t="n"/>
       <c r="Q151" s="3" t="inlineStr"/>
       <c r="R151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
+          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>sword_energy_charge</t>
+          <t>piercing_light</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10906,25 +10914,25 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>凝气术</t>
+          <t>一线天</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -10939,19 +10947,19 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L152" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>状态(energy_charge)</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N152" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O152" s="3" t="inlineStr"/>
       <c r="P152" s="4" t="n"/>
@@ -10961,12 +10969,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
+          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>sword_guard_formation</t>
+          <t>sword_blood_curse</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10976,61 +10984,73 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>万剑护体</t>
+          <t>血祭剑咒</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>状态(bleed)</t>
+        </is>
+      </c>
+      <c r="P153" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>状态(sword_guard)</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M153" s="3" t="inlineStr"/>
-      <c r="N153" s="4" t="n"/>
-      <c r="O153" s="3" t="inlineStr"/>
-      <c r="P153" s="4" t="n"/>
       <c r="Q153" s="3" t="inlineStr"/>
       <c r="R153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
+          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>sword_heart</t>
+          <t>sword_energy_charge</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -11040,7 +11060,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>剑心通明</t>
+          <t>凝气术</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -11048,7 +11068,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -11058,30 +11078,30 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L154" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>状态(energy_charge)</t>
         </is>
       </c>
       <c r="N154" s="4" t="n">
@@ -11095,12 +11115,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
+          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>sword_nurture</t>
+          <t>sword_guard_formation</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -11110,15 +11130,15 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>养剑诀</t>
+          <t>万剑护体</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -11128,7 +11148,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11143,7 +11163,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_intent)</t>
+          <t>状态(sword_guard)</t>
         </is>
       </c>
       <c r="L155" s="4" t="n">
@@ -11159,12 +11179,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
+          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>sword_qi_draw</t>
+          <t>sword_heart</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -11174,15 +11194,15 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>剑气引</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -11192,7 +11212,7 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -11207,15 +11227,15 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L156" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N156" s="4" t="n">
@@ -11229,12 +11249,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
+          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>sword_rain</t>
+          <t>sword_nurture</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -11244,44 +11264,44 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>剑雨</t>
+          <t>养剑诀</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>状态(sword_intent)</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="M157" s="3" t="inlineStr"/>
       <c r="N157" s="4" t="n"/>
@@ -11293,12 +11313,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>sword_shadow_strike</t>
+          <t>sword_qi_draw</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11308,7 +11328,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>瞬影剑</t>
+          <t>剑气引</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -11316,12 +11336,12 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -11331,7 +11351,7 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -11341,15 +11361,15 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L158" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="N158" s="4" t="n">
@@ -11363,12 +11383,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
+          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>sword_star_shatter</t>
+          <t>sword_rain</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -11378,7 +11398,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>碎星斩</t>
+          <t>剑雨</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
@@ -11391,12 +11411,12 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
@@ -11406,16 +11426,16 @@
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>target_status_bonus_damage_effect</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L159" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M159" s="3" t="inlineStr"/>
       <c r="N159" s="4" t="n"/>
@@ -11427,12 +11447,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
+          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>sword_wanjian</t>
+          <t>sword_shadow_strike</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -11442,47 +11462,53 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>万剑归宗</t>
+          <t>瞬影剑</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>player_status_damage_effect</t>
-        </is>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M160" s="3" t="inlineStr"/>
-      <c r="N160" s="4" t="n"/>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="3" t="inlineStr"/>
@@ -11491,12 +11517,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
+          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>sword_water_break</t>
+          <t>sword_star_shatter</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -11506,7 +11532,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>断水剑</t>
+          <t>碎星斩</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
@@ -11524,7 +11550,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -11534,25 +11560,19 @@
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>target_status_bonus_damage_effect</t>
         </is>
       </c>
       <c r="L161" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M161" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr"/>
+      <c r="N161" s="4" t="n"/>
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="4" t="n"/>
       <c r="Q161" s="3" t="inlineStr"/>
@@ -11561,12 +11581,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>sword_wind_return</t>
+          <t>sword_wanjian</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -11576,11 +11596,11 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>回风剑</t>
+          <t>万剑归宗</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
@@ -11594,7 +11614,7 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -11604,25 +11624,19 @@
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>player_status_damage_effect</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M162" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N162" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr"/>
+      <c r="N162" s="4" t="n"/>
       <c r="O162" s="3" t="inlineStr"/>
       <c r="P162" s="4" t="n"/>
       <c r="Q162" s="3" t="inlineStr"/>
@@ -11631,35 +11645,35 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ash_heart_guard.tres</t>
+          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ash_heart_guard</t>
+          <t>sword_water_break</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>灰烬护心</t>
+          <t>断水剑</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -11674,19 +11688,25 @@
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L163" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M163" s="3" t="inlineStr"/>
-      <c r="N163" s="4" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O163" s="3" t="inlineStr"/>
       <c r="P163" s="4" t="n"/>
       <c r="Q163" s="3" t="inlineStr"/>
@@ -11695,22 +11715,22 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>common_cards/circulating_breath.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>circulating_breath</t>
+          <t>sword_wind_return</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>周天吐纳</t>
+          <t>回风剑</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -11718,12 +11738,12 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -11738,24 +11758,24 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
           <t>护体</t>
         </is>
       </c>
-      <c r="L164" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M164" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
       <c r="N164" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O164" s="3" t="inlineStr"/>
       <c r="P164" s="4" t="n"/>
@@ -11765,12 +11785,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>common_cards/ash_heart_guard.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>ash_heart_guard</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11780,7 +11800,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>灰烬护心</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -11798,7 +11818,7 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -11813,11 +11833,11 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L165" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="4" t="n"/>
@@ -11829,12 +11849,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/discard_aegis.tres</t>
+          <t>common_cards/circulating_breath.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>discard_aegis</t>
+          <t>circulating_breath</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11844,7 +11864,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>弃念成罡</t>
+          <t>周天吐纳</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -11862,7 +11882,7 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
@@ -11877,14 +11897,20 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L166" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M166" s="3" t="inlineStr"/>
-      <c r="N166" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O166" s="3" t="inlineStr"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="3" t="inlineStr"/>
@@ -11893,12 +11919,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/embers_return.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>embers_return</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11908,7 +11934,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>烬归灵台</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -11926,12 +11952,12 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -11945,16 +11971,10 @@
         </is>
       </c>
       <c r="L167" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M167" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N167" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="4" t="n"/>
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -11963,12 +11983,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/flowing_cloud_guard.tres</t>
+          <t>common_cards/discard_aegis.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>flowing_cloud_guard</t>
+          <t>discard_aegis</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11978,7 +11998,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>流云护身</t>
+          <t>弃念成罡</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -11996,7 +12016,7 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -12014,7 +12034,9 @@
           <t>计数增幅</t>
         </is>
       </c>
-      <c r="L168" s="4" t="n"/>
+      <c r="L168" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="M168" s="3" t="inlineStr"/>
       <c r="N168" s="4" t="n"/>
       <c r="O168" s="3" t="inlineStr"/>
@@ -12025,12 +12047,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>common_cards/embers_return.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>embers_return</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12040,7 +12062,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>烬归灵台</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12048,22 +12070,22 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -12073,11 +12095,11 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L169" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -12085,7 +12107,7 @@
         </is>
       </c>
       <c r="N169" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O169" s="3" t="inlineStr"/>
       <c r="P169" s="4" t="n"/>
@@ -12095,12 +12117,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>common_cards/momentum_pursuit.tres</t>
+          <t>common_cards/flowing_cloud_guard.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>momentum_pursuit</t>
+          <t>flowing_cloud_guard</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12110,7 +12132,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>乘势追击</t>
+          <t>流云护身</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12118,12 +12140,12 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -12146,9 +12168,7 @@
           <t>计数增幅</t>
         </is>
       </c>
-      <c r="L170" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="L170" s="4" t="n"/>
       <c r="M170" s="3" t="inlineStr"/>
       <c r="N170" s="4" t="n"/>
       <c r="O170" s="3" t="inlineStr"/>
@@ -12159,12 +12179,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>common_cards/ink_flow_slash.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>ink_flow_slash</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -12174,7 +12194,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>墨流斩</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12211,15 +12231,15 @@
         </is>
       </c>
       <c r="L171" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N171" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="4" t="n"/>
@@ -12229,12 +12249,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>common_cards/returning_light.tres</t>
+          <t>common_cards/momentum_pursuit.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>returning_light</t>
+          <t>momentum_pursuit</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12244,7 +12264,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>回光返照</t>
+          <t>乘势追击</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -12252,12 +12272,12 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -12267,7 +12287,7 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -12277,11 +12297,11 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L172" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M172" s="3" t="inlineStr"/>
       <c r="N172" s="4" t="n"/>
@@ -12293,12 +12313,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>common_cards/spirit_stone_needle.tres</t>
+          <t>common_cards/muscle_resonance_strike.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>spirit_stone_needle</t>
+          <t>muscle_resonance_strike</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -12308,11 +12328,11 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>灵石飞针</t>
+          <t>劲气共鸣</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
@@ -12331,7 +12351,7 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -12345,10 +12365,16 @@
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M173" s="3" t="inlineStr"/>
-      <c r="N173" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -12357,12 +12383,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/blood_debt_curse.tres</t>
+          <t>common_cards/returning_light.tres</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>blood_debt_curse</t>
+          <t>returning_light</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -12372,11 +12398,11 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>血债</t>
+          <t>回光返照</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
@@ -12390,12 +12416,12 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -12405,11 +12431,11 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L174" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="4" t="n"/>
@@ -12421,12 +12447,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/spirit_stone_needle.tres</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>spirit_stone_needle</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -12436,7 +12462,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>灵石飞针</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
@@ -12444,12 +12470,12 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -12459,7 +12485,7 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -12467,8 +12493,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="4" t="n"/>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M175" s="3" t="inlineStr"/>
       <c r="N175" s="4" t="n"/>
       <c r="O175" s="3" t="inlineStr"/>
@@ -12479,12 +12511,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -12494,7 +12526,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -12525,8 +12557,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K176" s="3" t="inlineStr"/>
-      <c r="L176" s="4" t="n"/>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M176" s="3" t="inlineStr"/>
       <c r="N176" s="4" t="n"/>
       <c r="O176" s="3" t="inlineStr"/>
@@ -12537,12 +12575,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/karmic_fire_curse.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>karmic_fire_curse</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -12552,11 +12590,11 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
@@ -12575,7 +12613,7 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -12583,14 +12621,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="K177" s="3" t="inlineStr"/>
+      <c r="L177" s="4" t="n"/>
       <c r="M177" s="3" t="inlineStr"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="3" t="inlineStr"/>
@@ -12601,12 +12633,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -12616,7 +12648,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -12659,12 +12691,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>karmic_fire_curse</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -12674,7 +12706,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
@@ -12682,12 +12714,12 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -12697,7 +12729,7 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
@@ -12707,11 +12739,11 @@
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L179" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="4" t="n"/>
@@ -12723,12 +12755,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/status/underworld_writ.tres</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>underworld_writ</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -12738,11 +12770,11 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>判牒</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
@@ -12761,7 +12793,7 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -12781,22 +12813,22 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/strike.tres</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>strike</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
@@ -12814,7 +12846,7 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -12835,14 +12867,8 @@
       <c r="L181" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M181" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N181" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="M181" s="3" t="inlineStr"/>
+      <c r="N181" s="4" t="n"/>
       <c r="O181" s="3" t="inlineStr"/>
       <c r="P181" s="4" t="n"/>
       <c r="Q181" s="3" t="inlineStr"/>
@@ -12851,22 +12877,22 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>common_cards/toxin.tres</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -12874,45 +12900,33 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M182" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="3" t="inlineStr"/>
+      <c r="N182" s="4" t="n"/>
       <c r="O182" s="3" t="inlineStr"/>
       <c r="P182" s="4" t="n"/>
       <c r="Q182" s="3" t="inlineStr"/>
@@ -12921,12 +12935,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>fusion_cards/attack_guard_unity.tres</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>attack_guard_unity</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -12936,11 +12950,11 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>攻守合一</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
@@ -12949,12 +12963,12 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -12964,7 +12978,7 @@
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -12973,15 +12987,15 @@
         </is>
       </c>
       <c r="L183" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N183" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O183" s="3" t="inlineStr"/>
       <c r="P183" s="4" t="n"/>
@@ -12991,12 +13005,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>fusion_cards/blood_beast_rend.tres</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>blood_beast_rend</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -13006,7 +13020,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>血兽撕咬</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -13034,7 +13048,7 @@
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -13043,42 +13057,182 @@
         </is>
       </c>
       <c r="L184" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N184" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O184" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P184" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O184" s="3" t="inlineStr"/>
+      <c r="P184" s="4" t="n"/>
       <c r="Q184" s="3" t="inlineStr"/>
       <c r="R184" s="4" t="n"/>
     </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>demon_rain_swordfire</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>魔雨剑火</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>全体敌</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O185" s="3" t="inlineStr"/>
+      <c r="P185" s="4" t="n"/>
+      <c r="Q185" s="3" t="inlineStr"/>
+      <c r="R185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O186" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q186" s="3" t="inlineStr"/>
+      <c r="R186" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R186"/>
+  <dimension ref="A1:R187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4619,12 +4619,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_calamity_embryo.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_burn_impurity.tres</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>demon_calamity_embryo</t>
+          <t>demon_burn_impurity</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>劫火魔胎</t>
+          <t>焚秽诀</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -4667,44 +4667,34 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>焚化污染</t>
         </is>
       </c>
       <c r="N60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>延迟施放</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="3" t="inlineStr"/>
       <c r="R60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_calamity_embryo.tres</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>demon_defend</t>
+          <t>demon_calamity_embryo</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4714,7 +4704,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>劫火魔胎</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4732,43 +4722,59 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="4" t="n"/>
-      <c r="O61" s="3" t="inlineStr"/>
-      <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="R61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>demon_desperate_burst</t>
+          <t>demon_defend</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4778,44 +4784,44 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>绝命爆发</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="4" t="n"/>
@@ -4827,12 +4833,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>demon_flame</t>
+          <t>demon_desperate_burst</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4842,7 +4848,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>魔焰燎原</t>
+          <t>绝命爆发</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -4855,17 +4861,17 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -4875,20 +4881,14 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L63" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="4" t="n"/>
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="3" t="inlineStr"/>
@@ -4897,12 +4897,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_black</t>
+          <t>demon_flame</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>魔焰黑·噬血</t>
+          <t>魔焰燎原</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4940,30 +4940,26 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
           <t>自损</t>
         </is>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+      <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="3" t="inlineStr"/>
       <c r="R64" s="4" t="n"/>
@@ -4971,12 +4967,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_blue</t>
+          <t>demon_flame_black</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4986,7 +4982,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>魔焰蓝·灵涌</t>
+          <t>魔焰黑·噬血</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -4994,12 +4990,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5009,7 +5005,7 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -5019,19 +5015,25 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L65" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n"/>
-      <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="3" t="inlineStr"/>
       <c r="R65" s="4" t="n"/>
@@ -5039,12 +5041,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_green</t>
+          <t>demon_flame_blue</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5054,7 +5056,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>魔焰绿·镇煞</t>
+          <t>魔焰蓝·灵涌</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -5077,7 +5079,7 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -5087,11 +5089,17 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="4" t="n"/>
@@ -5101,12 +5109,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_heart</t>
+          <t>demon_flame_green</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5116,20 +5124,20 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>魔焰焚心</t>
+          <t>魔焰绿·镇煞</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5144,25 +5152,17 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="3" t="inlineStr"/>
@@ -5171,12 +5171,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_purple</t>
+          <t>demon_flame_heart</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>魔焰紫·蚀魂</t>
+          <t>魔焰焚心</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -5214,30 +5214,26 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
           <t>状态(exposed)</t>
         </is>
       </c>
-      <c r="L68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
       <c r="N68" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="3" t="inlineStr"/>
       <c r="R68" s="4" t="n"/>
@@ -5245,12 +5241,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_red</t>
+          <t>demon_flame_purple</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5260,11 +5256,11 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>魔焰红·焚界</t>
+          <t>魔焰紫·蚀魂</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -5273,12 +5269,12 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -5293,19 +5289,25 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="L69" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="N69" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
         <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="3" t="inlineStr"/>
       <c r="R69" s="4" t="n"/>
@@ -5313,12 +5315,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_white</t>
+          <t>demon_flame_red</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5328,11 +5330,11 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>魔焰白·护魂</t>
+          <t>魔焰红·焚界</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
@@ -5341,12 +5343,12 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -5365,21 +5367,15 @@
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="4" t="n"/>
@@ -5387,12 +5383,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_yellow</t>
+          <t>demon_flame_white</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5402,7 +5398,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>魔焰黄·狂烬</t>
+          <t>魔焰白·护魂</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -5410,17 +5406,17 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -5435,13 +5431,25 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="4" t="n"/>
-      <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="3" t="inlineStr"/>
       <c r="R71" s="4" t="n"/>
@@ -5449,12 +5457,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>demon_flesh_rebirth</t>
+          <t>demon_flame_yellow</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5464,7 +5472,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>血肉重生</t>
+          <t>魔焰黄·狂烬</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -5482,35 +5490,27 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="N72" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="4" t="n"/>
       <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="3" t="inlineStr"/>
@@ -5519,12 +5519,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_archive</t>
+          <t>demon_flesh_rebirth</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5534,11 +5534,11 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>窥心魔典</t>
+          <t>血肉重生</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -5567,14 +5567,20 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>configured_discover_effect</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -5583,12 +5589,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_lurking_soul_curse.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>demon_lurking_soul_curse</t>
+          <t>demon_forbidden_archive</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5598,11 +5604,11 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>伏魂咒</t>
+          <t>窥心魔典</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
@@ -5611,17 +5617,17 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -5631,25 +5637,15 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>configured_discover_effect</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>延迟施放</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="3" t="inlineStr"/>
       <c r="R74" s="4" t="n"/>
@@ -5657,12 +5653,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_lurking_soul_curse.tres</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_marks_return</t>
+          <t>demon_lurking_soul_curse</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5672,30 +5668,30 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>万印归墟</t>
+          <t>伏魂咒</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5705,13 +5701,25 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="3" t="inlineStr"/>
-      <c r="N75" s="4" t="n"/>
-      <c r="O75" s="3" t="inlineStr"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="3" t="inlineStr"/>
       <c r="R75" s="4" t="n"/>
@@ -5719,12 +5727,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_devour</t>
+          <t>demon_myriad_marks_return</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -5734,11 +5742,11 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>万魂噬天</t>
+          <t>万印归墟</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
@@ -5752,7 +5760,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -5767,20 +5775,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="3" t="inlineStr"/>
@@ -5789,12 +5789,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>demon_seven_flame_cycle</t>
+          <t>demon_myriad_soul_devour</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5804,30 +5804,30 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>七焰回环</t>
+          <t>万魂噬天</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -5837,12 +5837,20 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -5851,12 +5859,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_blade</t>
+          <t>demon_seven_flame_cycle</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5866,25 +5874,25 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>煞刃</t>
+          <t>七焰回环</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5899,7 +5907,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>耗煞伤害</t>
+          <t>configured_flame_effect</t>
         </is>
       </c>
       <c r="L78" s="4" t="n"/>
@@ -5913,12 +5921,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>demon_shadow_reenactment</t>
+          <t>demon_sha_blade</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5928,30 +5936,30 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>魔影复刻</t>
+          <t>煞刃</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5961,7 +5969,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>复刻</t>
+          <t>耗煞伤害</t>
         </is>
       </c>
       <c r="L79" s="4" t="n"/>
@@ -5975,12 +5983,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>demon_shatter_soul_seal</t>
+          <t>demon_shadow_reenactment</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5990,7 +5998,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>碎魂印</t>
+          <t>魔影复刻</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -6003,40 +6011,32 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>复刻</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="4" t="n"/>
       <c r="O80" s="3" t="inlineStr"/>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="3" t="inlineStr"/>
@@ -6045,12 +6045,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_devour_claw</t>
+          <t>demon_shatter_soul_seal</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>噬魂爪</t>
+          <t>碎魂印</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="L81" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="N81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="4" t="n"/>
@@ -6115,12 +6115,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_lamp_renewal</t>
+          <t>demon_soul_devour_claw</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>魂灯续燃</t>
+          <t>噬魂爪</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -6163,38 +6163,34 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="4" t="n"/>
       <c r="Q82" s="3" t="inlineStr"/>
       <c r="R82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>demon_strike</t>
+          <t>demon_soul_lamp_renewal</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6204,7 +6200,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>魂灯续燃</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -6212,7 +6208,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6222,43 +6218,53 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M83" s="3" t="inlineStr"/>
-      <c r="N83" s="4" t="n"/>
-      <c r="O83" s="3" t="inlineStr"/>
-      <c r="P83" s="4" t="n"/>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q83" s="3" t="inlineStr"/>
       <c r="R83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_membrane</t>
+          <t>demon_strike</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6268,7 +6274,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>血膜</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -6276,17 +6282,17 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -6296,30 +6302,20 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N84" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="3" t="inlineStr"/>
       <c r="R84" s="4" t="n"/>
@@ -6327,12 +6323,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_qi_guard</t>
+          <t>demon_blood_membrane</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6342,7 +6338,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>血气护体</t>
+          <t>血膜</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -6360,7 +6356,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -6375,13 +6371,25 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
           <t>configured_demonic_engine_effect</t>
         </is>
       </c>
-      <c r="L85" s="4" t="n"/>
-      <c r="M85" s="3" t="inlineStr"/>
-      <c r="N85" s="4" t="n"/>
-      <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="3" t="inlineStr"/>
       <c r="R85" s="4" t="n"/>
@@ -6389,12 +6397,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_recompense</t>
+          <t>demon_blood_qi_guard</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6404,11 +6412,11 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>血偿万道</t>
+          <t>血气护体</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
@@ -6422,7 +6430,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -6451,12 +6459,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_boundless</t>
+          <t>demon_blood_recompense</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6466,20 +6474,20 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>血海无量</t>
+          <t>血偿万道</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6499,15 +6507,11 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>configured_x_cost_self_damage_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L87" s="4" t="n"/>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>configured_x_cost_damage_effect</t>
-        </is>
-      </c>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="4" t="n"/>
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="4" t="n"/>
@@ -6517,12 +6521,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>demon_bloodthirst</t>
+          <t>demon_blood_sea_boundless</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6532,25 +6536,25 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>嗜血成性</t>
+          <t>血海无量</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -6565,11 +6569,15 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_x_cost_self_damage_effect</t>
         </is>
       </c>
       <c r="L88" s="4" t="n"/>
-      <c r="M88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>configured_x_cost_damage_effect</t>
+        </is>
+      </c>
       <c r="N88" s="4" t="n"/>
       <c r="O88" s="3" t="inlineStr"/>
       <c r="P88" s="4" t="n"/>
@@ -6579,12 +6587,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_breath</t>
+          <t>demon_bloodthirst</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6594,7 +6602,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>焰息</t>
+          <t>嗜血成性</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
@@ -6602,7 +6610,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6622,25 +6630,17 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="4" t="n"/>
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="3" t="inlineStr"/>
@@ -6649,12 +6649,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_continuity</t>
+          <t>demon_flame_breath</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>焰心承续</t>
+          <t>焰息</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6697,12 +6697,20 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="3" t="inlineStr"/>
-      <c r="N90" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O90" s="3" t="inlineStr"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="3" t="inlineStr"/>
@@ -6711,12 +6719,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_refining</t>
+          <t>demon_flame_continuity</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6726,7 +6734,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>炼焰术</t>
+          <t>焰心承续</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -6744,7 +6752,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -6754,7 +6762,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -6773,12 +6781,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_burn_sky</t>
+          <t>demon_flame_refining</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6788,30 +6796,30 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>万魂焚天</t>
+          <t>炼焰术</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -6821,7 +6829,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L92" s="4" t="n"/>
@@ -6835,12 +6843,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_nurture</t>
+          <t>demon_myriad_soul_burn_sky</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6850,40 +6858,40 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>养煞</t>
+          <t>万魂焚天</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L93" s="4" t="n"/>
@@ -6897,12 +6905,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_return</t>
+          <t>demon_sha_nurture</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6912,15 +6920,15 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>归煞</t>
+          <t>养煞</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -6930,12 +6938,12 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -6945,18 +6953,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>configured_consume_status_to_block_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L94" s="4" t="n"/>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="N94" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="4" t="n"/>
       <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="3" t="inlineStr"/>
@@ -6965,12 +6967,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_banner</t>
+          <t>demon_sha_return</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6980,11 +6982,11 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>引魂幡</t>
+          <t>归煞</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
@@ -6993,17 +6995,17 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -7013,15 +7015,13 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_consume_status_to_block_effect</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="n"/>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N95" s="4" t="n">
@@ -7035,12 +7035,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_echo</t>
+          <t>demon_soul_banner</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7050,45 +7050,53 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>噬魂回响</t>
+          <t>引魂幡</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>暗金</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="n"/>
-      <c r="M96" s="3" t="inlineStr"/>
-      <c r="N96" s="4" t="n"/>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O96" s="3" t="inlineStr"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="3" t="inlineStr"/>
@@ -7097,12 +7105,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_flame_cycle</t>
+          <t>demon_soul_echo</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7112,11 +7120,11 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>魂火相济</t>
+          <t>噬魂回响</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
@@ -7130,7 +7138,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -7140,7 +7148,7 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -7159,12 +7167,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_mark_sense</t>
+          <t>demon_soul_flame_cycle</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7174,7 +7182,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>魂印感应</t>
+          <t>魂火相济</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7192,7 +7200,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -7202,7 +7210,7 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -7221,12 +7229,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_rite</t>
+          <t>demon_soul_mark_sense</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7236,7 +7244,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>夺魂仪</t>
+          <t>魂印感应</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -7254,7 +7262,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -7283,12 +7291,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>forbidden_mantra</t>
+          <t>demon_soul_rite</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7298,7 +7306,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>禁咒入魔</t>
+          <t>夺魂仪</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -7316,7 +7324,7 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -7326,25 +7334,17 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="3" t="inlineStr"/>
+      <c r="N100" s="4" t="n"/>
       <c r="O100" s="3" t="inlineStr"/>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="3" t="inlineStr"/>
@@ -7353,12 +7353,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
+          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>hun_kai</t>
+          <t>forbidden_mantra</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>魂铠</t>
+          <t>禁咒入魔</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -7396,22 +7396,24 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N101" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="4" t="n"/>
@@ -7421,12 +7423,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>hun_zang</t>
+          <t>hun_kai</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7436,15 +7438,15 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>魂葬</t>
+          <t>魂铠</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -7454,7 +7456,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -7469,12 +7471,18 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_soul_mark_consume_effect</t>
         </is>
       </c>
       <c r="L102" s="4" t="n"/>
-      <c r="M102" s="3" t="inlineStr"/>
-      <c r="N102" s="4" t="n"/>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="O102" s="3" t="inlineStr"/>
       <c r="P102" s="4" t="n"/>
       <c r="Q102" s="3" t="inlineStr"/>
@@ -7483,12 +7491,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>ju_sha</t>
+          <t>hun_zang</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7498,25 +7506,25 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>聚煞</t>
+          <t>魂葬</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -7531,20 +7539,12 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L103" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>状态(sha_qi)</t>
-        </is>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="3" t="inlineStr"/>
+      <c r="N103" s="4" t="n"/>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="4" t="n"/>
       <c r="Q103" s="3" t="inlineStr"/>
@@ -7553,12 +7553,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
+          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>lie_hun</t>
+          <t>ju_sha</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7568,20 +7568,20 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>裂魂</t>
+          <t>聚煞</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -7601,12 +7601,20 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="n"/>
-      <c r="M104" s="3" t="inlineStr"/>
-      <c r="N104" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="3" t="inlineStr"/>
@@ -7615,12 +7623,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
+          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>demon_black_contract</t>
+          <t>lie_hun</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7630,7 +7638,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>黑契</t>
+          <t>裂魂</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
@@ -7638,12 +7646,12 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -7658,25 +7666,17 @@
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L105" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
-        </is>
-      </c>
-      <c r="N105" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="3" t="inlineStr"/>
+      <c r="N105" s="4" t="n"/>
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="3" t="inlineStr"/>
@@ -7685,12 +7685,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_oath</t>
+          <t>demon_black_contract</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7700,20 +7700,20 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>血誓</t>
+          <t>黑契</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -7733,19 +7733,19 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N106" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O106" s="3" t="inlineStr"/>
       <c r="P106" s="4" t="n"/>
@@ -7755,12 +7755,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea</t>
+          <t>demon_blood_oath</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7770,52 +7770,52 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>血海翻涌</t>
+          <t>血誓</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L107" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N107" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="4" t="n"/>
@@ -7825,12 +7825,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_self_heaven</t>
+          <t>demon_blood_sea</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7840,11 +7840,11 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>焚身问天</t>
+          <t>血海翻涌</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
@@ -7858,17 +7858,17 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
@@ -7877,36 +7877,30 @@
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N108" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O108" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="P108" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O108" s="3" t="inlineStr"/>
+      <c r="P108" s="4" t="n"/>
       <c r="Q108" s="3" t="inlineStr"/>
       <c r="R108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>demon_cut_soul</t>
+          <t>demon_burn_self_heaven</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7916,11 +7910,11 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>割魂刃</t>
+          <t>焚身问天</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
@@ -7929,17 +7923,17 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -7949,34 +7943,40 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N109" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O109" s="3" t="inlineStr"/>
-      <c r="P109" s="4" t="n"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q109" s="3" t="inlineStr"/>
       <c r="R109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_power</t>
+          <t>demon_cut_soul</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>禁咒开脉</t>
+          <t>割魂刃</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -8019,40 +8019,34 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M110" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N110" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O110" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O110" s="3" t="inlineStr"/>
+      <c r="P110" s="4" t="n"/>
       <c r="Q110" s="3" t="inlineStr"/>
       <c r="R110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>demon_ghost_hook</t>
+          <t>demon_forbidden_power</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -8062,7 +8056,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>幽钩</t>
+          <t>禁咒开脉</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -8070,17 +8064,17 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -8090,20 +8084,20 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L111" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N111" s="4" t="n">
@@ -8111,7 +8105,7 @@
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="P111" s="4" t="n">
@@ -8123,12 +8117,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>demon_hell_soul_seal</t>
+          <t>demon_ghost_hook</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8138,11 +8132,11 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>幽冥万魂印</t>
+          <t>幽钩</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
@@ -8151,12 +8145,12 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -8166,7 +8160,7 @@
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -8175,30 +8169,36 @@
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N112" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O112" s="3" t="inlineStr"/>
-      <c r="P112" s="4" t="n"/>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P112" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q112" s="3" t="inlineStr"/>
       <c r="R112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>demon_hundred_ghosts</t>
+          <t>demon_hell_soul_seal</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>百鬼留痕</t>
+          <t>幽冥万魂印</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -8241,17 +8241,19 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L113" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N113" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="4" t="n"/>
@@ -8261,12 +8263,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>demon_lantern_shadow</t>
+          <t>demon_hundred_ghosts</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8276,25 +8278,25 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>灯影噬魂</t>
+          <t>百鬼留痕</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -8309,19 +8311,17 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n"/>
       <c r="M114" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="4" t="n"/>
@@ -8331,12 +8331,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>demon_life_for_mana</t>
+          <t>demon_lantern_shadow</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8346,11 +8346,11 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>命换灵机</t>
+          <t>灯影噬魂</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -8379,15 +8379,15 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N115" s="4" t="n">
@@ -8401,12 +8401,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>demon_mark_bloom</t>
+          <t>demon_life_for_mana</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8416,52 +8416,52 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>印开彼岸</t>
+          <t>命换灵机</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="L116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M116" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N116" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O116" s="3" t="inlineStr"/>
       <c r="P116" s="4" t="n"/>
@@ -8471,12 +8471,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>demon_sacrificial_flame</t>
+          <t>demon_mark_bloom</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8486,25 +8486,25 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>祭焰</t>
+          <t>印开彼岸</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -8514,24 +8514,24 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L117" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N117" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="4" t="n"/>
@@ -8541,12 +8541,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_armor</t>
+          <t>demon_sacrificial_flame</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>魂衣</t>
+          <t>祭焰</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -8584,24 +8584,24 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" s="3" t="inlineStr"/>
       <c r="P118" s="4" t="n"/>
@@ -8611,12 +8611,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_price</t>
+          <t>demon_soul_armor</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -8626,15 +8626,15 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>以魂为价</t>
+          <t>魂衣</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -8654,45 +8654,39 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L119" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N119" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O119" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P119" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O119" s="3" t="inlineStr"/>
+      <c r="P119" s="4" t="n"/>
       <c r="Q119" s="3" t="inlineStr"/>
       <c r="R119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_prison</t>
+          <t>demon_soul_price</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -8702,7 +8696,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>万魂牢</t>
+          <t>以魂为价</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -8710,17 +8704,17 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -8730,33 +8724,45 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M120" s="3" t="inlineStr"/>
-      <c r="N120" s="4" t="n"/>
-      <c r="O120" s="3" t="inlineStr"/>
-      <c r="P120" s="4" t="n"/>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P120" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q120" s="3" t="inlineStr"/>
       <c r="R120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_siphon</t>
+          <t>demon_soul_prison</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -8766,25 +8772,25 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>摄魂归元</t>
+          <t>万魂牢</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -8794,45 +8800,33 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M121" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O121" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P121" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr"/>
+      <c r="N121" s="4" t="n"/>
+      <c r="O121" s="3" t="inlineStr"/>
+      <c r="P121" s="4" t="n"/>
       <c r="Q121" s="3" t="inlineStr"/>
       <c r="R121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_stamp</t>
+          <t>demon_soul_siphon</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8842,7 +8836,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>魂印</t>
+          <t>摄魂归元</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -8860,7 +8854,7 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -8870,7 +8864,7 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
@@ -8883,26 +8877,32 @@
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O122" s="3" t="inlineStr"/>
-      <c r="P122" s="4" t="n"/>
+      <c r="P122" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q122" s="3" t="inlineStr"/>
       <c r="R122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>demon_spirit_net</t>
+          <t>demon_soul_stamp</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>缚魂网</t>
+          <t>魂印</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -8940,16 +8940,16 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L123" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8967,12 +8967,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>demon_ten_thousand_sacrifice</t>
+          <t>demon_spirit_net</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8982,15 +8982,15 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>万祭归一</t>
+          <t>缚魂网</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -9000,34 +9000,34 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N124" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O124" s="3" t="inlineStr"/>
       <c r="P124" s="4" t="n"/>
@@ -9037,12 +9037,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>san_hun_tong_fen</t>
+          <t>demon_ten_thousand_sacrifice</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>三魂同焚</t>
+          <t>万祭归一</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -9070,27 +9070,35 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L125" s="4" t="n"/>
-      <c r="M125" s="3" t="inlineStr"/>
-      <c r="N125" s="4" t="n"/>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="4" t="n"/>
       <c r="Q125" s="3" t="inlineStr"/>
@@ -9099,12 +9107,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
+          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>shadow_step</t>
+          <t>san_hun_tong_fen</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -9114,20 +9122,20 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>影遁</t>
+          <t>三魂同焚</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -9137,22 +9145,20 @@
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="n"/>
       <c r="M126" s="3" t="inlineStr"/>
       <c r="N126" s="4" t="n"/>
       <c r="O126" s="3" t="inlineStr"/>
@@ -9163,12 +9169,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
+          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>she_hun_xu_yuan</t>
+          <t>shadow_step</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -9178,7 +9184,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>摄魂续元</t>
+          <t>影遁</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
@@ -9191,7 +9197,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -9201,48 +9207,38 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="n"/>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P127" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="4" t="n"/>
+      <c r="O127" s="3" t="inlineStr"/>
+      <c r="P127" s="4" t="n"/>
       <c r="Q127" s="3" t="inlineStr"/>
       <c r="R127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
+          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>soul_drain</t>
+          <t>she_hun_xu_yuan</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9252,7 +9248,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>摄魂</t>
+          <t>摄魂续元</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9260,7 +9256,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -9270,7 +9266,7 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
@@ -9280,28 +9276,26 @@
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L128" s="4" t="n">
-        <v>5</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="n"/>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="N128" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="P128" s="4" t="n">
@@ -9313,12 +9307,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
+          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>yin_sha_jue</t>
+          <t>soul_drain</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9328,7 +9322,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>引煞诀</t>
+          <t>摄魂</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9346,7 +9340,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -9356,7 +9350,7 @@
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
@@ -9365,40 +9359,46 @@
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N129" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O129" s="3" t="inlineStr"/>
-      <c r="P129" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P129" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q129" s="3" t="inlineStr"/>
       <c r="R129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>yin_sha_jue</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>引煞诀</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -9437,8 +9437,14 @@
       <c r="L130" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M130" s="3" t="inlineStr"/>
-      <c r="N130" s="4" t="n"/>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O130" s="3" t="inlineStr"/>
       <c r="P130" s="4" t="n"/>
       <c r="Q130" s="3" t="inlineStr"/>
@@ -9447,12 +9453,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
+          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>guard_sword</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9462,7 +9468,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>御剑守心</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9470,12 +9476,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -9495,20 +9501,14 @@
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N131" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr"/>
+      <c r="N131" s="4" t="n"/>
       <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="4" t="n"/>
       <c r="Q131" s="3" t="inlineStr"/>
@@ -9517,12 +9517,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
+          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>sword_blade_embryo</t>
+          <t>guard_sword</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>剑胎初鸣</t>
+          <t>御剑守心</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -9565,15 +9565,15 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N132" s="4" t="n">
@@ -9587,12 +9587,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>sword_breath_return</t>
+          <t>sword_blade_embryo</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>回风纳息</t>
+          <t>剑胎初鸣</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="L133" s="4" t="n">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N133" s="4" t="n">
@@ -9657,12 +9657,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_cut</t>
+          <t>sword_breath_return</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>云隙递剑</t>
+          <t>回风纳息</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -9700,20 +9700,20 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N134" s="4" t="n">
@@ -9727,12 +9727,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_scroll</t>
+          <t>sword_cloud_cut</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>云海剑书</t>
+          <t>云隙递剑</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -9770,19 +9770,25 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L135" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M135" s="3" t="inlineStr"/>
-      <c r="N135" s="4" t="n"/>
+      <c r="N135" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="4" t="n"/>
       <c r="Q135" s="3" t="inlineStr"/>
@@ -9791,12 +9797,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>sword_flow_shift</t>
+          <t>sword_cloud_scroll</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9806,7 +9812,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>流光换形</t>
+          <t>云海剑书</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -9839,20 +9845,14 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L136" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N136" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="M136" s="3" t="inlineStr"/>
+      <c r="N136" s="4" t="n"/>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="4" t="n"/>
       <c r="Q136" s="3" t="inlineStr"/>
@@ -9861,12 +9861,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>sword_forge_spark</t>
+          <t>sword_flow_shift</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>炉火铸锋</t>
+          <t>流光换形</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -9913,15 +9913,15 @@
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N137" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="4" t="n"/>
@@ -9931,12 +9931,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>sword_furnace_open</t>
+          <t>sword_forge_spark</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9946,15 +9946,15 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>剑炉大开</t>
+          <t>炉火铸锋</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -9979,11 +9979,11 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="N138" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="4" t="n"/>
@@ -10001,12 +10001,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>sword_hidden_edge</t>
+          <t>sword_furnace_open</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -10016,15 +10016,15 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>藏锋式</t>
+          <t>剑炉大开</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -10044,19 +10044,25 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L139" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M139" s="3" t="inlineStr"/>
-      <c r="N139" s="4" t="n"/>
+      <c r="N139" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="4" t="n"/>
       <c r="Q139" s="3" t="inlineStr"/>
@@ -10065,12 +10071,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>sword_hundred_forge</t>
+          <t>sword_hidden_edge</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -10080,7 +10086,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>百炼锋芒</t>
+          <t>藏锋式</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -10098,7 +10104,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -10108,7 +10114,7 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -10117,7 +10123,7 @@
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M140" s="3" t="inlineStr"/>
       <c r="N140" s="4" t="n"/>
@@ -10129,12 +10135,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>sword_iron_cleave</t>
+          <t>sword_hundred_forge</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -10144,20 +10150,20 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>斩铁成锋</t>
+          <t>百炼锋芒</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -10172,22 +10178,18 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M141" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr"/>
       <c r="N141" s="4" t="n"/>
       <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="4" t="n"/>
@@ -10197,12 +10199,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>sword_light_step</t>
+          <t>sword_iron_cleave</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10212,25 +10214,25 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>剑步轻灵</t>
+          <t>斩铁成锋</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -10240,25 +10242,23 @@
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L142" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N142" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N142" s="4" t="n"/>
       <c r="O142" s="3" t="inlineStr"/>
       <c r="P142" s="4" t="n"/>
       <c r="Q142" s="3" t="inlineStr"/>
@@ -10267,12 +10267,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>sword_marrow_forge</t>
+          <t>sword_light_step</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10282,11 +10282,11 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>洗髓铸刃</t>
+          <t>剑步轻灵</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -10319,11 +10319,11 @@
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N143" s="4" t="n">
@@ -10337,12 +10337,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>sword_probe_meridian</t>
+          <t>sword_marrow_forge</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>剑影探脉</t>
+          <t>洗髓铸刃</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
@@ -10360,17 +10360,17 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -10380,45 +10380,39 @@
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N144" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O144" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="P144" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O144" s="3" t="inlineStr"/>
+      <c r="P144" s="4" t="n"/>
       <c r="Q144" s="3" t="inlineStr"/>
       <c r="R144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>sword_ring_sheath</t>
+          <t>sword_probe_meridian</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10428,7 +10422,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>剑鸣归鞘</t>
+          <t>剑影探脉</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
@@ -10436,17 +10430,17 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -10461,34 +10455,40 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M145" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
       <c r="N145" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O145" s="3" t="inlineStr"/>
-      <c r="P145" s="4" t="n"/>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q145" s="3" t="inlineStr"/>
       <c r="R145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>sword_sky_river</t>
+          <t>sword_ring_sheath</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10498,52 +10498,52 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>天河倒卷</t>
+          <t>剑鸣归鞘</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L146" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N146" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O146" s="3" t="inlineStr"/>
       <c r="P146" s="4" t="n"/>
@@ -10553,12 +10553,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>sword_split_heaven</t>
+          <t>sword_sky_river</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>一剑开天</t>
+          <t>天河倒卷</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
@@ -10581,12 +10581,12 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -10605,14 +10605,16 @@
         </is>
       </c>
       <c r="L147" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="n"/>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="4" t="n"/>
       <c r="Q147" s="3" t="inlineStr"/>
@@ -10621,12 +10623,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>sword_temper_edge</t>
+          <t>sword_split_heaven</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10636,11 +10638,11 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>淬锋</t>
+          <t>一剑开天</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
@@ -10654,7 +10656,7 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -10664,7 +10666,7 @@
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -10673,7 +10675,7 @@
         </is>
       </c>
       <c r="L148" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10689,12 +10691,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>sword_trial_edge</t>
+          <t>sword_temper_edge</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10704,7 +10706,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>试锋</t>
+          <t>淬锋</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -10732,7 +10734,7 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -10741,16 +10743,14 @@
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="n"/>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="4" t="n"/>
       <c r="Q149" s="3" t="inlineStr"/>
@@ -10759,12 +10759,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>sword_void_roam</t>
+          <t>sword_trial_edge</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10774,11 +10774,11 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>太虚游剑</t>
+          <t>试锋</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
@@ -10811,36 +10811,30 @@
         </is>
       </c>
       <c r="L150" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N150" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O150" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O150" s="3" t="inlineStr"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>sword_wash_blade</t>
+          <t>sword_void_roam</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10850,25 +10844,25 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>洗剑诀</t>
+          <t>太虚游剑</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -10878,33 +10872,45 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L151" s="4" t="n">
+      <c r="N151" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M151" s="3" t="inlineStr"/>
-      <c r="N151" s="4" t="n"/>
-      <c r="O151" s="3" t="inlineStr"/>
-      <c r="P151" s="4" t="n"/>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q151" s="3" t="inlineStr"/>
       <c r="R151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>piercing_light</t>
+          <t>sword_wash_blade</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10914,53 +10920,47 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>一线天</t>
+          <t>洗剑诀</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M152" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M152" s="3" t="inlineStr"/>
+      <c r="N152" s="4" t="n"/>
       <c r="O152" s="3" t="inlineStr"/>
       <c r="P152" s="4" t="n"/>
       <c r="Q152" s="3" t="inlineStr"/>
@@ -10969,12 +10969,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
+          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>sword_blood_curse</t>
+          <t>piercing_light</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10984,11 +10984,11 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>血祭剑咒</t>
+          <t>一线天</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
@@ -11017,40 +11017,34 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L153" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N153" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O153" s="3" t="inlineStr">
-        <is>
-          <t>状态(bleed)</t>
-        </is>
-      </c>
-      <c r="P153" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="O153" s="3" t="inlineStr"/>
+      <c r="P153" s="4" t="n"/>
       <c r="Q153" s="3" t="inlineStr"/>
       <c r="R153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
+          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>sword_energy_charge</t>
+          <t>sword_blood_curse</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -11060,25 +11054,25 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>凝气术</t>
+          <t>血祭剑咒</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -11093,34 +11087,40 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L154" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>状态(energy_charge)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="N154" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O154" s="3" t="inlineStr"/>
-      <c r="P154" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>状态(bleed)</t>
+        </is>
+      </c>
+      <c r="P154" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q154" s="3" t="inlineStr"/>
       <c r="R154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
+          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>sword_guard_formation</t>
+          <t>sword_energy_charge</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -11130,15 +11130,15 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>万剑护体</t>
+          <t>凝气术</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11163,14 +11163,20 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_guard)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L155" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M155" s="3" t="inlineStr"/>
-      <c r="N155" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>状态(energy_charge)</t>
+        </is>
+      </c>
+      <c r="N155" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O155" s="3" t="inlineStr"/>
       <c r="P155" s="4" t="n"/>
       <c r="Q155" s="3" t="inlineStr"/>
@@ -11179,12 +11185,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
+          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>sword_heart</t>
+          <t>sword_guard_formation</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -11194,11 +11200,11 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>剑心通明</t>
+          <t>万剑护体</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
@@ -11212,35 +11218,29 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>状态(sword_guard)</t>
         </is>
       </c>
       <c r="L156" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M156" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N156" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr"/>
+      <c r="N156" s="4" t="n"/>
       <c r="O156" s="3" t="inlineStr"/>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="3" t="inlineStr"/>
@@ -11249,12 +11249,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
+          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>sword_nurture</t>
+          <t>sword_heart</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>养剑诀</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -11297,14 +11297,20 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_intent)</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L157" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M157" s="3" t="inlineStr"/>
-      <c r="N157" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N157" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O157" s="3" t="inlineStr"/>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="3" t="inlineStr"/>
@@ -11313,12 +11319,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
+          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>sword_qi_draw</t>
+          <t>sword_nurture</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11328,11 +11334,11 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>剑气引</t>
+          <t>养剑诀</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
@@ -11346,7 +11352,7 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
@@ -11361,20 +11367,14 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(sword_intent)</t>
         </is>
       </c>
       <c r="L158" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M158" s="3" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="N158" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M158" s="3" t="inlineStr"/>
+      <c r="N158" s="4" t="n"/>
       <c r="O158" s="3" t="inlineStr"/>
       <c r="P158" s="4" t="n"/>
       <c r="Q158" s="3" t="inlineStr"/>
@@ -11383,12 +11383,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
+          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>sword_rain</t>
+          <t>sword_qi_draw</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -11398,47 +11398,53 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>剑雨</t>
+          <t>剑气引</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="I159" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L159" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M159" s="3" t="inlineStr"/>
-      <c r="N159" s="4" t="n"/>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="N159" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="4" t="n"/>
       <c r="Q159" s="3" t="inlineStr"/>
@@ -11447,12 +11453,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>sword_shadow_strike</t>
+          <t>sword_rain</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -11462,11 +11468,11 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>瞬影剑</t>
+          <t>剑雨</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
@@ -11475,22 +11481,22 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -11499,16 +11505,10 @@
         </is>
       </c>
       <c r="L160" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M160" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr"/>
+      <c r="N160" s="4" t="n"/>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="3" t="inlineStr"/>
@@ -11517,12 +11517,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
+          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>sword_star_shatter</t>
+          <t>sword_shadow_strike</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -11532,11 +11532,11 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>碎星斩</t>
+          <t>瞬影剑</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
@@ -11550,29 +11550,35 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>target_status_bonus_damage_effect</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L161" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M161" s="3" t="inlineStr"/>
-      <c r="N161" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N161" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="4" t="n"/>
       <c r="Q161" s="3" t="inlineStr"/>
@@ -11581,12 +11587,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
+          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>sword_wanjian</t>
+          <t>sword_star_shatter</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -11596,11 +11602,11 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>万剑归宗</t>
+          <t>碎星斩</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
@@ -11629,11 +11635,11 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>player_status_damage_effect</t>
+          <t>target_status_bonus_damage_effect</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M162" s="3" t="inlineStr"/>
       <c r="N162" s="4" t="n"/>
@@ -11645,12 +11651,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>sword_water_break</t>
+          <t>sword_wanjian</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -11660,11 +11666,11 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>断水剑</t>
+          <t>万剑归宗</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
@@ -11678,7 +11684,7 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -11688,25 +11694,19 @@
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>player_status_damage_effect</t>
         </is>
       </c>
       <c r="L163" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M163" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N163" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr"/>
+      <c r="N163" s="4" t="n"/>
       <c r="O163" s="3" t="inlineStr"/>
       <c r="P163" s="4" t="n"/>
       <c r="Q163" s="3" t="inlineStr"/>
@@ -11715,12 +11715,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
+          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>sword_wind_return</t>
+          <t>sword_water_break</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11730,11 +11730,11 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>回风剑</t>
+          <t>断水剑</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -11767,15 +11767,15 @@
         </is>
       </c>
       <c r="L164" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N164" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O164" s="3" t="inlineStr"/>
       <c r="P164" s="4" t="n"/>
@@ -11785,22 +11785,22 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ash_heart_guard.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ash_heart_guard</t>
+          <t>sword_wind_return</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>灰烬护心</t>
+          <t>回风剑</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -11828,19 +11828,25 @@
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L165" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M165" s="3" t="inlineStr"/>
-      <c r="N165" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N165" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O165" s="3" t="inlineStr"/>
       <c r="P165" s="4" t="n"/>
       <c r="Q165" s="3" t="inlineStr"/>
@@ -11849,12 +11855,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/circulating_breath.tres</t>
+          <t>common_cards/ash_heart_guard.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>circulating_breath</t>
+          <t>ash_heart_guard</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11864,7 +11870,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>周天吐纳</t>
+          <t>灰烬护心</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -11882,7 +11888,7 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
@@ -11897,20 +11903,14 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L166" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M166" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N166" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr"/>
+      <c r="N166" s="4" t="n"/>
       <c r="O166" s="3" t="inlineStr"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="3" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>common_cards/circulating_breath.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>circulating_breath</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>周天吐纳</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -11973,8 +11973,14 @@
       <c r="L167" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M167" s="3" t="inlineStr"/>
-      <c r="N167" s="4" t="n"/>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -11983,12 +11989,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/discard_aegis.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>discard_aegis</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11998,7 +12004,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>弃念成罡</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -12016,7 +12022,7 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -12031,11 +12037,11 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L168" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M168" s="3" t="inlineStr"/>
       <c r="N168" s="4" t="n"/>
@@ -12047,12 +12053,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/embers_return.tres</t>
+          <t>common_cards/discard_aegis.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>embers_return</t>
+          <t>discard_aegis</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12062,7 +12068,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>烬归灵台</t>
+          <t>弃念成罡</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12080,12 +12086,12 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -12095,20 +12101,14 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L169" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N169" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr"/>
+      <c r="N169" s="4" t="n"/>
       <c r="O169" s="3" t="inlineStr"/>
       <c r="P169" s="4" t="n"/>
       <c r="Q169" s="3" t="inlineStr"/>
@@ -12117,12 +12117,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>common_cards/flowing_cloud_guard.tres</t>
+          <t>common_cards/embers_return.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>flowing_cloud_guard</t>
+          <t>embers_return</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>流云护身</t>
+          <t>烬归灵台</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
@@ -12165,12 +12165,20 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L170" s="4" t="n"/>
-      <c r="M170" s="3" t="inlineStr"/>
-      <c r="N170" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O170" s="3" t="inlineStr"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="3" t="inlineStr"/>
@@ -12179,12 +12187,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>common_cards/flowing_cloud_guard.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>flowing_cloud_guard</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -12194,7 +12202,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>流云护身</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12202,17 +12210,17 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
@@ -12227,20 +12235,12 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M171" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="n"/>
+      <c r="M171" s="3" t="inlineStr"/>
+      <c r="N171" s="4" t="n"/>
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -12249,12 +12249,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>common_cards/momentum_pursuit.tres</t>
+          <t>common_cards/ink_flow_slash.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>momentum_pursuit</t>
+          <t>ink_flow_slash</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>乘势追击</t>
+          <t>墨流斩</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -12297,14 +12297,20 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L172" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" s="3" t="inlineStr"/>
-      <c r="N172" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N172" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O172" s="3" t="inlineStr"/>
       <c r="P172" s="4" t="n"/>
       <c r="Q172" s="3" t="inlineStr"/>
@@ -12313,12 +12319,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>common_cards/momentum_pursuit.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>momentum_pursuit</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -12328,7 +12334,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>乘势追击</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12346,7 +12352,7 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -12361,20 +12367,14 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M173" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N173" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr"/>
+      <c r="N173" s="4" t="n"/>
       <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -12383,12 +12383,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>common_cards/returning_light.tres</t>
+          <t>common_cards/muscle_resonance_strike.tres</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>returning_light</t>
+          <t>muscle_resonance_strike</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>回光返照</t>
+          <t>劲气共鸣</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -12406,22 +12406,22 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -12431,14 +12431,20 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L174" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M174" s="3" t="inlineStr"/>
-      <c r="N174" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="O174" s="3" t="inlineStr"/>
       <c r="P174" s="4" t="n"/>
       <c r="Q174" s="3" t="inlineStr"/>
@@ -12447,12 +12453,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>common_cards/spirit_stone_needle.tres</t>
+          <t>common_cards/returning_light.tres</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>spirit_stone_needle</t>
+          <t>returning_light</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -12462,25 +12468,25 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>灵石飞针</t>
+          <t>回光返照</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -12495,11 +12501,11 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L175" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M175" s="3" t="inlineStr"/>
       <c r="N175" s="4" t="n"/>
@@ -12511,12 +12517,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/blood_debt_curse.tres</t>
+          <t>common_cards/spirit_stone_needle.tres</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>blood_debt_curse</t>
+          <t>spirit_stone_needle</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -12526,7 +12532,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>血债</t>
+          <t>灵石飞针</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -12534,12 +12540,12 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -12549,7 +12555,7 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -12559,11 +12565,11 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L176" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M176" s="3" t="inlineStr"/>
       <c r="N176" s="4" t="n"/>
@@ -12575,12 +12581,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -12590,7 +12596,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
@@ -12621,8 +12627,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="4" t="n"/>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M177" s="3" t="inlineStr"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="3" t="inlineStr"/>
@@ -12633,12 +12645,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -12648,7 +12660,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -12691,12 +12703,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/karmic_fire_curse.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>karmic_fire_curse</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -12706,11 +12718,11 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
@@ -12729,7 +12741,7 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
@@ -12737,14 +12749,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K179" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L179" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="K179" s="3" t="inlineStr"/>
+      <c r="L179" s="4" t="n"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="3" t="inlineStr"/>
@@ -12755,12 +12761,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>karmic_fire_curse</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -12770,11 +12776,11 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
@@ -12793,7 +12799,7 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -12801,8 +12807,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr"/>
-      <c r="L180" s="4" t="n"/>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M180" s="3" t="inlineStr"/>
       <c r="N180" s="4" t="n"/>
       <c r="O180" s="3" t="inlineStr"/>
@@ -12813,12 +12825,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/status/underworld_writ.tres</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>underworld_writ</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -12828,20 +12840,20 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>判牒</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -12859,14 +12871,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="K181" s="3" t="inlineStr"/>
+      <c r="L181" s="4" t="n"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="4" t="n"/>
       <c r="O181" s="3" t="inlineStr"/>
@@ -12877,12 +12883,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/strike.tres</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>strike</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -12892,7 +12898,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -12900,12 +12906,12 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -12915,7 +12921,7 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
@@ -12923,8 +12929,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr"/>
-      <c r="L182" s="4" t="n"/>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M182" s="3" t="inlineStr"/>
       <c r="N182" s="4" t="n"/>
       <c r="O182" s="3" t="inlineStr"/>
@@ -12935,22 +12947,22 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/toxin.tres</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
@@ -12958,22 +12970,22 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
@@ -12981,22 +12993,10 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L183" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M183" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N183" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="K183" s="3" t="inlineStr"/>
+      <c r="L183" s="4" t="n"/>
+      <c r="M183" s="3" t="inlineStr"/>
+      <c r="N183" s="4" t="n"/>
       <c r="O183" s="3" t="inlineStr"/>
       <c r="P183" s="4" t="n"/>
       <c r="Q183" s="3" t="inlineStr"/>
@@ -13005,12 +13005,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>fusion_cards/attack_guard_unity.tres</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>attack_guard_unity</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>攻守合一</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -13057,15 +13057,15 @@
         </is>
       </c>
       <c r="L184" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N184" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O184" s="3" t="inlineStr"/>
       <c r="P184" s="4" t="n"/>
@@ -13075,12 +13075,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>fusion_cards/blood_beast_rend.tres</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>blood_beast_rend</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -13090,52 +13090,52 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>血兽撕咬</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H185" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I185" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L185" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M185" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N185" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="4" t="n"/>
@@ -13145,12 +13145,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>demon_rain_swordfire</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -13160,11 +13160,11 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>魔雨剑火</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -13197,42 +13197,112 @@
         </is>
       </c>
       <c r="L186" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N186" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O186" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P186" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O186" s="3" t="inlineStr"/>
+      <c r="P186" s="4" t="n"/>
       <c r="Q186" s="3" t="inlineStr"/>
       <c r="R186" s="4" t="n"/>
     </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O187" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>

--- a/game_data.xlsx
+++ b/game_data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R187"/>
+  <dimension ref="A1:R188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4123,12 +4123,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_debt.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_ash_barrier.tres</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_debt</t>
+          <t>demon_ash_barrier</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -4138,30 +4138,30 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>血债清算</t>
+          <t>灰烬障</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4171,11 +4171,11 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>血债清算</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L53" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="4" t="n"/>
@@ -4187,12 +4187,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_forge_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_debt.tres</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_forge_armor</t>
+          <t>demon_blood_debt</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>血铸魔甲</t>
+          <t>血债清算</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -4235,20 +4235,14 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>血债清算</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="4" t="n"/>
       <c r="O54" s="3" t="inlineStr"/>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="3" t="inlineStr"/>
@@ -4257,12 +4251,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_repay.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_forge_armor.tres</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_repay</t>
+          <t>demon_blood_forge_armor</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4272,7 +4266,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>血偿</t>
+          <t>血铸魔甲</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -4290,7 +4284,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -4313,32 +4307,26 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="3" t="inlineStr"/>
       <c r="R55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_reversal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_repay.tres</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_reversal</t>
+          <t>demon_blood_repay</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4348,11 +4336,11 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>命血逆流</t>
+          <t>血偿</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
@@ -4366,12 +4354,12 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -4389,19 +4377,19 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="P56" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q56" s="3" t="inlineStr"/>
       <c r="R56" s="4" t="n"/>
@@ -4409,12 +4397,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_rite_slash.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_reversal.tres</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_rite_slash</t>
+          <t>demon_blood_reversal</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4424,30 +4412,30 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>血祭斩</t>
+          <t>命血逆流</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -4461,30 +4449,36 @@
         </is>
       </c>
       <c r="L57" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N57" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O57" s="3" t="inlineStr"/>
-      <c r="P57" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q57" s="3" t="inlineStr"/>
       <c r="R57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_sea_surge.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_rite_slash.tres</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_surge</t>
+          <t>demon_blood_rite_slash</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4494,52 +4488,52 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>血海滔天</t>
+          <t>血祭斩</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="N58" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="4" t="n"/>
@@ -4549,12 +4543,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_blood_ward.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_sea_surge.tres</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_ward</t>
+          <t>demon_blood_sea_surge</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4564,25 +4558,25 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>血盾</t>
+          <t>血海滔天</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -4592,24 +4586,24 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
           <t>自损</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
       <c r="N59" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="4" t="n"/>
@@ -4619,12 +4613,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_burn_impurity.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_blood_ward.tres</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_impurity</t>
+          <t>demon_blood_ward</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4634,7 +4628,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>焚秽诀</t>
+          <t>血盾</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4652,7 +4646,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4667,19 +4661,19 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
           <t>护体</t>
         </is>
       </c>
-      <c r="L60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>焚化污染</t>
-        </is>
-      </c>
       <c r="N60" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="4" t="n"/>
@@ -4689,12 +4683,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_calamity_embryo.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_burn_impurity.tres</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>demon_calamity_embryo</t>
+          <t>demon_burn_impurity</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4704,7 +4698,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>劫火魔胎</t>
+          <t>焚秽诀</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4722,12 +4716,12 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4737,44 +4731,34 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>焚化污染</t>
         </is>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="P61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>延迟施放</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="3" t="inlineStr"/>
       <c r="R61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_calamity_embryo.tres</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>demon_defend</t>
+          <t>demon_calamity_embryo</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4784,7 +4768,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>劫火魔胎</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -4802,43 +4786,59 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="4" t="n"/>
-      <c r="O62" s="3" t="inlineStr"/>
-      <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="R62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_defend.tres</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>demon_desperate_burst</t>
+          <t>demon_defend</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4848,44 +4848,44 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>绝命爆发</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L63" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="4" t="n"/>
@@ -4897,12 +4897,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_desperate_burst.tres</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>demon_flame</t>
+          <t>demon_desperate_burst</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>魔焰燎原</t>
+          <t>绝命爆发</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4945,20 +4945,14 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="3" t="inlineStr"/>
@@ -4967,12 +4961,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame.tres</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_black</t>
+          <t>demon_flame</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4982,11 +4976,11 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>魔焰黑·噬血</t>
+          <t>魔焰燎原</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
@@ -4995,7 +4989,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5010,30 +5004,26 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
           <t>自损</t>
         </is>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+      <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="3" t="inlineStr"/>
       <c r="R65" s="4" t="n"/>
@@ -5041,12 +5031,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_black.tres</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_blue</t>
+          <t>demon_flame_black</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -5056,7 +5046,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>魔焰蓝·灵涌</t>
+          <t>魔焰黑·噬血</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -5064,12 +5054,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5079,7 +5069,7 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -5089,19 +5079,25 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n"/>
-      <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="3" t="inlineStr"/>
       <c r="R66" s="4" t="n"/>
@@ -5109,12 +5105,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_blue.tres</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_green</t>
+          <t>demon_flame_blue</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5124,7 +5120,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>魔焰绿·镇煞</t>
+          <t>魔焰蓝·灵涌</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -5147,7 +5143,7 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -5157,11 +5153,17 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="4" t="n"/>
@@ -5171,12 +5173,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_green.tres</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_heart</t>
+          <t>demon_flame_green</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -5186,20 +5188,20 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>魔焰焚心</t>
+          <t>魔焰绿·镇煞</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5214,25 +5216,17 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="4" t="n"/>
       <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="3" t="inlineStr"/>
@@ -5241,12 +5235,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_heart.tres</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_purple</t>
+          <t>demon_flame_heart</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5256,11 +5250,11 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>魔焰紫·蚀魂</t>
+          <t>魔焰焚心</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -5274,7 +5268,7 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -5284,30 +5278,26 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
           <t>状态(exposed)</t>
         </is>
       </c>
-      <c r="L69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
       <c r="N69" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="3" t="inlineStr"/>
       <c r="R69" s="4" t="n"/>
@@ -5315,12 +5305,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_purple.tres</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_red</t>
+          <t>demon_flame_purple</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -5330,11 +5320,11 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>魔焰红·焚界</t>
+          <t>魔焰紫·蚀魂</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
@@ -5343,12 +5333,12 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -5363,19 +5353,25 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="L70" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="N70" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
         <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n"/>
-      <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="4" t="n"/>
@@ -5383,12 +5379,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_red.tres</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_white</t>
+          <t>demon_flame_red</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -5398,11 +5394,11 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>魔焰白·护魂</t>
+          <t>魔焰红·焚界</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
@@ -5411,12 +5407,12 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -5435,21 +5431,15 @@
         </is>
       </c>
       <c r="L71" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="3" t="inlineStr"/>
       <c r="R71" s="4" t="n"/>
@@ -5457,12 +5447,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_white.tres</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_yellow</t>
+          <t>demon_flame_white</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -5472,7 +5462,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>魔焰黄·狂烬</t>
+          <t>魔焰白·护魂</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -5480,17 +5470,17 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -5505,13 +5495,25 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
           <t>configured_flame_effect</t>
         </is>
       </c>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="4" t="n"/>
-      <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="3" t="inlineStr"/>
       <c r="R72" s="4" t="n"/>
@@ -5519,12 +5521,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flame_yellow.tres</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>demon_flesh_rebirth</t>
+          <t>demon_flame_yellow</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5534,7 +5536,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>血肉重生</t>
+          <t>魔焰黄·狂烬</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
@@ -5552,35 +5554,27 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_flame_effect</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -5589,12 +5583,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_flesh_rebirth.tres</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_archive</t>
+          <t>demon_flesh_rebirth</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -5604,11 +5598,11 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>窥心魔典</t>
+          <t>血肉重生</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
@@ -5637,14 +5631,20 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>configured_discover_effect</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="3" t="inlineStr"/>
-      <c r="N74" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="3" t="inlineStr"/>
@@ -5653,12 +5653,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_lurking_soul_curse.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_forbidden_archive.tres</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>demon_lurking_soul_curse</t>
+          <t>demon_forbidden_archive</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>伏魂咒</t>
+          <t>窥心魔典</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -5681,17 +5681,17 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5701,25 +5701,15 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>configured_discover_effect</t>
         </is>
       </c>
       <c r="L75" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>延迟施放</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="3" t="inlineStr"/>
       <c r="R75" s="4" t="n"/>
@@ -5727,12 +5717,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_lurking_soul_curse.tres</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_marks_return</t>
+          <t>demon_lurking_soul_curse</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -5742,30 +5732,30 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>万印归墟</t>
+          <t>伏魂咒</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5775,13 +5765,25 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="3" t="inlineStr"/>
-      <c r="N76" s="4" t="n"/>
-      <c r="O76" s="3" t="inlineStr"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>延迟施放</t>
+        </is>
+      </c>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="3" t="inlineStr"/>
       <c r="R76" s="4" t="n"/>
@@ -5789,12 +5791,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_marks_return.tres</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_devour</t>
+          <t>demon_myriad_marks_return</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5804,11 +5806,11 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>万魂噬天</t>
+          <t>万印归墟</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
@@ -5822,7 +5824,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -5837,20 +5839,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="4" t="n"/>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -5859,12 +5853,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_myriad_soul_devour.tres</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>demon_seven_flame_cycle</t>
+          <t>demon_myriad_soul_devour</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5874,30 +5868,30 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>七焰回环</t>
+          <t>万魂噬天</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -5907,12 +5901,20 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>configured_flame_effect</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="n"/>
-      <c r="M78" s="3" t="inlineStr"/>
-      <c r="N78" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="3" t="inlineStr"/>
@@ -5921,12 +5923,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_seven_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_blade</t>
+          <t>demon_seven_flame_cycle</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5936,25 +5938,25 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>煞刃</t>
+          <t>七焰回环</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -5969,7 +5971,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>耗煞伤害</t>
+          <t>configured_flame_effect</t>
         </is>
       </c>
       <c r="L79" s="4" t="n"/>
@@ -5983,12 +5985,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_sha_blade.tres</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>demon_shadow_reenactment</t>
+          <t>demon_sha_blade</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5998,30 +6000,30 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>魔影复刻</t>
+          <t>煞刃</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -6031,7 +6033,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>复刻</t>
+          <t>耗煞伤害</t>
         </is>
       </c>
       <c r="L80" s="4" t="n"/>
@@ -6045,12 +6047,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shadow_reenactment.tres</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>demon_shatter_soul_seal</t>
+          <t>demon_shadow_reenactment</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6060,7 +6062,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>碎魂印</t>
+          <t>魔影复刻</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6073,40 +6075,32 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>复刻</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="4" t="n"/>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="3" t="inlineStr"/>
@@ -6115,12 +6109,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_shatter_soul_seal.tres</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_devour_claw</t>
+          <t>demon_shatter_soul_seal</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6130,7 +6124,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>噬魂爪</t>
+          <t>碎魂印</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6138,7 +6132,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6148,7 +6142,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -6158,7 +6152,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -6167,7 +6161,7 @@
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -6175,7 +6169,7 @@
         </is>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" s="3" t="inlineStr"/>
       <c r="P82" s="4" t="n"/>
@@ -6185,12 +6179,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_devour_claw.tres</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_lamp_renewal</t>
+          <t>demon_soul_devour_claw</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6200,7 +6194,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>魂灯续燃</t>
+          <t>噬魂爪</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -6208,7 +6202,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6218,12 +6212,12 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -6233,38 +6227,34 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>灵气</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="4" t="n"/>
       <c r="Q83" s="3" t="inlineStr"/>
       <c r="R83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_soul_lamp_renewal.tres</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>demon_strike</t>
+          <t>demon_soul_lamp_renewal</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6274,7 +6264,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>魂灯续燃</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -6282,7 +6272,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6292,43 +6282,53 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M84" s="3" t="inlineStr"/>
-      <c r="N84" s="4" t="n"/>
-      <c r="O84" s="3" t="inlineStr"/>
-      <c r="P84" s="4" t="n"/>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>灵气</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q84" s="3" t="inlineStr"/>
       <c r="R84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
+          <t>characters/demonic_cultivator/cards/demon_strike.tres</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_membrane</t>
+          <t>demon_strike</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>血膜</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -6366,30 +6366,20 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N85" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="3" t="inlineStr"/>
       <c r="R85" s="4" t="n"/>
@@ -6397,12 +6387,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_membrane.tres</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_qi_guard</t>
+          <t>demon_blood_membrane</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6412,7 +6402,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>血气护体</t>
+          <t>血膜</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -6430,7 +6420,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -6445,13 +6435,25 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
           <t>configured_demonic_engine_effect</t>
         </is>
       </c>
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="3" t="inlineStr"/>
-      <c r="N86" s="4" t="n"/>
-      <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="3" t="inlineStr"/>
       <c r="R86" s="4" t="n"/>
@@ -6459,12 +6461,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_qi_guard.tres</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_recompense</t>
+          <t>demon_blood_qi_guard</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6474,11 +6476,11 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>血偿万道</t>
+          <t>血气护体</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
@@ -6492,7 +6494,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -6521,12 +6523,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_recompense.tres</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea_boundless</t>
+          <t>demon_blood_recompense</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6536,20 +6538,20 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>血海无量</t>
+          <t>血偿万道</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6569,15 +6571,11 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>configured_x_cost_self_damage_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L88" s="4" t="n"/>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>configured_x_cost_damage_effect</t>
-        </is>
-      </c>
+      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="4" t="n"/>
       <c r="O88" s="3" t="inlineStr"/>
       <c r="P88" s="4" t="n"/>
@@ -6587,12 +6585,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_blood_sea_boundless.tres</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>demon_bloodthirst</t>
+          <t>demon_blood_sea_boundless</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6602,25 +6600,25 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>嗜血成性</t>
+          <t>血海无量</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -6635,11 +6633,15 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_x_cost_self_damage_effect</t>
         </is>
       </c>
       <c r="L89" s="4" t="n"/>
-      <c r="M89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>configured_x_cost_damage_effect</t>
+        </is>
+      </c>
       <c r="N89" s="4" t="n"/>
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="4" t="n"/>
@@ -6649,12 +6651,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_bloodthirst.tres</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_breath</t>
+          <t>demon_bloodthirst</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6664,7 +6666,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>焰息</t>
+          <t>嗜血成性</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -6672,7 +6674,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -6692,25 +6694,17 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="4" t="n"/>
       <c r="O90" s="3" t="inlineStr"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="3" t="inlineStr"/>
@@ -6719,12 +6713,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_breath.tres</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_continuity</t>
+          <t>demon_flame_breath</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6734,7 +6728,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>焰心承续</t>
+          <t>焰息</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -6742,7 +6736,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -6767,12 +6761,20 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="3" t="inlineStr"/>
-      <c r="N91" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="3" t="inlineStr"/>
@@ -6781,12 +6783,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_continuity.tres</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>demon_flame_refining</t>
+          <t>demon_flame_continuity</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6796,7 +6798,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>炼焰术</t>
+          <t>焰心承续</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -6814,7 +6816,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -6824,7 +6826,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -6843,12 +6845,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_flame_refining.tres</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>demon_myriad_soul_burn_sky</t>
+          <t>demon_flame_refining</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6858,30 +6860,30 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>万魂焚天</t>
+          <t>炼焰术</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -6891,7 +6893,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L93" s="4" t="n"/>
@@ -6905,12 +6907,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_myriad_soul_burn_sky.tres</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_nurture</t>
+          <t>demon_myriad_soul_burn_sky</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6920,40 +6922,40 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>养煞</t>
+          <t>万魂焚天</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>configured_demonic_engine_effect</t>
+          <t>configured_soul_mark_detonate_effect</t>
         </is>
       </c>
       <c r="L94" s="4" t="n"/>
@@ -6967,12 +6969,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_nurture.tres</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>demon_sha_return</t>
+          <t>demon_sha_nurture</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6982,15 +6984,15 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>归煞</t>
+          <t>养煞</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -7000,12 +7002,12 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -7015,18 +7017,12 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>configured_consume_status_to_block_effect</t>
+          <t>configured_demonic_engine_effect</t>
         </is>
       </c>
       <c r="L95" s="4" t="n"/>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>灵气</t>
-        </is>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="4" t="n"/>
       <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="3" t="inlineStr"/>
@@ -7035,12 +7031,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_sha_return.tres</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_banner</t>
+          <t>demon_sha_return</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7050,11 +7046,11 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>引魂幡</t>
+          <t>归煞</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
@@ -7063,17 +7059,17 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -7083,15 +7079,13 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_consume_status_to_block_effect</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="n"/>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>灵气</t>
         </is>
       </c>
       <c r="N96" s="4" t="n">
@@ -7105,12 +7099,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_banner.tres</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_echo</t>
+          <t>demon_soul_banner</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7120,45 +7114,53 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>噬魂回响</t>
+          <t>引魂幡</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>功法</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>自身</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>暗金</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>configured_demonic_engine_effect</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="3" t="inlineStr"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="3" t="inlineStr"/>
@@ -7167,12 +7169,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_echo.tres</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_flame_cycle</t>
+          <t>demon_soul_echo</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7182,11 +7184,11 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>魂火相济</t>
+          <t>噬魂回响</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
@@ -7200,7 +7202,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -7210,7 +7212,7 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -7229,12 +7231,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_flame_cycle.tres</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_mark_sense</t>
+          <t>demon_soul_flame_cycle</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7244,7 +7246,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>魂印感应</t>
+          <t>魂火相济</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -7262,7 +7264,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -7272,7 +7274,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
@@ -7291,12 +7293,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_mark_sense.tres</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_rite</t>
+          <t>demon_soul_mark_sense</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7306,7 +7308,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>夺魂仪</t>
+          <t>魂印感应</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -7324,7 +7326,7 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -7353,12 +7355,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
+          <t>characters/demonic_cultivator/cards/engines/demon_soul_rite.tres</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>forbidden_mantra</t>
+          <t>demon_soul_rite</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7368,7 +7370,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>禁咒入魔</t>
+          <t>夺魂仪</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -7386,7 +7388,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -7396,25 +7398,17 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L101" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N101" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_demonic_engine_effect</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="4" t="n"/>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="3" t="inlineStr"/>
@@ -7423,12 +7417,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
+          <t>characters/demonic_cultivator/cards/forbidden_mantra.tres</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>hun_kai</t>
+          <t>forbidden_mantra</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7438,7 +7432,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>魂铠</t>
+          <t>禁咒入魔</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -7446,17 +7440,17 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -7466,22 +7460,24 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L102" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N102" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O102" s="3" t="inlineStr"/>
       <c r="P102" s="4" t="n"/>
@@ -7491,12 +7487,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_kai.tres</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>hun_zang</t>
+          <t>hun_kai</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7506,15 +7502,15 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>魂葬</t>
+          <t>魂铠</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -7524,7 +7520,7 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -7539,12 +7535,18 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
+          <t>configured_soul_mark_consume_effect</t>
         </is>
       </c>
       <c r="L103" s="4" t="n"/>
-      <c r="M103" s="3" t="inlineStr"/>
-      <c r="N103" s="4" t="n"/>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="4" t="n"/>
       <c r="Q103" s="3" t="inlineStr"/>
@@ -7553,12 +7555,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
+          <t>characters/demonic_cultivator/cards/hun_zang.tres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>ju_sha</t>
+          <t>hun_zang</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7568,25 +7570,25 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>聚煞</t>
+          <t>魂葬</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -7601,20 +7603,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>状态(sha_qi)</t>
-        </is>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="3" t="inlineStr"/>
+      <c r="N104" s="4" t="n"/>
       <c r="O104" s="3" t="inlineStr"/>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="3" t="inlineStr"/>
@@ -7623,12 +7617,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
+          <t>characters/demonic_cultivator/cards/ju_sha.tres</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>lie_hun</t>
+          <t>ju_sha</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7638,20 +7632,20 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>裂魂</t>
+          <t>聚煞</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -7671,12 +7665,20 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L105" s="4" t="n"/>
-      <c r="M105" s="3" t="inlineStr"/>
-      <c r="N105" s="4" t="n"/>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="3" t="inlineStr"/>
@@ -7685,12 +7687,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
+          <t>characters/demonic_cultivator/cards/lie_hun.tres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>demon_black_contract</t>
+          <t>lie_hun</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7700,7 +7702,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>黑契</t>
+          <t>裂魂</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -7708,12 +7710,12 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -7728,25 +7730,17 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L106" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>状态(muscle)</t>
-        </is>
-      </c>
-      <c r="N106" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="n"/>
+      <c r="M106" s="3" t="inlineStr"/>
+      <c r="N106" s="4" t="n"/>
       <c r="O106" s="3" t="inlineStr"/>
       <c r="P106" s="4" t="n"/>
       <c r="Q106" s="3" t="inlineStr"/>
@@ -7755,12 +7749,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_black_contract.tres</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_oath</t>
+          <t>demon_black_contract</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7770,20 +7764,20 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>血誓</t>
+          <t>黑契</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -7803,19 +7797,19 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L107" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="N107" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="4" t="n"/>
@@ -7825,12 +7819,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_oath.tres</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>demon_blood_sea</t>
+          <t>demon_blood_oath</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7840,52 +7834,52 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>血海翻涌</t>
+          <t>血誓</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L108" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M108" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N108" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="O108" s="3" t="inlineStr"/>
       <c r="P108" s="4" t="n"/>
@@ -7895,12 +7889,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_blood_sea.tres</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>demon_burn_self_heaven</t>
+          <t>demon_blood_sea</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7910,11 +7904,11 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>焚身问天</t>
+          <t>血海翻涌</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
@@ -7928,17 +7922,17 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -7947,36 +7941,30 @@
         </is>
       </c>
       <c r="L109" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N109" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O109" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="4" t="n"/>
       <c r="Q109" s="3" t="inlineStr"/>
       <c r="R109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_burn_self_heaven.tres</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>demon_cut_soul</t>
+          <t>demon_burn_self_heaven</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7986,11 +7974,11 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>割魂刃</t>
+          <t>焚身问天</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
@@ -7999,17 +7987,17 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -8019,34 +8007,40 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>半血爆伤</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N110" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O110" s="3" t="inlineStr"/>
-      <c r="P110" s="4" t="n"/>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q110" s="3" t="inlineStr"/>
       <c r="R110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_cut_soul.tres</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>demon_forbidden_power</t>
+          <t>demon_cut_soul</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -8056,7 +8050,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>禁咒开脉</t>
+          <t>割魂刃</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -8064,17 +8058,17 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -8089,40 +8083,34 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>半血爆伤</t>
         </is>
       </c>
       <c r="L111" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M111" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N111" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O111" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P111" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="4" t="n"/>
       <c r="Q111" s="3" t="inlineStr"/>
       <c r="R111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_forbidden_power.tres</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>demon_ghost_hook</t>
+          <t>demon_forbidden_power</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8132,7 +8120,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>幽钩</t>
+          <t>禁咒开脉</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -8140,17 +8128,17 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -8160,20 +8148,20 @@
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N112" s="4" t="n">
@@ -8181,7 +8169,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="P112" s="4" t="n">
@@ -8193,12 +8181,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ghost_hook.tres</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>demon_hell_soul_seal</t>
+          <t>demon_ghost_hook</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8208,11 +8196,11 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>幽冥万魂印</t>
+          <t>幽钩</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -8221,12 +8209,12 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -8236,7 +8224,7 @@
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
@@ -8245,30 +8233,36 @@
         </is>
       </c>
       <c r="L113" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N113" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O113" s="3" t="inlineStr"/>
-      <c r="P113" s="4" t="n"/>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q113" s="3" t="inlineStr"/>
       <c r="R113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hell_soul_seal.tres</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>demon_hundred_ghosts</t>
+          <t>demon_hell_soul_seal</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8278,11 +8272,11 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>百鬼留痕</t>
+          <t>幽冥万魂印</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
@@ -8296,7 +8290,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -8311,17 +8305,19 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="n"/>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N114" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="4" t="n"/>
@@ -8331,12 +8327,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_hundred_ghosts.tres</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>demon_lantern_shadow</t>
+          <t>demon_hundred_ghosts</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8346,25 +8342,25 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>灯影噬魂</t>
+          <t>百鬼留痕</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -8379,19 +8375,17 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L115" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="n"/>
       <c r="M115" s="3" t="inlineStr">
         <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="4" t="n"/>
@@ -8401,12 +8395,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_lantern_shadow.tres</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>demon_life_for_mana</t>
+          <t>demon_lantern_shadow</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8416,11 +8410,11 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>命换灵机</t>
+          <t>灯影噬魂</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
@@ -8429,7 +8423,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -8449,15 +8443,15 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N116" s="4" t="n">
@@ -8471,12 +8465,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_life_for_mana.tres</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>demon_mark_bloom</t>
+          <t>demon_life_for_mana</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8486,52 +8480,52 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>印开彼岸</t>
+          <t>命换灵机</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="N117" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="4" t="n"/>
@@ -8541,12 +8535,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_mark_bloom.tres</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>demon_sacrificial_flame</t>
+          <t>demon_mark_bloom</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -8556,25 +8550,25 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>祭焰</t>
+          <t>印开彼岸</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -8584,24 +8578,24 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N118" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O118" s="3" t="inlineStr"/>
       <c r="P118" s="4" t="n"/>
@@ -8611,12 +8605,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_sacrificial_flame.tres</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_armor</t>
+          <t>demon_sacrificial_flame</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -8626,7 +8620,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>魂衣</t>
+          <t>祭焰</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -8634,12 +8628,12 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -8654,24 +8648,24 @@
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L119" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" s="3" t="inlineStr"/>
       <c r="P119" s="4" t="n"/>
@@ -8681,12 +8675,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_armor.tres</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_price</t>
+          <t>demon_soul_armor</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -8696,15 +8690,15 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>以魂为价</t>
+          <t>魂衣</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -8714,7 +8708,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -8724,45 +8718,39 @@
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N120" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O120" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P120" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O120" s="3" t="inlineStr"/>
+      <c r="P120" s="4" t="n"/>
       <c r="Q120" s="3" t="inlineStr"/>
       <c r="R120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_price.tres</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_prison</t>
+          <t>demon_soul_price</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -8772,7 +8760,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>万魂牢</t>
+          <t>以魂为价</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
@@ -8780,17 +8768,17 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -8800,33 +8788,45 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L121" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M121" s="3" t="inlineStr"/>
-      <c r="N121" s="4" t="n"/>
-      <c r="O121" s="3" t="inlineStr"/>
-      <c r="P121" s="4" t="n"/>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P121" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q121" s="3" t="inlineStr"/>
       <c r="R121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_prison.tres</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_siphon</t>
+          <t>demon_soul_prison</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8836,25 +8836,25 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>摄魂归元</t>
+          <t>万魂牢</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -8864,45 +8864,33 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O122" s="3" t="inlineStr">
-        <is>
-          <t>状态(soul_mark)</t>
-        </is>
-      </c>
-      <c r="P122" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr"/>
+      <c r="N122" s="4" t="n"/>
+      <c r="O122" s="3" t="inlineStr"/>
+      <c r="P122" s="4" t="n"/>
       <c r="Q122" s="3" t="inlineStr"/>
       <c r="R122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_siphon.tres</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>demon_soul_stamp</t>
+          <t>demon_soul_siphon</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8912,7 +8900,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>魂印</t>
+          <t>摄魂归元</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
@@ -8930,7 +8918,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -8940,7 +8928,7 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
@@ -8953,26 +8941,32 @@
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
           <t>状态(soul_mark)</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O123" s="3" t="inlineStr"/>
-      <c r="P123" s="4" t="n"/>
+      <c r="P123" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q123" s="3" t="inlineStr"/>
       <c r="R123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_soul_stamp.tres</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>demon_spirit_net</t>
+          <t>demon_soul_stamp</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8982,7 +8976,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>缚魂网</t>
+          <t>魂印</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -8990,7 +8984,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -9010,16 +9004,16 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>状态(exposed)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -9037,12 +9031,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_spirit_net.tres</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>demon_ten_thousand_sacrifice</t>
+          <t>demon_spirit_net</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -9052,15 +9046,15 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>万祭归一</t>
+          <t>缚魂网</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -9070,34 +9064,34 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="L125" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>状态(soul_mark)</t>
         </is>
       </c>
       <c r="N125" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="4" t="n"/>
@@ -9107,12 +9101,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
+          <t>characters/demonic_cultivator/cards/phase3/demon_ten_thousand_sacrifice.tres</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>san_hun_tong_fen</t>
+          <t>demon_ten_thousand_sacrifice</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -9122,7 +9116,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>三魂同焚</t>
+          <t>万祭归一</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9140,27 +9134,35 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_detonate_effect</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="n"/>
-      <c r="M126" s="3" t="inlineStr"/>
-      <c r="N126" s="4" t="n"/>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="O126" s="3" t="inlineStr"/>
       <c r="P126" s="4" t="n"/>
       <c r="Q126" s="3" t="inlineStr"/>
@@ -9169,12 +9171,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
+          <t>characters/demonic_cultivator/cards/san_hun_tong_fen.tres</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>shadow_step</t>
+          <t>san_hun_tong_fen</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -9184,20 +9186,20 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>影遁</t>
+          <t>三魂同焚</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -9207,22 +9209,20 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>牌堆检索</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>configured_soul_mark_detonate_effect</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n"/>
       <c r="M127" s="3" t="inlineStr"/>
       <c r="N127" s="4" t="n"/>
       <c r="O127" s="3" t="inlineStr"/>
@@ -9233,12 +9233,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
+          <t>characters/demonic_cultivator/cards/shadow_step.tres</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>she_hun_xu_yuan</t>
+          <t>shadow_step</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>摄魂续元</t>
+          <t>影遁</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -9271,48 +9271,38 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>configured_soul_mark_consume_effect</t>
-        </is>
-      </c>
-      <c r="L128" s="4" t="n"/>
-      <c r="M128" s="3" t="inlineStr">
-        <is>
-          <t>治疗</t>
-        </is>
-      </c>
-      <c r="N128" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O128" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P128" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>牌堆检索</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr"/>
+      <c r="N128" s="4" t="n"/>
+      <c r="O128" s="3" t="inlineStr"/>
+      <c r="P128" s="4" t="n"/>
       <c r="Q128" s="3" t="inlineStr"/>
       <c r="R128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
+          <t>characters/demonic_cultivator/cards/she_hun_xu_yuan.tres</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>soul_drain</t>
+          <t>she_hun_xu_yuan</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9322,7 +9312,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>摄魂</t>
+          <t>摄魂续元</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9330,7 +9320,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -9340,7 +9330,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -9350,28 +9340,26 @@
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L129" s="4" t="n">
-        <v>5</v>
-      </c>
+          <t>configured_soul_mark_consume_effect</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="n"/>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="N129" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>状态(soul_mark)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="P129" s="4" t="n">
@@ -9383,12 +9371,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
+          <t>characters/demonic_cultivator/cards/soul_drain.tres</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>yin_sha_jue</t>
+          <t>soul_drain</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9398,7 +9386,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>引煞诀</t>
+          <t>摄魂</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9416,7 +9404,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
@@ -9426,7 +9414,7 @@
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -9435,40 +9423,46 @@
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>状态(sha_qi)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O130" s="3" t="inlineStr"/>
-      <c r="P130" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>状态(soul_mark)</t>
+        </is>
+      </c>
+      <c r="P130" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q130" s="3" t="inlineStr"/>
       <c r="R130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
+          <t>characters/demonic_cultivator/cards/yin_sha_jue.tres</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>flying_sword</t>
+          <t>yin_sha_jue</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>剑修</t>
+          <t>魔修</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>飞剑</t>
+          <t>引煞诀</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9486,7 +9480,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -9496,7 +9490,7 @@
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -9507,8 +9501,14 @@
       <c r="L131" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M131" s="3" t="inlineStr"/>
-      <c r="N131" s="4" t="n"/>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>状态(sha_qi)</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="4" t="n"/>
       <c r="Q131" s="3" t="inlineStr"/>
@@ -9517,12 +9517,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
+          <t>characters/sword_cultivator/cards/flying_sword.tres</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>guard_sword</t>
+          <t>flying_sword</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>御剑守心</t>
+          <t>飞剑</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -9565,20 +9565,14 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M132" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N132" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr"/>
+      <c r="N132" s="4" t="n"/>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="4" t="n"/>
       <c r="Q132" s="3" t="inlineStr"/>
@@ -9587,12 +9581,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
+          <t>characters/sword_cultivator/cards/guard_sword.tres</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>sword_blade_embryo</t>
+          <t>guard_sword</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9602,7 +9596,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>剑胎初鸣</t>
+          <t>御剑守心</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9610,7 +9604,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -9635,15 +9629,15 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N133" s="4" t="n">
@@ -9657,12 +9651,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_blade_embryo.tres</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>sword_breath_return</t>
+          <t>sword_blade_embryo</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9672,7 +9666,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>回风纳息</t>
+          <t>剑胎初鸣</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9680,7 +9674,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -9700,12 +9694,12 @@
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="L134" s="4" t="n">
@@ -9713,7 +9707,7 @@
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>状态(qi_flow)</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N134" s="4" t="n">
@@ -9727,12 +9721,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_breath_return.tres</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_cut</t>
+          <t>sword_breath_return</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9742,7 +9736,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>云隙递剑</t>
+          <t>回风纳息</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -9750,12 +9744,12 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -9770,20 +9764,20 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(qi_flow)</t>
         </is>
       </c>
       <c r="N135" s="4" t="n">
@@ -9797,12 +9791,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_cut.tres</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>sword_cloud_scroll</t>
+          <t>sword_cloud_cut</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9812,7 +9806,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>云海剑书</t>
+          <t>云隙递剑</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -9820,17 +9814,17 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -9840,19 +9834,25 @@
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L136" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M136" s="3" t="inlineStr"/>
-      <c r="N136" s="4" t="n"/>
+      <c r="N136" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O136" s="3" t="inlineStr"/>
       <c r="P136" s="4" t="n"/>
       <c r="Q136" s="3" t="inlineStr"/>
@@ -9861,12 +9861,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_cloud_scroll.tres</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>sword_flow_shift</t>
+          <t>sword_cloud_scroll</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>流光换形</t>
+          <t>云海剑书</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -9909,20 +9909,14 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M137" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N137" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="M137" s="3" t="inlineStr"/>
+      <c r="N137" s="4" t="n"/>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="4" t="n"/>
       <c r="Q137" s="3" t="inlineStr"/>
@@ -9931,12 +9925,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_flow_shift.tres</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>sword_forge_spark</t>
+          <t>sword_flow_shift</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9946,7 +9940,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>炉火铸锋</t>
+          <t>流光换形</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -9964,7 +9958,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -9974,7 +9968,7 @@
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -9983,15 +9977,15 @@
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N138" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138" s="3" t="inlineStr"/>
       <c r="P138" s="4" t="n"/>
@@ -10001,12 +9995,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_forge_spark.tres</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>sword_furnace_open</t>
+          <t>sword_forge_spark</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -10016,15 +10010,15 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>剑炉大开</t>
+          <t>炉火铸锋</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -10034,7 +10028,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -10049,11 +10043,11 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -10061,7 +10055,7 @@
         </is>
       </c>
       <c r="N139" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="4" t="n"/>
@@ -10071,12 +10065,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_furnace_open.tres</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>sword_hidden_edge</t>
+          <t>sword_furnace_open</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -10086,15 +10080,15 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>藏锋式</t>
+          <t>剑炉大开</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -10104,7 +10098,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -10114,19 +10108,25 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
+          <t>状态(muscle)</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
           <t>状态(forge_sword)</t>
         </is>
       </c>
-      <c r="L140" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M140" s="3" t="inlineStr"/>
-      <c r="N140" s="4" t="n"/>
+      <c r="N140" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O140" s="3" t="inlineStr"/>
       <c r="P140" s="4" t="n"/>
       <c r="Q140" s="3" t="inlineStr"/>
@@ -10135,12 +10135,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hidden_edge.tres</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>sword_hundred_forge</t>
+          <t>sword_hidden_edge</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>百炼锋芒</t>
+          <t>藏锋式</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M141" s="3" t="inlineStr"/>
       <c r="N141" s="4" t="n"/>
@@ -10199,12 +10199,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_hundred_forge.tres</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>sword_iron_cleave</t>
+          <t>sword_hundred_forge</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10214,20 +10214,20 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>斩铁成锋</t>
+          <t>百炼锋芒</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -10242,22 +10242,18 @@
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="L142" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M142" s="3" t="inlineStr">
-        <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr"/>
       <c r="N142" s="4" t="n"/>
       <c r="O142" s="3" t="inlineStr"/>
       <c r="P142" s="4" t="n"/>
@@ -10267,12 +10263,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_iron_cleave.tres</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>sword_light_step</t>
+          <t>sword_iron_cleave</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10282,25 +10278,25 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>剑步轻灵</t>
+          <t>斩铁成锋</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -10310,25 +10306,23 @@
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N143" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="n"/>
       <c r="O143" s="3" t="inlineStr"/>
       <c r="P143" s="4" t="n"/>
       <c r="Q143" s="3" t="inlineStr"/>
@@ -10337,12 +10331,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_light_step.tres</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>sword_marrow_forge</t>
+          <t>sword_light_step</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10352,11 +10346,11 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>洗髓铸刃</t>
+          <t>剑步轻灵</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
@@ -10370,7 +10364,7 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -10389,11 +10383,11 @@
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="N144" s="4" t="n">
@@ -10407,12 +10401,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_marrow_forge.tres</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>sword_probe_meridian</t>
+          <t>sword_marrow_forge</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10422,7 +10416,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>剑影探脉</t>
+          <t>洗髓铸刃</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
@@ -10430,17 +10424,17 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -10450,45 +10444,39 @@
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L145" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N145" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O145" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="P145" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O145" s="3" t="inlineStr"/>
+      <c r="P145" s="4" t="n"/>
       <c r="Q145" s="3" t="inlineStr"/>
       <c r="R145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_probe_meridian.tres</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>sword_ring_sheath</t>
+          <t>sword_probe_meridian</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10498,7 +10486,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>剑鸣归鞘</t>
+          <t>剑影探脉</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -10506,17 +10494,17 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
@@ -10531,34 +10519,40 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L146" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" s="3" t="inlineStr">
-        <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
       <c r="N146" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O146" s="3" t="inlineStr"/>
-      <c r="P146" s="4" t="n"/>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>状态(exposed)</t>
+        </is>
+      </c>
+      <c r="P146" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q146" s="3" t="inlineStr"/>
       <c r="R146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_ring_sheath.tres</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>sword_sky_river</t>
+          <t>sword_ring_sheath</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10568,52 +10562,52 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>天河倒卷</t>
+          <t>剑鸣归鞘</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>全体敌</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>抽牌</t>
         </is>
       </c>
       <c r="L147" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N147" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="4" t="n"/>
@@ -10623,12 +10617,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_sky_river.tres</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>sword_split_heaven</t>
+          <t>sword_sky_river</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10638,11 +10632,11 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>一剑开天</t>
+          <t>天河倒卷</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
@@ -10651,12 +10645,12 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -10666,7 +10660,7 @@
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -10675,14 +10669,16 @@
         </is>
       </c>
       <c r="L148" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>consume_status_effect</t>
-        </is>
-      </c>
-      <c r="N148" s="4" t="n"/>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O148" s="3" t="inlineStr"/>
       <c r="P148" s="4" t="n"/>
       <c r="Q148" s="3" t="inlineStr"/>
@@ -10691,12 +10687,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_split_heaven.tres</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>sword_temper_edge</t>
+          <t>sword_split_heaven</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10706,11 +10702,11 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>淬锋</t>
+          <t>一剑开天</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
@@ -10724,7 +10720,7 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -10734,7 +10730,7 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -10743,7 +10739,7 @@
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -10759,12 +10755,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_temper_edge.tres</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>sword_trial_edge</t>
+          <t>sword_temper_edge</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10774,7 +10770,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>试锋</t>
+          <t>淬锋</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -10802,7 +10798,7 @@
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -10811,16 +10807,14 @@
         </is>
       </c>
       <c r="L150" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>状态(forge_sword)</t>
-        </is>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>consume_status_effect</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="n"/>
       <c r="O150" s="3" t="inlineStr"/>
       <c r="P150" s="4" t="n"/>
       <c r="Q150" s="3" t="inlineStr"/>
@@ -10829,12 +10823,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_trial_edge.tres</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>sword_void_roam</t>
+          <t>sword_trial_edge</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10844,11 +10838,11 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>太虚游剑</t>
+          <t>试锋</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
@@ -10862,7 +10856,7 @@
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>暗金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -10881,36 +10875,30 @@
         </is>
       </c>
       <c r="L151" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(forge_sword)</t>
         </is>
       </c>
       <c r="N151" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O151" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="P151" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O151" s="3" t="inlineStr"/>
+      <c r="P151" s="4" t="n"/>
       <c r="Q151" s="3" t="inlineStr"/>
       <c r="R151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_void_roam.tres</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>sword_wash_blade</t>
+          <t>sword_void_roam</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10920,25 +10908,25 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>洗剑诀</t>
+          <t>太虚游剑</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>暗金</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -10948,33 +10936,45 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
           <t>抽牌</t>
         </is>
       </c>
-      <c r="L152" s="4" t="n">
+      <c r="N152" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M152" s="3" t="inlineStr"/>
-      <c r="N152" s="4" t="n"/>
-      <c r="O152" s="3" t="inlineStr"/>
-      <c r="P152" s="4" t="n"/>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="P152" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q152" s="3" t="inlineStr"/>
       <c r="R152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
+          <t>characters/sword_cultivator/cards/phase3/sword_wash_blade.tres</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>piercing_light</t>
+          <t>sword_wash_blade</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10984,53 +10984,47 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>一线天</t>
+          <t>洗剑诀</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>单体</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>蓝</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M153" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N153" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M153" s="3" t="inlineStr"/>
+      <c r="N153" s="4" t="n"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="4" t="n"/>
       <c r="Q153" s="3" t="inlineStr"/>
@@ -11039,12 +11033,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
+          <t>characters/sword_cultivator/cards/piercing_light.tres</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>sword_blood_curse</t>
+          <t>piercing_light</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -11054,11 +11048,11 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>血祭剑咒</t>
+          <t>一线天</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
@@ -11087,40 +11081,34 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L154" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N154" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O154" s="3" t="inlineStr">
-        <is>
-          <t>状态(bleed)</t>
-        </is>
-      </c>
-      <c r="P154" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="O154" s="3" t="inlineStr"/>
+      <c r="P154" s="4" t="n"/>
       <c r="Q154" s="3" t="inlineStr"/>
       <c r="R154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
+          <t>characters/sword_cultivator/cards/sword_blood_curse.tres</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>sword_energy_charge</t>
+          <t>sword_blood_curse</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -11130,25 +11118,25 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>凝气术</t>
+          <t>血祭剑咒</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11163,34 +11151,40 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="L155" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>状态(energy_charge)</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="N155" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O155" s="3" t="inlineStr"/>
-      <c r="P155" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>状态(bleed)</t>
+        </is>
+      </c>
+      <c r="P155" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q155" s="3" t="inlineStr"/>
       <c r="R155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
+          <t>characters/sword_cultivator/cards/sword_energy_charge.tres</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>sword_guard_formation</t>
+          <t>sword_energy_charge</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -11200,15 +11194,15 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>万剑护体</t>
+          <t>凝气术</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>功法</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -11218,7 +11212,7 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -11233,14 +11227,20 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_guard)</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L156" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M156" s="3" t="inlineStr"/>
-      <c r="N156" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>状态(energy_charge)</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O156" s="3" t="inlineStr"/>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="3" t="inlineStr"/>
@@ -11249,12 +11249,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
+          <t>characters/sword_cultivator/cards/sword_guard_formation.tres</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>sword_heart</t>
+          <t>sword_guard_formation</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -11264,11 +11264,11 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>剑心通明</t>
+          <t>万剑护体</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
@@ -11282,35 +11282,29 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>状态(muscle)</t>
+          <t>状态(sword_guard)</t>
         </is>
       </c>
       <c r="L157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M157" s="3" t="inlineStr">
-        <is>
-          <t>状态(qi_flow)</t>
-        </is>
-      </c>
-      <c r="N157" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr"/>
+      <c r="N157" s="4" t="n"/>
       <c r="O157" s="3" t="inlineStr"/>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="3" t="inlineStr"/>
@@ -11319,12 +11313,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
+          <t>characters/sword_cultivator/cards/sword_heart.tres</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>sword_nurture</t>
+          <t>sword_heart</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11334,7 +11328,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>养剑诀</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -11342,7 +11336,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>功法</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -11352,7 +11346,7 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
@@ -11367,14 +11361,20 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>状态(sword_intent)</t>
+          <t>状态(muscle)</t>
         </is>
       </c>
       <c r="L158" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M158" s="3" t="inlineStr"/>
-      <c r="N158" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>状态(qi_flow)</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O158" s="3" t="inlineStr"/>
       <c r="P158" s="4" t="n"/>
       <c r="Q158" s="3" t="inlineStr"/>
@@ -11383,12 +11383,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
+          <t>characters/sword_cultivator/cards/sword_nurture.tres</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>sword_qi_draw</t>
+          <t>sword_nurture</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -11398,11 +11398,11 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>剑气引</t>
+          <t>养剑诀</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
@@ -11431,20 +11431,14 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>抽牌</t>
+          <t>状态(sword_intent)</t>
         </is>
       </c>
       <c r="L159" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M159" s="3" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="N159" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="M159" s="3" t="inlineStr"/>
+      <c r="N159" s="4" t="n"/>
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="4" t="n"/>
       <c r="Q159" s="3" t="inlineStr"/>
@@ -11453,12 +11447,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
+          <t>characters/sword_cultivator/cards/sword_qi_draw.tres</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>sword_rain</t>
+          <t>sword_qi_draw</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -11468,47 +11462,53 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>剑雨</t>
+          <t>剑气引</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M160" s="3" t="inlineStr"/>
-      <c r="N160" s="4" t="n"/>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="N160" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="3" t="inlineStr"/>
@@ -11517,12 +11517,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
+          <t>characters/sword_cultivator/cards/sword_rain.tres</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>sword_shadow_strike</t>
+          <t>sword_rain</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -11532,11 +11532,11 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>瞬影剑</t>
+          <t>剑雨</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
@@ -11545,22 +11545,22 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -11569,16 +11569,10 @@
         </is>
       </c>
       <c r="L161" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M161" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr"/>
+      <c r="N161" s="4" t="n"/>
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="4" t="n"/>
       <c r="Q161" s="3" t="inlineStr"/>
@@ -11587,12 +11581,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
+          <t>characters/sword_cultivator/cards/sword_shadow_strike.tres</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>sword_star_shatter</t>
+          <t>sword_shadow_strike</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -11602,11 +11596,11 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>碎星斩</t>
+          <t>瞬影剑</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
@@ -11620,29 +11614,35 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>target_status_bonus_damage_effect</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L162" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M162" s="3" t="inlineStr"/>
-      <c r="N162" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O162" s="3" t="inlineStr"/>
       <c r="P162" s="4" t="n"/>
       <c r="Q162" s="3" t="inlineStr"/>
@@ -11651,12 +11651,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
+          <t>characters/sword_cultivator/cards/sword_star_shatter.tres</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>sword_wanjian</t>
+          <t>sword_star_shatter</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -11666,11 +11666,11 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>万剑归宗</t>
+          <t>碎星斩</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
@@ -11699,11 +11699,11 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>player_status_damage_effect</t>
+          <t>target_status_bonus_damage_effect</t>
         </is>
       </c>
       <c r="L163" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M163" s="3" t="inlineStr"/>
       <c r="N163" s="4" t="n"/>
@@ -11715,12 +11715,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wanjian.tres</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>sword_water_break</t>
+          <t>sword_wanjian</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11730,11 +11730,11 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>断水剑</t>
+          <t>万剑归宗</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -11758,25 +11758,19 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>player_status_damage_effect</t>
         </is>
       </c>
       <c r="L164" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M164" s="3" t="inlineStr">
-        <is>
-          <t>状态(exposed)</t>
-        </is>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr"/>
+      <c r="N164" s="4" t="n"/>
       <c r="O164" s="3" t="inlineStr"/>
       <c r="P164" s="4" t="n"/>
       <c r="Q164" s="3" t="inlineStr"/>
@@ -11785,12 +11779,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
+          <t>characters/sword_cultivator/cards/sword_water_break.tres</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>sword_wind_return</t>
+          <t>sword_water_break</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11800,11 +11794,11 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>回风剑</t>
+          <t>断水剑</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
@@ -11818,7 +11812,7 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -11828,7 +11822,7 @@
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -11837,15 +11831,15 @@
         </is>
       </c>
       <c r="L165" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>状态(exposed)</t>
         </is>
       </c>
       <c r="N165" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O165" s="3" t="inlineStr"/>
       <c r="P165" s="4" t="n"/>
@@ -11855,22 +11849,22 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ash_heart_guard.tres</t>
+          <t>characters/sword_cultivator/cards/sword_wind_return.tres</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ash_heart_guard</t>
+          <t>sword_wind_return</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>剑修</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>灰烬护心</t>
+          <t>回风剑</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -11878,17 +11872,17 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
@@ -11898,19 +11892,25 @@
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>木</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L166" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M166" s="3" t="inlineStr"/>
-      <c r="N166" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="O166" s="3" t="inlineStr"/>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="3" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>common_cards/circulating_breath.tres</t>
+          <t>common_cards/ash_heart_guard.tres</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>circulating_breath</t>
+          <t>ash_heart_guard</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>周天吐纳</t>
+          <t>灰烬护心</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -11967,20 +11967,14 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L167" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M167" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N167" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="4" t="n"/>
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -11989,12 +11983,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>common_cards/defend.tres</t>
+          <t>common_cards/circulating_breath.tres</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>circulating_breath</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -12004,7 +11998,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>周天吐纳</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -12043,8 +12037,14 @@
       <c r="L168" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M168" s="3" t="inlineStr"/>
-      <c r="N168" s="4" t="n"/>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O168" s="3" t="inlineStr"/>
       <c r="P168" s="4" t="n"/>
       <c r="Q168" s="3" t="inlineStr"/>
@@ -12053,12 +12053,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>common_cards/discard_aegis.tres</t>
+          <t>common_cards/defend.tres</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>discard_aegis</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>弃念成罡</t>
+          <t>防御</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -12101,11 +12101,11 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="L169" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M169" s="3" t="inlineStr"/>
       <c r="N169" s="4" t="n"/>
@@ -12117,12 +12117,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>common_cards/embers_return.tres</t>
+          <t>common_cards/discard_aegis.tres</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>embers_return</t>
+          <t>discard_aegis</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>烬归灵台</t>
+          <t>弃念成罡</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
@@ -12165,20 +12165,14 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L170" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M170" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N170" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr"/>
+      <c r="N170" s="4" t="n"/>
       <c r="O170" s="3" t="inlineStr"/>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="3" t="inlineStr"/>
@@ -12187,12 +12181,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>common_cards/flowing_cloud_guard.tres</t>
+          <t>common_cards/embers_return.tres</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>flowing_cloud_guard</t>
+          <t>embers_return</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -12202,7 +12196,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>流云护身</t>
+          <t>烬归灵台</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12225,7 +12219,7 @@
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -12235,12 +12229,20 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="n"/>
-      <c r="M171" s="3" t="inlineStr"/>
-      <c r="N171" s="4" t="n"/>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -12249,12 +12251,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>common_cards/ink_flow_slash.tres</t>
+          <t>common_cards/flowing_cloud_guard.tres</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ink_flow_slash</t>
+          <t>flowing_cloud_guard</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12264,7 +12266,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>墨流斩</t>
+          <t>流云护身</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -12272,17 +12274,17 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -12297,20 +12299,12 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L172" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M172" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>计数增幅</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="n"/>
+      <c r="M172" s="3" t="inlineStr"/>
+      <c r="N172" s="4" t="n"/>
       <c r="O172" s="3" t="inlineStr"/>
       <c r="P172" s="4" t="n"/>
       <c r="Q172" s="3" t="inlineStr"/>
@@ -12319,12 +12313,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>common_cards/momentum_pursuit.tres</t>
+          <t>common_cards/ink_flow_slash.tres</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>momentum_pursuit</t>
+          <t>ink_flow_slash</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -12334,7 +12328,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>乘势追击</t>
+          <t>墨流斩</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12352,7 +12346,7 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -12367,14 +12361,20 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>计数增幅</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L173" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M173" s="3" t="inlineStr"/>
-      <c r="N173" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -12383,12 +12383,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>common_cards/muscle_resonance_strike.tres</t>
+          <t>common_cards/momentum_pursuit.tres</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>muscle_resonance_strike</t>
+          <t>momentum_pursuit</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>劲气共鸣</t>
+          <t>乘势追击</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
@@ -12431,20 +12431,14 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>计数增幅</t>
         </is>
       </c>
       <c r="L174" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M174" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="N174" s="4" t="n">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr"/>
+      <c r="N174" s="4" t="n"/>
       <c r="O174" s="3" t="inlineStr"/>
       <c r="P174" s="4" t="n"/>
       <c r="Q174" s="3" t="inlineStr"/>
@@ -12453,12 +12447,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>common_cards/returning_light.tres</t>
+          <t>common_cards/muscle_resonance_strike.tres</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>returning_light</t>
+          <t>muscle_resonance_strike</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -12468,7 +12462,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>回光返照</t>
+          <t>劲气共鸣</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
@@ -12476,22 +12470,22 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -12501,14 +12495,20 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L175" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M175" s="3" t="inlineStr"/>
-      <c r="N175" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="O175" s="3" t="inlineStr"/>
       <c r="P175" s="4" t="n"/>
       <c r="Q175" s="3" t="inlineStr"/>
@@ -12517,12 +12517,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>common_cards/spirit_stone_needle.tres</t>
+          <t>common_cards/returning_light.tres</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>spirit_stone_needle</t>
+          <t>returning_light</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -12532,25 +12532,25 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>灵石飞针</t>
+          <t>回光返照</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>蓝</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
@@ -12565,11 +12565,11 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="L176" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M176" s="3" t="inlineStr"/>
       <c r="N176" s="4" t="n"/>
@@ -12581,12 +12581,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/blood_debt_curse.tres</t>
+          <t>common_cards/spirit_stone_needle.tres</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>blood_debt_curse</t>
+          <t>spirit_stone_needle</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>血债</t>
+          <t>灵石飞针</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
@@ -12604,12 +12604,12 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -12629,11 +12629,11 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="L177" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M177" s="3" t="inlineStr"/>
       <c r="N177" s="4" t="n"/>
@@ -12645,12 +12645,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/eclipse_scar.tres</t>
+          <t>common_cards/status/blood_debt_curse.tres</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>eclipse_scar</t>
+          <t>blood_debt_curse</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>蚀痕</t>
+          <t>血债</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -12691,8 +12691,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K178" s="3" t="inlineStr"/>
-      <c r="L178" s="4" t="n"/>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M178" s="3" t="inlineStr"/>
       <c r="N178" s="4" t="n"/>
       <c r="O178" s="3" t="inlineStr"/>
@@ -12703,12 +12709,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/heart_demon.tres</t>
+          <t>common_cards/status/eclipse_scar.tres</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>heart_demon</t>
+          <t>eclipse_scar</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -12718,7 +12724,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>心魔</t>
+          <t>蚀痕</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
@@ -12761,12 +12767,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/karmic_fire_curse.tres</t>
+          <t>common_cards/status/heart_demon.tres</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>karmic_fire_curse</t>
+          <t>heart_demon</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -12776,11 +12782,11 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>心魔</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
@@ -12799,7 +12805,7 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -12807,14 +12813,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="L180" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="K180" s="3" t="inlineStr"/>
+      <c r="L180" s="4" t="n"/>
       <c r="M180" s="3" t="inlineStr"/>
       <c r="N180" s="4" t="n"/>
       <c r="O180" s="3" t="inlineStr"/>
@@ -12825,12 +12825,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>common_cards/status/underworld_writ.tres</t>
+          <t>common_cards/status/karmic_fire_curse.tres</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>underworld_writ</t>
+          <t>karmic_fire_curse</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -12840,11 +12840,11 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>判牒</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
@@ -12871,8 +12871,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K181" s="3" t="inlineStr"/>
-      <c r="L181" s="4" t="n"/>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="4" t="n"/>
       <c r="O181" s="3" t="inlineStr"/>
@@ -12883,12 +12889,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>common_cards/strike.tres</t>
+          <t>common_cards/status/underworld_writ.tres</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>underworld_writ</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -12898,20 +12904,20 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>判牒</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -12929,14 +12935,8 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="K182" s="3" t="inlineStr"/>
+      <c r="L182" s="4" t="n"/>
       <c r="M182" s="3" t="inlineStr"/>
       <c r="N182" s="4" t="n"/>
       <c r="O182" s="3" t="inlineStr"/>
@@ -12947,12 +12947,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>common_cards/toxin.tres</t>
+          <t>common_cards/strike.tres</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>toxin</t>
+          <t>strike</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>浊气</t>
+          <t>打击</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
@@ -12993,8 +12993,14 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K183" s="3" t="inlineStr"/>
-      <c r="L183" s="4" t="n"/>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="4" t="n"/>
       <c r="O183" s="3" t="inlineStr"/>
@@ -13005,22 +13011,22 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/attack_guard_unity.tres</t>
+          <t>common_cards/toxin.tres</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>attack_guard_unity</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>融合</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>攻守合一</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -13028,22 +13034,22 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>白</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
@@ -13051,22 +13057,10 @@
           <t>无</t>
         </is>
       </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L184" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M184" s="3" t="inlineStr">
-        <is>
-          <t>护体</t>
-        </is>
-      </c>
-      <c r="N184" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="K184" s="3" t="inlineStr"/>
+      <c r="L184" s="4" t="n"/>
+      <c r="M184" s="3" t="inlineStr"/>
+      <c r="N184" s="4" t="n"/>
       <c r="O184" s="3" t="inlineStr"/>
       <c r="P184" s="4" t="n"/>
       <c r="Q184" s="3" t="inlineStr"/>
@@ -13075,12 +13069,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/blood_beast_rend.tres</t>
+          <t>fusion_cards/attack_guard_unity.tres</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>blood_beast_rend</t>
+          <t>attack_guard_unity</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -13090,7 +13084,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>血兽撕咬</t>
+          <t>攻守合一</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
@@ -13118,7 +13112,7 @@
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
@@ -13127,15 +13121,15 @@
         </is>
       </c>
       <c r="L185" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>自损</t>
+          <t>护体</t>
         </is>
       </c>
       <c r="N185" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="4" t="n"/>
@@ -13145,12 +13139,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/demon_rain_swordfire.tres</t>
+          <t>fusion_cards/blood_beast_rend.tres</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>demon_rain_swordfire</t>
+          <t>blood_beast_rend</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -13160,52 +13154,52 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>魔雨剑火</t>
+          <t>血兽撕咬</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>自损</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>全体敌</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="L186" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M186" s="3" t="inlineStr">
-        <is>
-          <t>自损</t>
-        </is>
-      </c>
-      <c r="N186" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="O186" s="3" t="inlineStr"/>
       <c r="P186" s="4" t="n"/>
@@ -13215,12 +13209,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>fusion_cards/sword_shield_chime.tres</t>
+          <t>fusion_cards/demon_rain_swordfire.tres</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>sword_shield_chime</t>
+          <t>demon_rain_swordfire</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -13230,11 +13224,11 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>剑盾合鸣</t>
+          <t>魔雨剑火</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
@@ -13243,12 +13237,12 @@
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>单体</t>
+          <t>全体敌</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>蓝</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -13258,7 +13252,7 @@
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -13267,42 +13261,112 @@
         </is>
       </c>
       <c r="L187" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>护体</t>
+          <t>自损</t>
         </is>
       </c>
       <c r="N187" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O187" s="3" t="inlineStr">
-        <is>
-          <t>抽牌</t>
-        </is>
-      </c>
-      <c r="P187" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O187" s="3" t="inlineStr"/>
+      <c r="P187" s="4" t="n"/>
       <c r="Q187" s="3" t="inlineStr"/>
       <c r="R187" s="4" t="n"/>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>fusion_cards/sword_shield_chime.tres</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>sword_shield_chime</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>融合</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>剑盾合鸣</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>护体</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
+          <t>抽牌</t>
+        </is>
+      </c>
+      <c r="P188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q188" s="3" t="inlineStr"/>
+      <c r="R188" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="F2:F187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"攻击,技能,功法"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自身,单体,全体敌,所有"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"白,蓝,金,暗金"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"无,金,木,水,火,土"</formula1>
     </dataValidation>
   </dataValidations>
